--- a/budget-hours/Karbon_Budget_Hours_2026-10.xlsx
+++ b/budget-hours/Karbon_Budget_Hours_2026-10.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4017" uniqueCount="650">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4017" uniqueCount="651">
   <si>
     <t xml:space="preserve">Enter in Karbon  (Time &amp; Budget → Add Budget Estimate)</t>
   </si>
@@ -1157,7 +1157,7 @@
     <t xml:space="preserve">Mountain Trade Supply Inc|Accounting|Run Payroll in Paychex|Bi-weekly</t>
   </si>
   <si>
-    <t xml:space="preserve">Payroll time ÷ pay periods per month (75% share). Payroll takeover in progress (Paychex/401k/PFML); tax audit budgeted separately. Confirm payroll is ongoing.</t>
+    <t xml:space="preserve">Payroll time ÷ pay periods per month (75% share). Payroll takeover in progress (Paychex/401k/PFML); tax audit budgeted separately. Confirm payroll is ongoing. Review = Lisa oversight, 15 min per occurrence (work moving to Jessica).</t>
   </si>
   <si>
     <t xml:space="preserve">Mountain Trade Supply Inc|Monthly Financials|Month End Close|Monthly</t>
@@ -1343,7 +1343,7 @@
     <t xml:space="preserve">VV1012 LLC|Payroll|Bi-Weekly QuickBooks Payroll Processing|Bi-weekly</t>
   </si>
   <si>
-    <t xml:space="preserve">Payroll time ÷ pay periods per month.</t>
+    <t xml:space="preserve">Payroll time ÷ pay periods per month. Review = Lisa oversight, 15 min per occurrence (work moving to Jessica).</t>
   </si>
   <si>
     <t xml:space="preserve">VV1012 LLC|Monthly Financials|Month End Close|Monthly</t>
@@ -1361,6 +1361,9 @@
     <t xml:space="preserve">VV1012 LLC|Default|Weekly Bank Settlements - From Toast|Weekly</t>
   </si>
   <si>
+    <t xml:space="preserve">Weekly bookkeeping/settlement time ÷ weeks per month. Review = Lisa oversight, 15 min per occurrence (work moving to Jessica).</t>
+  </si>
+  <si>
     <t xml:space="preserve">VV1012 LLC|Bookkeeping|Weekly Cash Flow Review|Weekly</t>
   </si>
   <si>
@@ -1382,7 +1385,7 @@
     <t xml:space="preserve">VVNS LLC|Accounting|Bi-Weekly QuickBooks Payroll Processing|Bi-weekly</t>
   </si>
   <si>
-    <t xml:space="preserve">Payroll time ÷ pay periods per month. Opened Sept 2026 – provisional, modelled on VV1012 (operating Toast restaurant). Revisit after 2–3 months open.</t>
+    <t xml:space="preserve">Payroll time ÷ pay periods per month. Opened Sept 2026 – provisional, modelled on VV1012 (operating Toast restaurant). Revisit after 2–3 months open. Review = Lisa oversight, 15 min per occurrence (work moving to Jessica).</t>
   </si>
   <si>
     <t xml:space="preserve">VVNS LLC|Monthly Financials|Month End Close|Monthly</t>
@@ -1400,7 +1403,7 @@
     <t xml:space="preserve">VVNS LLC|Accounting|Weekly Bank Settlements - From Toast|Weekly</t>
   </si>
   <si>
-    <t xml:space="preserve">Weekly bookkeeping/settlement time ÷ weeks per month. Opened Sept 2026 – provisional, modelled on VV1012 (operating Toast restaurant). Revisit after 2–3 months open.</t>
+    <t xml:space="preserve">Weekly bookkeeping/settlement time ÷ weeks per month. Opened Sept 2026 – provisional, modelled on VV1012 (operating Toast restaurant). Revisit after 2–3 months open. Review = Lisa oversight, 15 min per occurrence (work moving to Jessica).</t>
   </si>
   <si>
     <t xml:space="preserve">VVNS LLC|Accounting|Weekly Cash Flow Review|Weekly</t>
@@ -4790,11 +4793,11 @@
       </c>
       <c r="F70" s="6" t="n">
         <f aca="false">ROUND('Recurring Budgets'!G76*60,0)/1440</f>
-        <v>0</v>
+        <v>0.0104166666666667</v>
       </c>
       <c r="G70" s="7" t="n">
         <f aca="false">ROUND('Recurring Budgets'!G76*Assumptions!$B$5,0)</f>
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="H70" s="8" t="str">
         <f aca="false">'Recurring Budgets'!L76</f>
@@ -5875,11 +5878,11 @@
       </c>
       <c r="F105" s="6" t="n">
         <f aca="false">ROUND('Recurring Budgets'!G111*60,0)/1440</f>
-        <v>0</v>
+        <v>0.0104166666666667</v>
       </c>
       <c r="G105" s="7" t="n">
         <f aca="false">ROUND('Recurring Budgets'!G111*Assumptions!$B$5,0)</f>
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="H105" s="8" t="str">
         <f aca="false">'Recurring Budgets'!L111</f>
@@ -5968,11 +5971,11 @@
       </c>
       <c r="F108" s="6" t="n">
         <f aca="false">ROUND('Recurring Budgets'!G114*60,0)/1440</f>
-        <v>0</v>
+        <v>0.0104166666666667</v>
       </c>
       <c r="G108" s="7" t="n">
         <f aca="false">ROUND('Recurring Budgets'!G114*Assumptions!$B$5,0)</f>
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="H108" s="8" t="str">
         <f aca="false">'Recurring Budgets'!L114</f>
@@ -6123,11 +6126,11 @@
       </c>
       <c r="F113" s="6" t="n">
         <f aca="false">ROUND('Recurring Budgets'!G119*60,0)/1440</f>
-        <v>0</v>
+        <v>0.0104166666666667</v>
       </c>
       <c r="G113" s="7" t="n">
         <f aca="false">ROUND('Recurring Budgets'!G119*Assumptions!$B$5,0)</f>
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="H113" s="8" t="str">
         <f aca="false">'Recurring Budgets'!L119</f>
@@ -6216,11 +6219,11 @@
       </c>
       <c r="F116" s="6" t="n">
         <f aca="false">ROUND('Recurring Budgets'!G122*60,0)/1440</f>
-        <v>0</v>
+        <v>0.0104166666666667</v>
       </c>
       <c r="G116" s="7" t="n">
         <f aca="false">ROUND('Recurring Budgets'!G122*Assumptions!$B$5,0)</f>
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="H116" s="8" t="str">
         <f aca="false">'Recurring Budgets'!L122</f>
@@ -8366,13 +8369,13 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8380,10 +8383,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="37" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C2" s="37" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8391,10 +8394,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="37" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C3" s="37" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8402,10 +8405,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="37" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C4" s="37" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8413,10 +8416,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="37" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C5" s="37" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8424,10 +8427,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="37" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C6" s="37" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8435,10 +8438,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="37" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C7" s="37" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8446,10 +8449,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="37" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C8" s="37" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8457,10 +8460,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="37" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C9" s="37" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8468,10 +8471,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="37" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C10" s="37" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8479,10 +8482,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="37" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C11" s="37" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8490,10 +8493,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="37" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C12" s="37" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
   </sheetData>
@@ -15150,15 +15153,15 @@
         <v>0.9167</v>
       </c>
       <c r="G76" s="15" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="H76" s="21" t="n">
         <f aca="false">F76+G76</f>
-        <v>0.9167</v>
+        <v>1.1667</v>
       </c>
       <c r="I76" s="2" t="n">
         <f aca="false">ROUND(H76*60,0)</f>
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="J76" s="2" t="n">
         <f aca="false">ROUND(F76*60,0)</f>
@@ -15166,14 +15169,14 @@
       </c>
       <c r="K76" s="2" t="n">
         <f aca="false">ROUND(G76*60,0)</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L76" s="9" t="s">
         <v>185</v>
       </c>
       <c r="M76" s="22" t="n">
         <f aca="false">F76*IF(L76="CFO",Assumptions!$B$5,Assumptions!$B$4)+G76*Assumptions!$B$5</f>
-        <v>229.175</v>
+        <v>291.675</v>
       </c>
       <c r="N76" s="16" t="n">
         <f aca="false">F76*INDEX(Assumptions!$B$8:$B$14,MATCH(E76,Assumptions!$A$8:$A$14,0))</f>
@@ -15181,7 +15184,7 @@
       </c>
       <c r="O76" s="16" t="n">
         <f aca="false">G76*INDEX(Assumptions!$B$8:$B$14,MATCH(E76,Assumptions!$A$8:$A$14,0))</f>
-        <v>0</v>
+        <v>0.541666666666667</v>
       </c>
       <c r="P76" s="25" t="s">
         <v>232</v>
@@ -17360,15 +17363,15 @@
         <v>4.25</v>
       </c>
       <c r="G111" s="15" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="H111" s="21" t="n">
         <f aca="false">F111+G111</f>
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
       <c r="I111" s="2" t="n">
         <f aca="false">ROUND(H111*60,0)</f>
-        <v>255</v>
+        <v>270</v>
       </c>
       <c r="J111" s="2" t="n">
         <f aca="false">ROUND(F111*60,0)</f>
@@ -17376,14 +17379,14 @@
       </c>
       <c r="K111" s="2" t="n">
         <f aca="false">ROUND(G111*60,0)</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L111" s="9" t="s">
         <v>87</v>
       </c>
       <c r="M111" s="22" t="n">
         <f aca="false">F111*IF(L111="CFO",Assumptions!$B$5,Assumptions!$B$4)+G111*Assumptions!$B$5</f>
-        <v>403.75</v>
+        <v>466.25</v>
       </c>
       <c r="N111" s="16" t="n">
         <f aca="false">F111*INDEX(Assumptions!$B$8:$B$14,MATCH(E111,Assumptions!$A$8:$A$14,0))</f>
@@ -17391,7 +17394,7 @@
       </c>
       <c r="O111" s="16" t="n">
         <f aca="false">G111*INDEX(Assumptions!$B$8:$B$14,MATCH(E111,Assumptions!$A$8:$A$14,0))</f>
-        <v>0</v>
+        <v>0.541666666666667</v>
       </c>
       <c r="P111" s="28" t="s">
         <v>312</v>
@@ -17549,15 +17552,15 @@
         <v>1.0833</v>
       </c>
       <c r="G114" s="15" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="H114" s="21" t="n">
         <f aca="false">F114+G114</f>
-        <v>1.0833</v>
+        <v>1.3333</v>
       </c>
       <c r="I114" s="2" t="n">
         <f aca="false">ROUND(H114*60,0)</f>
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="J114" s="2" t="n">
         <f aca="false">ROUND(F114*60,0)</f>
@@ -17565,14 +17568,14 @@
       </c>
       <c r="K114" s="2" t="n">
         <f aca="false">ROUND(G114*60,0)</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L114" s="9" t="s">
         <v>87</v>
       </c>
       <c r="M114" s="22" t="n">
         <f aca="false">F114*IF(L114="CFO",Assumptions!$B$5,Assumptions!$B$4)+G114*Assumptions!$B$5</f>
-        <v>102.9135</v>
+        <v>165.4135</v>
       </c>
       <c r="N114" s="16" t="n">
         <f aca="false">F114*INDEX(Assumptions!$B$8:$B$14,MATCH(E114,Assumptions!$A$8:$A$14,0))</f>
@@ -17580,13 +17583,13 @@
       </c>
       <c r="O114" s="16" t="n">
         <f aca="false">G114*INDEX(Assumptions!$B$8:$B$14,MATCH(E114,Assumptions!$A$8:$A$14,0))</f>
-        <v>0</v>
+        <v>1.08333333333333</v>
       </c>
       <c r="P114" s="28" t="s">
         <v>312</v>
       </c>
       <c r="Q114" s="24" t="s">
-        <v>277</v>
+        <v>442</v>
       </c>
       <c r="R114" s="2" t="s">
         <v>229</v>
@@ -17594,7 +17597,7 @@
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="2" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B115" s="10" t="s">
         <v>76</v>
@@ -17649,7 +17652,7 @@
         <v>312</v>
       </c>
       <c r="Q115" s="24" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="R115" s="2" t="s">
         <v>229</v>
@@ -17657,7 +17660,7 @@
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="2" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B116" s="10" t="s">
         <v>81</v>
@@ -17721,7 +17724,7 @@
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="2" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B117" s="10" t="s">
         <v>81</v>
@@ -17784,7 +17787,7 @@
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="2" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B118" s="10" t="s">
         <v>82</v>
@@ -17840,7 +17843,7 @@
         <v>264</v>
       </c>
       <c r="Q118" s="24" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="R118" s="2" t="s">
         <v>229</v>
@@ -17848,7 +17851,7 @@
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B119" s="10" t="s">
         <v>82</v>
@@ -17866,15 +17869,15 @@
         <v>4.25</v>
       </c>
       <c r="G119" s="15" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="H119" s="21" t="n">
         <f aca="false">F119+G119</f>
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
       <c r="I119" s="2" t="n">
         <f aca="false">ROUND(H119*60,0)</f>
-        <v>255</v>
+        <v>270</v>
       </c>
       <c r="J119" s="2" t="n">
         <f aca="false">ROUND(F119*60,0)</f>
@@ -17882,14 +17885,14 @@
       </c>
       <c r="K119" s="2" t="n">
         <f aca="false">ROUND(G119*60,0)</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L119" s="9" t="s">
         <v>87</v>
       </c>
       <c r="M119" s="22" t="n">
         <f aca="false">F119*IF(L119="CFO",Assumptions!$B$5,Assumptions!$B$4)+G119*Assumptions!$B$5</f>
-        <v>403.75</v>
+        <v>466.25</v>
       </c>
       <c r="N119" s="16" t="n">
         <f aca="false">F119*INDEX(Assumptions!$B$8:$B$14,MATCH(E119,Assumptions!$A$8:$A$14,0))</f>
@@ -17897,13 +17900,13 @@
       </c>
       <c r="O119" s="16" t="n">
         <f aca="false">G119*INDEX(Assumptions!$B$8:$B$14,MATCH(E119,Assumptions!$A$8:$A$14,0))</f>
-        <v>0</v>
+        <v>0.541666666666667</v>
       </c>
       <c r="P119" s="27" t="s">
         <v>264</v>
       </c>
       <c r="Q119" s="24" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="R119" s="2" t="s">
         <v>229</v>
@@ -17911,7 +17914,7 @@
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="2" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B120" s="10" t="s">
         <v>82</v>
@@ -17966,7 +17969,7 @@
         <v>264</v>
       </c>
       <c r="Q120" s="24" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="R120" s="2" t="s">
         <v>229</v>
@@ -17974,7 +17977,7 @@
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="2" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B121" s="10" t="s">
         <v>82</v>
@@ -18029,7 +18032,7 @@
         <v>264</v>
       </c>
       <c r="Q121" s="24" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="R121" s="2" t="s">
         <v>229</v>
@@ -18037,7 +18040,7 @@
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="2" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B122" s="10" t="s">
         <v>82</v>
@@ -18055,15 +18058,15 @@
         <v>1.0833</v>
       </c>
       <c r="G122" s="15" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="H122" s="21" t="n">
         <f aca="false">F122+G122</f>
-        <v>1.0833</v>
+        <v>1.3333</v>
       </c>
       <c r="I122" s="2" t="n">
         <f aca="false">ROUND(H122*60,0)</f>
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="J122" s="2" t="n">
         <f aca="false">ROUND(F122*60,0)</f>
@@ -18071,14 +18074,14 @@
       </c>
       <c r="K122" s="2" t="n">
         <f aca="false">ROUND(G122*60,0)</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L122" s="9" t="s">
         <v>87</v>
       </c>
       <c r="M122" s="22" t="n">
         <f aca="false">F122*IF(L122="CFO",Assumptions!$B$5,Assumptions!$B$4)+G122*Assumptions!$B$5</f>
-        <v>102.9135</v>
+        <v>165.4135</v>
       </c>
       <c r="N122" s="16" t="n">
         <f aca="false">F122*INDEX(Assumptions!$B$8:$B$14,MATCH(E122,Assumptions!$A$8:$A$14,0))</f>
@@ -18086,13 +18089,13 @@
       </c>
       <c r="O122" s="16" t="n">
         <f aca="false">G122*INDEX(Assumptions!$B$8:$B$14,MATCH(E122,Assumptions!$A$8:$A$14,0))</f>
-        <v>0</v>
+        <v>1.08333333333333</v>
       </c>
       <c r="P122" s="27" t="s">
         <v>264</v>
       </c>
       <c r="Q122" s="24" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="R122" s="2" t="s">
         <v>229</v>
@@ -18100,7 +18103,7 @@
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="2" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B123" s="10" t="s">
         <v>82</v>
@@ -18155,7 +18158,7 @@
         <v>264</v>
       </c>
       <c r="Q123" s="24" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="R123" s="2" t="s">
         <v>229</v>
@@ -18163,7 +18166,7 @@
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="2" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B124" s="10" t="s">
         <v>83</v>
@@ -18227,7 +18230,7 @@
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="2" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B125" s="10" t="s">
         <v>83</v>
@@ -18282,7 +18285,7 @@
         <v>312</v>
       </c>
       <c r="Q125" s="24" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="R125" s="2" t="s">
         <v>235</v>
@@ -18337,34 +18340,34 @@
         <v>3</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>211</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>5</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="L1" s="5" t="s">
         <v>216</v>
@@ -18387,7 +18390,7 @@
         <v>11</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>231</v>
@@ -18396,16 +18399,16 @@
         <v>46295</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I2" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P2,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -18453,16 +18456,16 @@
         <v>46325</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>161</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="I3" s="16" t="n">
         <f aca="false">INDEX('1099 Oct 30'!$F$5:$F$45,MATCH(P3,'1099 Oct 30'!$A$5:$A$45,0))</f>
@@ -18487,7 +18490,7 @@
         <v>227</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="P3" s="2" t="s">
         <v>11</v>
@@ -18498,7 +18501,7 @@
         <v>11</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>231</v>
@@ -18507,16 +18510,16 @@
         <v>46325</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I4" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P4,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -18555,7 +18558,7 @@
         <v>16</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>237</v>
@@ -18564,16 +18567,16 @@
         <v>46303</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I5" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P5,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -18612,7 +18615,7 @@
         <v>16</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>240</v>
@@ -18621,16 +18624,16 @@
         <v>46314</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I6" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P6,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -18678,16 +18681,16 @@
         <v>46325</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>161</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="I7" s="16" t="n">
         <f aca="false">INDEX('1099 Oct 30'!$F$5:$F$45,MATCH(P7,'1099 Oct 30'!$A$5:$A$45,0))</f>
@@ -18712,7 +18715,7 @@
         <v>227</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="P7" s="2" t="s">
         <v>16</v>
@@ -18723,7 +18726,7 @@
         <v>19</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>243</v>
@@ -18732,16 +18735,16 @@
         <v>46265</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I8" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P8,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -18780,7 +18783,7 @@
         <v>22</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>231</v>
@@ -18789,16 +18792,16 @@
         <v>46295</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I9" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P9,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -18846,16 +18849,16 @@
         <v>46325</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>161</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="I10" s="16" t="n">
         <f aca="false">INDEX('1099 Oct 30'!$F$5:$F$45,MATCH(P10,'1099 Oct 30'!$A$5:$A$45,0))</f>
@@ -18880,7 +18883,7 @@
         <v>227</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="P10" s="2" t="s">
         <v>22</v>
@@ -18891,7 +18894,7 @@
         <v>22</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>231</v>
@@ -18900,16 +18903,16 @@
         <v>46325</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I11" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P11,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -18948,7 +18951,7 @@
         <v>23</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>231</v>
@@ -18957,16 +18960,16 @@
         <v>46295</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I12" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P12,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -19014,16 +19017,16 @@
         <v>46325</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>161</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="I13" s="16" t="n">
         <f aca="false">INDEX('1099 Oct 30'!$F$5:$F$45,MATCH(P13,'1099 Oct 30'!$A$5:$A$45,0))</f>
@@ -19048,7 +19051,7 @@
         <v>227</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="P13" s="2" t="s">
         <v>23</v>
@@ -19059,7 +19062,7 @@
         <v>24</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>231</v>
@@ -19068,16 +19071,16 @@
         <v>46295</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I14" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P14,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -19125,16 +19128,16 @@
         <v>46325</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>161</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="I15" s="16" t="n">
         <f aca="false">INDEX('1099 Oct 30'!$F$5:$F$45,MATCH(P15,'1099 Oct 30'!$A$5:$A$45,0))</f>
@@ -19159,7 +19162,7 @@
         <v>227</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="P15" s="2" t="s">
         <v>24</v>
@@ -19170,7 +19173,7 @@
         <v>25</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>231</v>
@@ -19179,16 +19182,16 @@
         <v>46301</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I16" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P16,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -19236,16 +19239,16 @@
         <v>46325</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>161</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="I17" s="16" t="n">
         <f aca="false">INDEX('1099 Oct 30'!$F$5:$F$45,MATCH(P17,'1099 Oct 30'!$A$5:$A$45,0))</f>
@@ -19270,7 +19273,7 @@
         <v>227</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="P17" s="2" t="s">
         <v>25</v>
@@ -19281,7 +19284,7 @@
         <v>26</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>231</v>
@@ -19290,16 +19293,16 @@
         <v>46301</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I18" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P18,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -19347,16 +19350,16 @@
         <v>46325</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>161</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="I19" s="16" t="n">
         <f aca="false">INDEX('1099 Oct 30'!$F$5:$F$45,MATCH(P19,'1099 Oct 30'!$A$5:$A$45,0))</f>
@@ -19381,7 +19384,7 @@
         <v>227</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="P19" s="2" t="s">
         <v>26</v>
@@ -19392,7 +19395,7 @@
         <v>27</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>231</v>
@@ -19401,16 +19404,16 @@
         <v>46275</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I20" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P20,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -19449,7 +19452,7 @@
         <v>27</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>276</v>
@@ -19458,16 +19461,16 @@
         <v>46297</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I21" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P21,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -19506,7 +19509,7 @@
         <v>27</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>231</v>
@@ -19515,16 +19518,16 @@
         <v>46304</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I22" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P22,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -19572,16 +19575,16 @@
         <v>46325</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>161</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="I23" s="16" t="n">
         <f aca="false">INDEX('1099 Oct 30'!$F$5:$F$45,MATCH(P23,'1099 Oct 30'!$A$5:$A$45,0))</f>
@@ -19606,7 +19609,7 @@
         <v>227</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="P23" s="2" t="s">
         <v>27</v>
@@ -19617,7 +19620,7 @@
         <v>27</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>271</v>
@@ -19626,16 +19629,16 @@
         <v>46325</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I24" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P24,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -19674,7 +19677,7 @@
         <v>31</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>231</v>
@@ -19683,16 +19686,16 @@
         <v>46281</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I25" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P25,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -19731,7 +19734,7 @@
         <v>31</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>231</v>
@@ -19740,16 +19743,16 @@
         <v>46311</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I26" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P26,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -19797,16 +19800,16 @@
         <v>46325</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>161</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="I27" s="16" t="n">
         <f aca="false">INDEX('1099 Oct 30'!$F$5:$F$45,MATCH(P27,'1099 Oct 30'!$A$5:$A$45,0))</f>
@@ -19831,7 +19834,7 @@
         <v>227</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="P27" s="2" t="s">
         <v>31</v>
@@ -19842,7 +19845,7 @@
         <v>32</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>237</v>
@@ -19851,16 +19854,16 @@
         <v>46295</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I28" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P28,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -19899,7 +19902,7 @@
         <v>32</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>271</v>
@@ -19908,16 +19911,16 @@
         <v>46325</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I29" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P29,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -19959,22 +19962,22 @@
         <v>89</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D30" s="31" t="n">
         <v>46291</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>90</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="I30" s="15" t="n">
         <v>2.5</v>
@@ -19998,7 +20001,7 @@
         <v>227</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="P30" s="2"/>
     </row>
@@ -20007,7 +20010,7 @@
         <v>33</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>231</v>
@@ -20016,16 +20019,16 @@
         <v>46282</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I31" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P31,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -20064,7 +20067,7 @@
         <v>33</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>231</v>
@@ -20073,16 +20076,16 @@
         <v>46304</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I32" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P32,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -20130,16 +20133,16 @@
         <v>46325</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>161</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="I33" s="16" t="n">
         <f aca="false">INDEX('1099 Oct 30'!$F$5:$F$45,MATCH(P33,'1099 Oct 30'!$A$5:$A$45,0))</f>
@@ -20164,7 +20167,7 @@
         <v>227</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="P33" s="2" t="s">
         <v>33</v>
@@ -20175,7 +20178,7 @@
         <v>34</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>231</v>
@@ -20184,16 +20187,16 @@
         <v>46276</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I34" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P34,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -20232,7 +20235,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>231</v>
@@ -20241,16 +20244,16 @@
         <v>46307</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I35" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P35,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -20298,16 +20301,16 @@
         <v>46325</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>161</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="I36" s="16" t="n">
         <f aca="false">INDEX('1099 Oct 30'!$F$5:$F$45,MATCH(P36,'1099 Oct 30'!$A$5:$A$45,0))</f>
@@ -20332,7 +20335,7 @@
         <v>227</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="P36" s="2" t="s">
         <v>34</v>
@@ -20343,7 +20346,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>231</v>
@@ -20352,16 +20355,16 @@
         <v>46275</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I37" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P37,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -20400,7 +20403,7 @@
         <v>35</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>231</v>
@@ -20409,16 +20412,16 @@
         <v>46304</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I38" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P38,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -20466,16 +20469,16 @@
         <v>46325</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>161</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="I39" s="16" t="n">
         <f aca="false">INDEX('1099 Oct 30'!$F$5:$F$45,MATCH(P39,'1099 Oct 30'!$A$5:$A$45,0))</f>
@@ -20500,7 +20503,7 @@
         <v>227</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="P39" s="2" t="s">
         <v>35</v>
@@ -20520,16 +20523,16 @@
         <v>46297</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>90</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="I40" s="15" t="n">
         <v>0.5</v>
@@ -20553,7 +20556,7 @@
         <v>227</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="P40" s="2"/>
     </row>
@@ -20571,16 +20574,16 @@
         <v>46297</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>90</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="I41" s="15" t="n">
         <v>0.5</v>
@@ -20604,7 +20607,7 @@
         <v>227</v>
       </c>
       <c r="O41" s="2" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="P41" s="2"/>
     </row>
@@ -20616,22 +20619,22 @@
         <v>94</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D42" s="31" t="n">
         <v>46295</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>90</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="I42" s="15" t="n">
         <v>10</v>
@@ -20655,7 +20658,7 @@
         <v>227</v>
       </c>
       <c r="O42" s="2" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="P42" s="2"/>
     </row>
@@ -20673,16 +20676,16 @@
         <v>46304</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I43" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P43,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -20730,16 +20733,16 @@
         <v>46325</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>161</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="I44" s="16" t="n">
         <f aca="false">INDEX('1099 Oct 30'!$F$5:$F$45,MATCH(P44,'1099 Oct 30'!$A$5:$A$45,0))</f>
@@ -20764,7 +20767,7 @@
         <v>227</v>
       </c>
       <c r="O44" s="2" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="P44" s="2" t="s">
         <v>36</v>
@@ -20778,22 +20781,22 @@
         <v>95</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D45" s="31" t="n">
         <v>46288</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>90</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="I45" s="15" t="n">
         <v>5.5</v>
@@ -20817,7 +20820,7 @@
         <v>227</v>
       </c>
       <c r="O45" s="2" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="P45" s="2"/>
     </row>
@@ -20826,7 +20829,7 @@
         <v>37</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>231</v>
@@ -20835,16 +20838,16 @@
         <v>46308</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I46" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P46,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -20892,16 +20895,16 @@
         <v>46325</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>161</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="I47" s="16" t="n">
         <f aca="false">INDEX('1099 Oct 30'!$F$5:$F$45,MATCH(P47,'1099 Oct 30'!$A$5:$A$45,0))</f>
@@ -20926,7 +20929,7 @@
         <v>227</v>
       </c>
       <c r="O47" s="2" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="P47" s="2" t="s">
         <v>37</v>
@@ -20937,7 +20940,7 @@
         <v>38</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>231</v>
@@ -20946,16 +20949,16 @@
         <v>46295</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I48" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P48,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -21003,16 +21006,16 @@
         <v>46325</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>161</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="I49" s="16" t="n">
         <f aca="false">INDEX('1099 Oct 30'!$F$5:$F$45,MATCH(P49,'1099 Oct 30'!$A$5:$A$45,0))</f>
@@ -21037,7 +21040,7 @@
         <v>227</v>
       </c>
       <c r="O49" s="2" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="P49" s="2" t="s">
         <v>38</v>
@@ -21048,7 +21051,7 @@
         <v>39</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>231</v>
@@ -21057,16 +21060,16 @@
         <v>46302</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I50" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P50,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -21114,16 +21117,16 @@
         <v>46325</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>161</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="I51" s="16" t="n">
         <f aca="false">INDEX('1099 Oct 30'!$F$5:$F$45,MATCH(P51,'1099 Oct 30'!$A$5:$A$45,0))</f>
@@ -21148,7 +21151,7 @@
         <v>227</v>
       </c>
       <c r="O51" s="2" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="P51" s="2" t="s">
         <v>39</v>
@@ -21159,7 +21162,7 @@
         <v>40</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>231</v>
@@ -21168,16 +21171,16 @@
         <v>46269</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I52" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P52,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -21216,7 +21219,7 @@
         <v>40</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>231</v>
@@ -21225,16 +21228,16 @@
         <v>46301</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I53" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P53,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -21282,16 +21285,16 @@
         <v>46325</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>161</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="I54" s="16" t="n">
         <f aca="false">INDEX('1099 Oct 30'!$F$5:$F$45,MATCH(P54,'1099 Oct 30'!$A$5:$A$45,0))</f>
@@ -21316,7 +21319,7 @@
         <v>227</v>
       </c>
       <c r="O54" s="2" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="P54" s="2" t="s">
         <v>40</v>
@@ -21336,10 +21339,10 @@
         <v>46325</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>161</v>
@@ -21365,7 +21368,7 @@
         <v>41</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>231</v>
@@ -21374,16 +21377,16 @@
         <v>46286</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I56" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P56,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -21422,7 +21425,7 @@
         <v>41</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>231</v>
@@ -21431,16 +21434,16 @@
         <v>46316</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I57" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P57,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -21488,16 +21491,16 @@
         <v>46265</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>161</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="I58" s="15" t="n">
         <v>0.75</v>
@@ -21521,7 +21524,7 @@
         <v>227</v>
       </c>
       <c r="O58" s="2" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="P58" s="2"/>
     </row>
@@ -21530,7 +21533,7 @@
         <v>43</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>231</v>
@@ -21539,16 +21542,16 @@
         <v>46295</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I59" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P59,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -21590,22 +21593,22 @@
         <v>97</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D60" s="31" t="n">
         <v>46295</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>90</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="I60" s="15" t="n">
         <v>8</v>
@@ -21629,7 +21632,7 @@
         <v>227</v>
       </c>
       <c r="O60" s="2" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="P60" s="2"/>
     </row>
@@ -21638,7 +21641,7 @@
         <v>43</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>237</v>
@@ -21647,16 +21650,16 @@
         <v>46300</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I61" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P61,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -21695,7 +21698,7 @@
         <v>43</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>237</v>
@@ -21704,16 +21707,16 @@
         <v>46307</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I62" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P62,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -21752,7 +21755,7 @@
         <v>43</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>231</v>
@@ -21761,16 +21764,16 @@
         <v>46311</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I63" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P63,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -21818,16 +21821,16 @@
         <v>46325</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>161</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="I64" s="16" t="n">
         <f aca="false">INDEX('1099 Oct 30'!$F$5:$F$45,MATCH(P64,'1099 Oct 30'!$A$5:$A$45,0))</f>
@@ -21852,7 +21855,7 @@
         <v>227</v>
       </c>
       <c r="O64" s="2" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="P64" s="2" t="s">
         <v>43</v>
@@ -21872,16 +21875,16 @@
         <v>46304</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>90</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="I65" s="15" t="n">
         <v>3</v>
@@ -21905,7 +21908,7 @@
         <v>227</v>
       </c>
       <c r="O65" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="P65" s="2"/>
     </row>
@@ -21923,16 +21926,16 @@
         <v>46325</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>161</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="I66" s="16" t="n">
         <f aca="false">INDEX('1099 Oct 30'!$F$5:$F$45,MATCH(P66,'1099 Oct 30'!$A$5:$A$45,0))</f>
@@ -21957,7 +21960,7 @@
         <v>227</v>
       </c>
       <c r="O66" s="2" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="P66" s="2" t="s">
         <v>45</v>
@@ -21968,7 +21971,7 @@
         <v>46</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>243</v>
@@ -21977,16 +21980,16 @@
         <v>46248</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I67" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P67,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -22025,7 +22028,7 @@
         <v>46</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>237</v>
@@ -22034,16 +22037,16 @@
         <v>46321</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I68" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P68,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -22091,16 +22094,16 @@
         <v>46325</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>161</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="I69" s="16" t="n">
         <f aca="false">INDEX('1099 Oct 30'!$F$5:$F$45,MATCH(P69,'1099 Oct 30'!$A$5:$A$45,0))</f>
@@ -22125,7 +22128,7 @@
         <v>227</v>
       </c>
       <c r="O69" s="2" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="P69" s="2" t="s">
         <v>46</v>
@@ -22136,7 +22139,7 @@
         <v>46</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>271</v>
@@ -22145,16 +22148,16 @@
         <v>46325</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I70" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P70,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -22202,10 +22205,10 @@
         <v>46219</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>15</v>
@@ -22240,10 +22243,10 @@
         <v>46224</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>13</v>
@@ -22278,10 +22281,10 @@
         <v>46248</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>15</v>
@@ -22307,7 +22310,7 @@
         <v>203</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>276</v>
@@ -22316,10 +22319,10 @@
         <v>46273</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>90</v>
@@ -22345,7 +22348,7 @@
         <v>203</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>231</v>
@@ -22354,10 +22357,10 @@
         <v>46281</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>15</v>
@@ -22383,7 +22386,7 @@
         <v>203</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>240</v>
@@ -22392,10 +22395,10 @@
         <v>46283</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>15</v>
@@ -22421,7 +22424,7 @@
         <v>203</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>237</v>
@@ -22430,10 +22433,10 @@
         <v>46293</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>90</v>
@@ -22459,7 +22462,7 @@
         <v>203</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>237</v>
@@ -22468,10 +22471,10 @@
         <v>46295</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>30</v>
@@ -22497,7 +22500,7 @@
         <v>203</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>237</v>
@@ -22506,10 +22509,10 @@
         <v>46302</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>30</v>
@@ -22535,7 +22538,7 @@
         <v>203</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>276</v>
@@ -22544,10 +22547,10 @@
         <v>46303</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>90</v>
@@ -22582,10 +22585,10 @@
         <v>46310</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>13</v>
@@ -22620,10 +22623,10 @@
         <v>46310</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>13</v>
@@ -22649,7 +22652,7 @@
         <v>203</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>240</v>
@@ -22658,10 +22661,10 @@
         <v>46310</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>15</v>
@@ -22687,7 +22690,7 @@
         <v>203</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>231</v>
@@ -22696,10 +22699,10 @@
         <v>46311</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>15</v>
@@ -22734,10 +22737,10 @@
         <v>46325</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>161</v>
@@ -22763,7 +22766,7 @@
         <v>203</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>271</v>
@@ -22772,10 +22775,10 @@
         <v>46325</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>21</v>
@@ -22801,7 +22804,7 @@
         <v>47</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>231</v>
@@ -22810,16 +22813,16 @@
         <v>46301</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I87" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P87,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -22867,16 +22870,16 @@
         <v>46325</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>161</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="I88" s="16" t="n">
         <f aca="false">INDEX('1099 Oct 30'!$F$5:$F$45,MATCH(P88,'1099 Oct 30'!$A$5:$A$45,0))</f>
@@ -22901,7 +22904,7 @@
         <v>227</v>
       </c>
       <c r="O88" s="2" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="P88" s="2" t="s">
         <v>47</v>
@@ -22915,22 +22918,22 @@
         <v>100</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D89" s="31" t="n">
         <v>46290</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>90</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="I89" s="15" t="n">
         <v>5.5</v>
@@ -22954,7 +22957,7 @@
         <v>227</v>
       </c>
       <c r="O89" s="2" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="P89" s="2"/>
     </row>
@@ -22963,7 +22966,7 @@
         <v>48</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>231</v>
@@ -22972,16 +22975,16 @@
         <v>46301</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I90" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P90,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -23020,7 +23023,7 @@
         <v>48</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>240</v>
@@ -23029,16 +23032,16 @@
         <v>46310</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G91" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I91" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P91,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -23086,16 +23089,16 @@
         <v>46325</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G92" s="2" t="s">
         <v>161</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="I92" s="16" t="n">
         <f aca="false">INDEX('1099 Oct 30'!$F$5:$F$45,MATCH(P92,'1099 Oct 30'!$A$5:$A$45,0))</f>
@@ -23120,7 +23123,7 @@
         <v>227</v>
       </c>
       <c r="O92" s="2" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="P92" s="2" t="s">
         <v>48</v>
@@ -23140,16 +23143,16 @@
         <v>46265</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="G93" s="2" t="s">
         <v>161</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="I93" s="15" t="n">
         <v>0.75</v>
@@ -23173,7 +23176,7 @@
         <v>227</v>
       </c>
       <c r="O93" s="2" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="P93" s="2"/>
     </row>
@@ -23182,7 +23185,7 @@
         <v>50</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>231</v>
@@ -23191,16 +23194,16 @@
         <v>46295</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="G94" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I94" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P94,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -23239,7 +23242,7 @@
         <v>50</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>237</v>
@@ -23248,16 +23251,16 @@
         <v>46300</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G95" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I95" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P95,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -23296,7 +23299,7 @@
         <v>50</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>237</v>
@@ -23305,16 +23308,16 @@
         <v>46307</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G96" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I96" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P96,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -23353,7 +23356,7 @@
         <v>50</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>231</v>
@@ -23362,16 +23365,16 @@
         <v>46311</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G97" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I97" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P97,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -23419,16 +23422,16 @@
         <v>46325</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G98" s="2" t="s">
         <v>161</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="I98" s="16" t="n">
         <f aca="false">INDEX('1099 Oct 30'!$F$5:$F$45,MATCH(P98,'1099 Oct 30'!$A$5:$A$45,0))</f>
@@ -23453,7 +23456,7 @@
         <v>227</v>
       </c>
       <c r="O98" s="2" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="P98" s="2" t="s">
         <v>50</v>
@@ -23464,7 +23467,7 @@
         <v>52</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>231</v>
@@ -23473,16 +23476,16 @@
         <v>46295</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G99" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I99" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P99,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -23530,16 +23533,16 @@
         <v>46325</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G100" s="2" t="s">
         <v>161</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="I100" s="16" t="n">
         <f aca="false">INDEX('1099 Oct 30'!$F$5:$F$45,MATCH(P100,'1099 Oct 30'!$A$5:$A$45,0))</f>
@@ -23564,7 +23567,7 @@
         <v>227</v>
       </c>
       <c r="O100" s="2" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="P100" s="2" t="s">
         <v>52</v>
@@ -23575,7 +23578,7 @@
         <v>53</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>231</v>
@@ -23584,16 +23587,16 @@
         <v>46295</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="G101" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I101" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P101,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -23641,16 +23644,16 @@
         <v>46325</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G102" s="2" t="s">
         <v>161</v>
       </c>
       <c r="H102" s="2" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="I102" s="16" t="n">
         <f aca="false">INDEX('1099 Oct 30'!$F$5:$F$45,MATCH(P102,'1099 Oct 30'!$A$5:$A$45,0))</f>
@@ -23675,7 +23678,7 @@
         <v>227</v>
       </c>
       <c r="O102" s="2" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="P102" s="2" t="s">
         <v>53</v>
@@ -23695,16 +23698,16 @@
         <v>46290</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G103" s="2" t="s">
         <v>90</v>
       </c>
       <c r="H103" s="2" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="I103" s="15" t="n">
         <v>8</v>
@@ -23728,7 +23731,7 @@
         <v>227</v>
       </c>
       <c r="O103" s="2" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="P103" s="2"/>
     </row>
@@ -23740,22 +23743,22 @@
         <v>102</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D104" s="31" t="n">
         <v>46295</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="G104" s="2" t="s">
         <v>90</v>
       </c>
       <c r="H104" s="2" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="I104" s="15" t="n">
         <v>10</v>
@@ -23779,7 +23782,7 @@
         <v>227</v>
       </c>
       <c r="O104" s="2" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="P104" s="2"/>
     </row>
@@ -23788,7 +23791,7 @@
         <v>54</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>237</v>
@@ -23797,16 +23800,16 @@
         <v>46301</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G105" s="2" t="s">
         <v>56</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I105" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P105,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -23814,19 +23817,19 @@
       </c>
       <c r="J105" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$G$2:$G$125,MATCH(P105,'Recurring Budgets'!$A$2:$A$125,0))</f>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="K105" s="21" t="n">
         <f aca="false">I105+J105</f>
-        <v>0.9167</v>
+        <v>1.1667</v>
       </c>
       <c r="L105" s="2" t="n">
         <f aca="false">ROUND(K105*60,0)</f>
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="M105" s="22" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$M$2:$M$125,MATCH(P105,'Recurring Budgets'!$A$2:$A$125,0))</f>
-        <v>229.175</v>
+        <v>291.675</v>
       </c>
       <c r="N105" s="8" t="str">
         <f aca="false">INDEX('Recurring Budgets'!$P$2:$P$125,MATCH(P105,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -23834,7 +23837,7 @@
       </c>
       <c r="O105" s="8" t="str">
         <f aca="false">INDEX('Recurring Budgets'!$Q$2:$Q$125,MATCH(P105,'Recurring Budgets'!$A$2:$A$125,0))</f>
-        <v>Payroll time ÷ pay periods per month (75% share). Payroll takeover in progress (Paychex/401k/PFML); tax audit budgeted separately. Confirm payroll is ongoing.</v>
+        <v>Payroll time ÷ pay periods per month (75% share). Payroll takeover in progress (Paychex/401k/PFML); tax audit budgeted separately. Confirm payroll is ongoing. Review = Lisa oversight, 15 min per occurrence (work moving to Jessica).</v>
       </c>
       <c r="P105" s="2" t="s">
         <v>373</v>
@@ -23845,7 +23848,7 @@
         <v>54</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>371</v>
@@ -23854,16 +23857,16 @@
         <v>46302</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G106" s="2" t="s">
         <v>56</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I106" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P106,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -23911,16 +23914,16 @@
         <v>46325</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G107" s="2" t="s">
         <v>161</v>
       </c>
       <c r="H107" s="2" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="I107" s="16" t="n">
         <f aca="false">INDEX('1099 Oct 30'!$F$5:$F$45,MATCH(P107,'1099 Oct 30'!$A$5:$A$45,0))</f>
@@ -23945,7 +23948,7 @@
         <v>227</v>
       </c>
       <c r="O107" s="2" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="P107" s="2" t="s">
         <v>54</v>
@@ -23956,7 +23959,7 @@
         <v>58</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>240</v>
@@ -23965,16 +23968,16 @@
         <v>46314</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G108" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I108" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P108,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -24022,16 +24025,16 @@
         <v>46325</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G109" s="2" t="s">
         <v>161</v>
       </c>
       <c r="H109" s="2" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="I109" s="16" t="n">
         <f aca="false">INDEX('1099 Oct 30'!$F$5:$F$45,MATCH(P109,'1099 Oct 30'!$A$5:$A$45,0))</f>
@@ -24056,7 +24059,7 @@
         <v>227</v>
       </c>
       <c r="O109" s="2" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="P109" s="2" t="s">
         <v>58</v>
@@ -24067,7 +24070,7 @@
         <v>58</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>380</v>
@@ -24076,16 +24079,16 @@
         <v>46325</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G110" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H110" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I110" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P110,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -24124,7 +24127,7 @@
         <v>61</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>231</v>
@@ -24133,16 +24136,16 @@
         <v>46296</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G111" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H111" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I111" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P111,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -24190,16 +24193,16 @@
         <v>46297</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="G112" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H112" s="2" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="I112" s="15" t="n">
         <v>0.5</v>
@@ -24223,7 +24226,7 @@
         <v>227</v>
       </c>
       <c r="O112" s="2" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="P112" s="2"/>
     </row>
@@ -24241,16 +24244,16 @@
         <v>46325</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G113" s="2" t="s">
         <v>161</v>
       </c>
       <c r="H113" s="2" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="I113" s="16" t="n">
         <f aca="false">INDEX('1099 Oct 30'!$F$5:$F$45,MATCH(P113,'1099 Oct 30'!$A$5:$A$45,0))</f>
@@ -24275,7 +24278,7 @@
         <v>227</v>
       </c>
       <c r="O113" s="2" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="P113" s="2" t="s">
         <v>61</v>
@@ -24286,7 +24289,7 @@
         <v>61</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>271</v>
@@ -24295,16 +24298,16 @@
         <v>46325</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="G114" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H114" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I114" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P114,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -24343,7 +24346,7 @@
         <v>61</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>231</v>
@@ -24352,16 +24355,16 @@
         <v>46325</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G115" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H115" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I115" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P115,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -24400,7 +24403,7 @@
         <v>63</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>271</v>
@@ -24409,16 +24412,16 @@
         <v>46325</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="G116" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H116" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I116" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P116,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -24457,7 +24460,7 @@
         <v>63</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>237</v>
@@ -24466,16 +24469,16 @@
         <v>46325</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G117" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H117" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I117" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P117,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -24517,22 +24520,22 @@
         <v>103</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D118" s="31" t="n">
         <v>46295</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="G118" s="2" t="s">
         <v>90</v>
       </c>
       <c r="H118" s="2" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="I118" s="15" t="n">
         <v>5.5</v>
@@ -24556,7 +24559,7 @@
         <v>227</v>
       </c>
       <c r="O118" s="2" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="P118" s="2"/>
     </row>
@@ -24565,7 +24568,7 @@
         <v>64</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>276</v>
@@ -24574,16 +24577,16 @@
         <v>46295</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G119" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H119" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I119" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P119,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -24622,7 +24625,7 @@
         <v>64</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>276</v>
@@ -24631,16 +24634,16 @@
         <v>46296</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="G120" s="2" t="s">
         <v>66</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I120" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P120,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -24679,7 +24682,7 @@
         <v>64</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>276</v>
@@ -24688,16 +24691,16 @@
         <v>46297</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G121" s="2" t="s">
         <v>66</v>
       </c>
       <c r="H121" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I121" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P121,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -24736,7 +24739,7 @@
         <v>64</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>276</v>
@@ -24745,16 +24748,16 @@
         <v>46300</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G122" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H122" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I122" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P122,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -24793,7 +24796,7 @@
         <v>64</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>276</v>
@@ -24802,16 +24805,16 @@
         <v>46302</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G123" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H123" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I123" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P123,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -24853,22 +24856,22 @@
         <v>104</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D124" s="31" t="n">
         <v>46265</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="G124" s="2" t="s">
         <v>90</v>
       </c>
       <c r="H124" s="2" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="I124" s="15" t="n">
         <v>4</v>
@@ -24892,7 +24895,7 @@
         <v>227</v>
       </c>
       <c r="O124" s="2" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="P124" s="2"/>
     </row>
@@ -24901,7 +24904,7 @@
         <v>68</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>231</v>
@@ -24910,16 +24913,16 @@
         <v>46316</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G125" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H125" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I125" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P125,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -24967,16 +24970,16 @@
         <v>46325</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G126" s="2" t="s">
         <v>161</v>
       </c>
       <c r="H126" s="2" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="I126" s="16" t="n">
         <f aca="false">INDEX('1099 Oct 30'!$F$5:$F$45,MATCH(P126,'1099 Oct 30'!$A$5:$A$45,0))</f>
@@ -25001,7 +25004,7 @@
         <v>227</v>
       </c>
       <c r="O126" s="2" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="P126" s="2" t="s">
         <v>68</v>
@@ -25012,7 +25015,7 @@
         <v>69</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>243</v>
@@ -25021,16 +25024,16 @@
         <v>46265</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="G127" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H127" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I127" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P127,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -25069,7 +25072,7 @@
         <v>69</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>240</v>
@@ -25078,16 +25081,16 @@
         <v>46314</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G128" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H128" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I128" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P128,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -25126,7 +25129,7 @@
         <v>69</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>231</v>
@@ -25135,16 +25138,16 @@
         <v>46321</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G129" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H129" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I129" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P129,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -25192,16 +25195,16 @@
         <v>46325</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G130" s="2" t="s">
         <v>161</v>
       </c>
       <c r="H130" s="2" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="I130" s="16" t="n">
         <f aca="false">INDEX('1099 Oct 30'!$F$5:$F$45,MATCH(P130,'1099 Oct 30'!$A$5:$A$45,0))</f>
@@ -25226,7 +25229,7 @@
         <v>227</v>
       </c>
       <c r="O130" s="2" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="P130" s="2" t="s">
         <v>69</v>
@@ -25246,16 +25249,16 @@
         <v>46326</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="G131" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H131" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I131" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P131,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -25294,7 +25297,7 @@
         <v>69</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>231</v>
@@ -25303,16 +25306,16 @@
         <v>46326</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="G132" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H132" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I132" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P132,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -25360,16 +25363,16 @@
         <v>46326</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="G133" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H133" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I133" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P133,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -25417,16 +25420,16 @@
         <v>46326</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G134" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H134" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I134" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P134,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -25474,16 +25477,16 @@
         <v>46326</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="G135" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H135" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I135" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P135,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -25531,16 +25534,16 @@
         <v>46326</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="G136" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H136" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I136" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P136,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -25588,16 +25591,16 @@
         <v>46326</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="G137" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H137" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I137" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P137,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -25645,16 +25648,16 @@
         <v>46326</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G138" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H138" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I138" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P138,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -25693,7 +25696,7 @@
         <v>70</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>231</v>
@@ -25702,16 +25705,16 @@
         <v>46297</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="G139" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H139" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I139" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P139,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -25750,7 +25753,7 @@
         <v>70</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>231</v>
@@ -25759,16 +25762,16 @@
         <v>46310</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="G140" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H140" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I140" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P140,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -25816,16 +25819,16 @@
         <v>46325</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G141" s="2" t="s">
         <v>161</v>
       </c>
       <c r="H141" s="2" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="I141" s="16" t="n">
         <f aca="false">INDEX('1099 Oct 30'!$F$5:$F$45,MATCH(P141,'1099 Oct 30'!$A$5:$A$45,0))</f>
@@ -25850,7 +25853,7 @@
         <v>227</v>
       </c>
       <c r="O141" s="2" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="P141" s="2" t="s">
         <v>70</v>
@@ -25861,7 +25864,7 @@
         <v>70</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>271</v>
@@ -25870,16 +25873,16 @@
         <v>46325</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="G142" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H142" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I142" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P142,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -25918,7 +25921,7 @@
         <v>71</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>231</v>
@@ -25927,16 +25930,16 @@
         <v>46296</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="G143" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H143" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I143" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P143,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -25984,16 +25987,16 @@
         <v>46325</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G144" s="2" t="s">
         <v>161</v>
       </c>
       <c r="H144" s="2" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="I144" s="16" t="n">
         <f aca="false">INDEX('1099 Oct 30'!$F$5:$F$45,MATCH(P144,'1099 Oct 30'!$A$5:$A$45,0))</f>
@@ -26018,7 +26021,7 @@
         <v>227</v>
       </c>
       <c r="O144" s="2" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="P144" s="2" t="s">
         <v>71</v>
@@ -26029,7 +26032,7 @@
         <v>71</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>231</v>
@@ -26038,16 +26041,16 @@
         <v>46325</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G145" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H145" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I145" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P145,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -26086,7 +26089,7 @@
         <v>72</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>237</v>
@@ -26095,16 +26098,16 @@
         <v>46310</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="G146" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H146" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I146" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P146,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -26152,16 +26155,16 @@
         <v>46325</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G147" s="2" t="s">
         <v>161</v>
       </c>
       <c r="H147" s="2" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="I147" s="16" t="n">
         <f aca="false">INDEX('1099 Oct 30'!$F$5:$F$45,MATCH(P147,'1099 Oct 30'!$A$5:$A$45,0))</f>
@@ -26186,7 +26189,7 @@
         <v>227</v>
       </c>
       <c r="O147" s="2" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="P147" s="2" t="s">
         <v>72</v>
@@ -26206,16 +26209,16 @@
         <v>46304</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="G148" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H148" s="2" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="I148" s="15" t="n">
         <v>2.5</v>
@@ -26239,7 +26242,7 @@
         <v>227</v>
       </c>
       <c r="O148" s="2" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="P148" s="2"/>
     </row>
@@ -26257,16 +26260,16 @@
         <v>46304</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="G149" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H149" s="2" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="I149" s="15" t="n">
         <v>2.5</v>
@@ -26290,7 +26293,7 @@
         <v>227</v>
       </c>
       <c r="O149" s="2" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="P149" s="2"/>
     </row>
@@ -26308,16 +26311,16 @@
         <v>46304</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="G150" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H150" s="2" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="I150" s="15" t="n">
         <v>2.5</v>
@@ -26341,7 +26344,7 @@
         <v>227</v>
       </c>
       <c r="O150" s="2" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="P150" s="2"/>
     </row>
@@ -26359,16 +26362,16 @@
         <v>46311</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="G151" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H151" s="2" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="I151" s="15" t="n">
         <v>2.5</v>
@@ -26392,7 +26395,7 @@
         <v>227</v>
       </c>
       <c r="O151" s="2" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="P151" s="2"/>
     </row>
@@ -26401,7 +26404,7 @@
         <v>73</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>231</v>
@@ -26410,16 +26413,16 @@
         <v>46311</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G152" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H152" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I152" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P152,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -26467,16 +26470,16 @@
         <v>46311</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="G153" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H153" s="2" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="I153" s="15" t="n">
         <v>2.5</v>
@@ -26500,7 +26503,7 @@
         <v>227</v>
       </c>
       <c r="O153" s="2" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="P153" s="2"/>
     </row>
@@ -26518,16 +26521,16 @@
         <v>46311</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="G154" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H154" s="2" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="I154" s="15" t="n">
         <v>2.5</v>
@@ -26551,7 +26554,7 @@
         <v>227</v>
       </c>
       <c r="O154" s="2" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="P154" s="2"/>
     </row>
@@ -26569,16 +26572,16 @@
         <v>46311</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="G155" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H155" s="2" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="I155" s="15" t="n">
         <v>2.5</v>
@@ -26602,7 +26605,7 @@
         <v>227</v>
       </c>
       <c r="O155" s="2" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="P155" s="2"/>
     </row>
@@ -26611,7 +26614,7 @@
         <v>73</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>231</v>
@@ -26620,16 +26623,16 @@
         <v>46314</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G156" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H156" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I156" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P156,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -26677,16 +26680,16 @@
         <v>46325</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G157" s="2" t="s">
         <v>161</v>
       </c>
       <c r="H157" s="2" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="I157" s="16" t="n">
         <f aca="false">INDEX('1099 Oct 30'!$F$5:$F$45,MATCH(P157,'1099 Oct 30'!$A$5:$A$45,0))</f>
@@ -26711,7 +26714,7 @@
         <v>227</v>
       </c>
       <c r="O157" s="2" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="P157" s="2" t="s">
         <v>73</v>
@@ -26722,7 +26725,7 @@
         <v>73</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>271</v>
@@ -26731,16 +26734,16 @@
         <v>46325</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="G158" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H158" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I158" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P158,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -26779,7 +26782,7 @@
         <v>74</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>231</v>
@@ -26788,16 +26791,16 @@
         <v>46301</v>
       </c>
       <c r="E159" s="2" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G159" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H159" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I159" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P159,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -26845,16 +26848,16 @@
         <v>46325</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G160" s="2" t="s">
         <v>161</v>
       </c>
       <c r="H160" s="2" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="I160" s="16" t="n">
         <f aca="false">INDEX('1099 Oct 30'!$F$5:$F$45,MATCH(P160,'1099 Oct 30'!$A$5:$A$45,0))</f>
@@ -26879,7 +26882,7 @@
         <v>227</v>
       </c>
       <c r="O160" s="2" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="P160" s="2" t="s">
         <v>74</v>
@@ -26890,7 +26893,7 @@
         <v>75</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C161" s="2" t="s">
         <v>231</v>
@@ -26899,16 +26902,16 @@
         <v>46301</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G161" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H161" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I161" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P161,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -26956,16 +26959,16 @@
         <v>46325</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G162" s="2" t="s">
         <v>161</v>
       </c>
       <c r="H162" s="2" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="I162" s="16" t="n">
         <f aca="false">INDEX('1099 Oct 30'!$F$5:$F$45,MATCH(P162,'1099 Oct 30'!$A$5:$A$45,0))</f>
@@ -26990,7 +26993,7 @@
         <v>227</v>
       </c>
       <c r="O162" s="2" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="P162" s="2" t="s">
         <v>75</v>
@@ -27004,22 +27007,22 @@
         <v>113</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D163" s="31" t="n">
         <v>46297</v>
       </c>
       <c r="E163" s="2" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="G163" s="2" t="s">
         <v>90</v>
       </c>
       <c r="H163" s="2" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="I163" s="15" t="n">
         <v>2.5</v>
@@ -27043,7 +27046,7 @@
         <v>227</v>
       </c>
       <c r="O163" s="2" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="P163" s="2"/>
     </row>
@@ -27052,7 +27055,7 @@
         <v>76</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>243</v>
@@ -27061,16 +27064,16 @@
         <v>46293</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="G164" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H164" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I164" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P164,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -27078,19 +27081,19 @@
       </c>
       <c r="J164" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$G$2:$G$125,MATCH(P164,'Recurring Budgets'!$A$2:$A$125,0))</f>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="K164" s="21" t="n">
         <f aca="false">I164+J164</f>
-        <v>1.0833</v>
+        <v>1.3333</v>
       </c>
       <c r="L164" s="2" t="n">
         <f aca="false">ROUND(K164*60,0)</f>
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="M164" s="22" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$M$2:$M$125,MATCH(P164,'Recurring Budgets'!$A$2:$A$125,0))</f>
-        <v>102.9135</v>
+        <v>165.4135</v>
       </c>
       <c r="N164" s="8" t="str">
         <f aca="false">INDEX('Recurring Budgets'!$P$2:$P$125,MATCH(P164,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -27098,7 +27101,7 @@
       </c>
       <c r="O164" s="8" t="str">
         <f aca="false">INDEX('Recurring Budgets'!$Q$2:$Q$125,MATCH(P164,'Recurring Budgets'!$A$2:$A$125,0))</f>
-        <v>Weekly bookkeeping/settlement time ÷ weeks per month.</v>
+        <v>Weekly bookkeeping/settlement time ÷ weeks per month. Review = Lisa oversight, 15 min per occurrence (work moving to Jessica).</v>
       </c>
       <c r="P164" s="2" t="s">
         <v>441</v>
@@ -27109,7 +27112,7 @@
         <v>76</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C165" s="2" t="s">
         <v>276</v>
@@ -27118,16 +27121,16 @@
         <v>46293</v>
       </c>
       <c r="E165" s="2" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="G165" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H165" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I165" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P165,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -27158,7 +27161,7 @@
         <v>CFO cash-flow/advisory time ÷ weeks per month.</v>
       </c>
       <c r="P165" s="2" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27175,16 +27178,16 @@
         <v>46295</v>
       </c>
       <c r="E166" s="2" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="F166" s="2" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="G166" s="2" t="s">
         <v>90</v>
       </c>
       <c r="H166" s="2" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="I166" s="15" t="n">
         <v>3.5</v>
@@ -27208,7 +27211,7 @@
         <v>227</v>
       </c>
       <c r="O166" s="2" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="P166" s="2"/>
     </row>
@@ -27217,7 +27220,7 @@
         <v>76</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C167" s="2" t="s">
         <v>243</v>
@@ -27226,16 +27229,16 @@
         <v>46300</v>
       </c>
       <c r="E167" s="2" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G167" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H167" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I167" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P167,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -27243,19 +27246,19 @@
       </c>
       <c r="J167" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$G$2:$G$125,MATCH(P167,'Recurring Budgets'!$A$2:$A$125,0))</f>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="K167" s="21" t="n">
         <f aca="false">I167+J167</f>
-        <v>1.0833</v>
+        <v>1.3333</v>
       </c>
       <c r="L167" s="2" t="n">
         <f aca="false">ROUND(K167*60,0)</f>
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="M167" s="22" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$M$2:$M$125,MATCH(P167,'Recurring Budgets'!$A$2:$A$125,0))</f>
-        <v>102.9135</v>
+        <v>165.4135</v>
       </c>
       <c r="N167" s="8" t="str">
         <f aca="false">INDEX('Recurring Budgets'!$P$2:$P$125,MATCH(P167,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -27263,7 +27266,7 @@
       </c>
       <c r="O167" s="8" t="str">
         <f aca="false">INDEX('Recurring Budgets'!$Q$2:$Q$125,MATCH(P167,'Recurring Budgets'!$A$2:$A$125,0))</f>
-        <v>Weekly bookkeeping/settlement time ÷ weeks per month.</v>
+        <v>Weekly bookkeeping/settlement time ÷ weeks per month. Review = Lisa oversight, 15 min per occurrence (work moving to Jessica).</v>
       </c>
       <c r="P167" s="2" t="s">
         <v>441</v>
@@ -27274,7 +27277,7 @@
         <v>76</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C168" s="2" t="s">
         <v>231</v>
@@ -27283,16 +27286,16 @@
         <v>46302</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F168" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G168" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H168" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I168" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P168,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -27331,7 +27334,7 @@
         <v>76</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C169" s="2" t="s">
         <v>371</v>
@@ -27340,16 +27343,16 @@
         <v>46304</v>
       </c>
       <c r="E169" s="2" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G169" s="2" t="s">
         <v>56</v>
       </c>
       <c r="H169" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I169" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P169,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -27357,19 +27360,19 @@
       </c>
       <c r="J169" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$G$2:$G$125,MATCH(P169,'Recurring Budgets'!$A$2:$A$125,0))</f>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="K169" s="21" t="n">
         <f aca="false">I169+J169</f>
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
       <c r="L169" s="2" t="n">
         <f aca="false">ROUND(K169*60,0)</f>
-        <v>255</v>
+        <v>270</v>
       </c>
       <c r="M169" s="22" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$M$2:$M$125,MATCH(P169,'Recurring Budgets'!$A$2:$A$125,0))</f>
-        <v>403.75</v>
+        <v>466.25</v>
       </c>
       <c r="N169" s="8" t="str">
         <f aca="false">INDEX('Recurring Budgets'!$P$2:$P$125,MATCH(P169,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -27377,7 +27380,7 @@
       </c>
       <c r="O169" s="8" t="str">
         <f aca="false">INDEX('Recurring Budgets'!$Q$2:$Q$125,MATCH(P169,'Recurring Budgets'!$A$2:$A$125,0))</f>
-        <v>Payroll time ÷ pay periods per month.</v>
+        <v>Payroll time ÷ pay periods per month. Review = Lisa oversight, 15 min per occurrence (work moving to Jessica).</v>
       </c>
       <c r="P169" s="2" t="s">
         <v>435</v>
@@ -27388,7 +27391,7 @@
         <v>76</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C170" s="2" t="s">
         <v>240</v>
@@ -27397,16 +27400,16 @@
         <v>46310</v>
       </c>
       <c r="E170" s="2" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="G170" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H170" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I170" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P170,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -27454,16 +27457,16 @@
         <v>46325</v>
       </c>
       <c r="E171" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G171" s="2" t="s">
         <v>161</v>
       </c>
       <c r="H171" s="2" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="I171" s="16" t="n">
         <f aca="false">INDEX('1099 Oct 30'!$F$5:$F$45,MATCH(P171,'1099 Oct 30'!$A$5:$A$45,0))</f>
@@ -27488,7 +27491,7 @@
         <v>227</v>
       </c>
       <c r="O171" s="2" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="P171" s="2" t="s">
         <v>76</v>
@@ -27499,7 +27502,7 @@
         <v>81</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C172" s="2" t="s">
         <v>231</v>
@@ -27508,16 +27511,16 @@
         <v>46301</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G172" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H172" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I172" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P172,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -27548,7 +27551,7 @@
         <v>Josephine's Apr–May 2026 closes + allowance for a new person (Valentina's hours not used).</v>
       </c>
       <c r="P172" s="2" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27565,16 +27568,16 @@
         <v>46325</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G173" s="2" t="s">
         <v>161</v>
       </c>
       <c r="H173" s="2" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="I173" s="16" t="n">
         <f aca="false">INDEX('1099 Oct 30'!$F$5:$F$45,MATCH(P173,'1099 Oct 30'!$A$5:$A$45,0))</f>
@@ -27599,7 +27602,7 @@
         <v>227</v>
       </c>
       <c r="O173" s="2" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="P173" s="2" t="s">
         <v>81</v>
@@ -27610,7 +27613,7 @@
         <v>82</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C174" s="2" t="s">
         <v>240</v>
@@ -27619,16 +27622,16 @@
         <v>46280</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G174" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H174" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I174" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P174,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -27659,7 +27662,7 @@
         <v>Sales tax time per month. Opened Sept 2026 – provisional, modelled on VV1012 (operating Toast restaurant). Revisit after 2–3 months open.</v>
       </c>
       <c r="P174" s="2" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27667,7 +27670,7 @@
         <v>82</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C175" s="2" t="s">
         <v>237</v>
@@ -27676,16 +27679,16 @@
         <v>46293</v>
       </c>
       <c r="E175" s="2" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F175" s="2" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="G175" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H175" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I175" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P175,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -27693,19 +27696,19 @@
       </c>
       <c r="J175" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$G$2:$G$125,MATCH(P175,'Recurring Budgets'!$A$2:$A$125,0))</f>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="K175" s="21" t="n">
         <f aca="false">I175+J175</f>
-        <v>1.0833</v>
+        <v>1.3333</v>
       </c>
       <c r="L175" s="2" t="n">
         <f aca="false">ROUND(K175*60,0)</f>
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="M175" s="22" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$M$2:$M$125,MATCH(P175,'Recurring Budgets'!$A$2:$A$125,0))</f>
-        <v>102.9135</v>
+        <v>165.4135</v>
       </c>
       <c r="N175" s="8" t="str">
         <f aca="false">INDEX('Recurring Budgets'!$P$2:$P$125,MATCH(P175,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -27713,10 +27716,10 @@
       </c>
       <c r="O175" s="8" t="str">
         <f aca="false">INDEX('Recurring Budgets'!$Q$2:$Q$125,MATCH(P175,'Recurring Budgets'!$A$2:$A$125,0))</f>
-        <v>Weekly bookkeeping/settlement time ÷ weeks per month. Opened Sept 2026 – provisional, modelled on VV1012 (operating Toast restaurant). Revisit after 2–3 months open.</v>
+        <v>Weekly bookkeeping/settlement time ÷ weeks per month. Opened Sept 2026 – provisional, modelled on VV1012 (operating Toast restaurant). Revisit after 2–3 months open. Review = Lisa oversight, 15 min per occurrence (work moving to Jessica).</v>
       </c>
       <c r="P175" s="2" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27724,7 +27727,7 @@
         <v>82</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C176" s="2" t="s">
         <v>237</v>
@@ -27733,16 +27736,16 @@
         <v>46293</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="G176" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H176" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I176" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P176,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -27773,7 +27776,7 @@
         <v>CFO cash-flow/advisory time ÷ weeks per month. Opened Sept 2026 – provisional, modelled on VV1012 (operating Toast restaurant). Revisit after 2–3 months open.</v>
       </c>
       <c r="P176" s="2" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27781,7 +27784,7 @@
         <v>82</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C177" s="2" t="s">
         <v>237</v>
@@ -27790,16 +27793,16 @@
         <v>46295</v>
       </c>
       <c r="E177" s="2" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="G177" s="2" t="s">
         <v>56</v>
       </c>
       <c r="H177" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I177" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P177,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -27807,19 +27810,19 @@
       </c>
       <c r="J177" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$G$2:$G$125,MATCH(P177,'Recurring Budgets'!$A$2:$A$125,0))</f>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="K177" s="21" t="n">
         <f aca="false">I177+J177</f>
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
       <c r="L177" s="2" t="n">
         <f aca="false">ROUND(K177*60,0)</f>
-        <v>255</v>
+        <v>270</v>
       </c>
       <c r="M177" s="22" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$M$2:$M$125,MATCH(P177,'Recurring Budgets'!$A$2:$A$125,0))</f>
-        <v>403.75</v>
+        <v>466.25</v>
       </c>
       <c r="N177" s="8" t="str">
         <f aca="false">INDEX('Recurring Budgets'!$P$2:$P$125,MATCH(P177,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -27827,10 +27830,10 @@
       </c>
       <c r="O177" s="8" t="str">
         <f aca="false">INDEX('Recurring Budgets'!$Q$2:$Q$125,MATCH(P177,'Recurring Budgets'!$A$2:$A$125,0))</f>
-        <v>Payroll time ÷ pay periods per month. Opened Sept 2026 – provisional, modelled on VV1012 (operating Toast restaurant). Revisit after 2–3 months open.</v>
+        <v>Payroll time ÷ pay periods per month. Opened Sept 2026 – provisional, modelled on VV1012 (operating Toast restaurant). Revisit after 2–3 months open. Review = Lisa oversight, 15 min per occurrence (work moving to Jessica).</v>
       </c>
       <c r="P177" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27841,22 +27844,22 @@
         <v>114</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D178" s="31" t="n">
         <v>46295</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="G178" s="2" t="s">
         <v>90</v>
       </c>
       <c r="H178" s="2" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="I178" s="15" t="n">
         <v>3.5</v>
@@ -27880,7 +27883,7 @@
         <v>227</v>
       </c>
       <c r="O178" s="2" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="P178" s="2"/>
     </row>
@@ -27889,7 +27892,7 @@
         <v>82</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C179" s="2" t="s">
         <v>231</v>
@@ -27898,16 +27901,16 @@
         <v>46301</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G179" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H179" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I179" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P179,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -27938,7 +27941,7 @@
         <v>Includes Month-end 3.2. Opened Sept 2026 – provisional, modelled on VV1012 (operating Toast restaurant). Revisit after 2–3 months open.</v>
       </c>
       <c r="P179" s="2" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27946,7 +27949,7 @@
         <v>82</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C180" s="2" t="s">
         <v>240</v>
@@ -27955,16 +27958,16 @@
         <v>46310</v>
       </c>
       <c r="E180" s="2" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G180" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H180" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I180" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P180,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -27995,7 +27998,7 @@
         <v>Sales tax time per month. Opened Sept 2026 – provisional, modelled on VV1012 (operating Toast restaurant). Revisit after 2–3 months open.</v>
       </c>
       <c r="P180" s="2" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28012,16 +28015,16 @@
         <v>46325</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G181" s="2" t="s">
         <v>161</v>
       </c>
       <c r="H181" s="2" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="I181" s="16" t="n">
         <f aca="false">INDEX('1099 Oct 30'!$F$5:$F$45,MATCH(P181,'1099 Oct 30'!$A$5:$A$45,0))</f>
@@ -28046,7 +28049,7 @@
         <v>227</v>
       </c>
       <c r="O181" s="2" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="P181" s="2" t="s">
         <v>82</v>
@@ -28057,7 +28060,7 @@
         <v>83</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C182" s="2" t="s">
         <v>237</v>
@@ -28066,16 +28069,16 @@
         <v>46218</v>
       </c>
       <c r="E182" s="2" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G182" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H182" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I182" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P182,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -28106,7 +28109,7 @@
         <v>Includes Month-end 6.5, Payroll 1.2.</v>
       </c>
       <c r="P182" s="2" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28114,7 +28117,7 @@
         <v>83</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C183" s="2" t="s">
         <v>237</v>
@@ -28123,16 +28126,16 @@
         <v>46315</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G183" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H183" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I183" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P183,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -28163,7 +28166,7 @@
         <v>Includes Month-end 6.5, Payroll 1.2.</v>
       </c>
       <c r="P183" s="2" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28180,16 +28183,16 @@
         <v>46325</v>
       </c>
       <c r="E184" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F184" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G184" s="2" t="s">
         <v>161</v>
       </c>
       <c r="H184" s="2" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="I184" s="16" t="n">
         <f aca="false">INDEX('1099 Oct 30'!$F$5:$F$45,MATCH(P184,'1099 Oct 30'!$A$5:$A$45,0))</f>
@@ -28214,7 +28217,7 @@
         <v>227</v>
       </c>
       <c r="O184" s="2" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="P184" s="2" t="s">
         <v>83</v>
@@ -28240,7 +28243,7 @@
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="4" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B186" s="2"/>
       <c r="C186" s="2"/>
@@ -28255,19 +28258,19 @@
       </c>
       <c r="J186" s="4" t="n">
         <f aca="false">SUM(J2:J184)</f>
-        <v>54.5</v>
+        <v>56</v>
       </c>
       <c r="K186" s="4" t="n">
         <f aca="false">SUM(K2:K184)</f>
-        <v>592.3333</v>
+        <v>593.8333</v>
       </c>
       <c r="L186" s="4" t="n">
         <f aca="false">SUM(L2:L184)</f>
-        <v>35544</v>
+        <v>35634</v>
       </c>
       <c r="M186" s="32" t="n">
         <f aca="false">SUM(M2:M184)</f>
-        <v>72133.356</v>
+        <v>72508.356</v>
       </c>
       <c r="N186" s="2"/>
       <c r="O186" s="2"/>
@@ -28302,7 +28305,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="33" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -28323,19 +28326,19 @@
         <v>3</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28505,7 +28508,7 @@
         <v>264</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28675,7 +28678,7 @@
         <v>232</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28784,7 +28787,7 @@
         <v>261</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28807,7 +28810,7 @@
         <v>232</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28916,7 +28919,7 @@
         <v>264</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28992,17 +28995,17 @@
       </c>
       <c r="C34" s="34" t="n">
         <f aca="false">SUMIFS('Recurring Budgets'!$O$2:$O$125,'Recurring Budgets'!$B$2:$B$125,A34)</f>
-        <v>0.0833</v>
+        <v>0.624966666666667</v>
       </c>
       <c r="D34" s="35" t="n">
         <f aca="false">B34+C34</f>
-        <v>8.2916</v>
+        <v>8.83326666666667</v>
       </c>
       <c r="E34" s="28" t="s">
         <v>376</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29216,7 +29219,7 @@
         <v>376</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29239,7 +29242,7 @@
         <v>312</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29273,11 +29276,11 @@
       </c>
       <c r="C47" s="34" t="n">
         <f aca="false">SUMIFS('Recurring Budgets'!$O$2:$O$125,'Recurring Budgets'!$B$2:$B$125,A47)</f>
-        <v>2.8333</v>
+        <v>4.4583</v>
       </c>
       <c r="D47" s="35" t="n">
         <f aca="false">B47+C47</f>
-        <v>25.375</v>
+        <v>27</v>
       </c>
       <c r="E47" s="28" t="s">
         <v>312</v>
@@ -29315,17 +29318,17 @@
       </c>
       <c r="C49" s="34" t="n">
         <f aca="false">SUMIFS('Recurring Budgets'!$O$2:$O$125,'Recurring Budgets'!$B$2:$B$125,A49)</f>
-        <v>2.8333</v>
+        <v>4.4583</v>
       </c>
       <c r="D49" s="35" t="n">
         <f aca="false">B49+C49</f>
-        <v>25.375</v>
+        <v>27</v>
       </c>
       <c r="E49" s="27" t="s">
         <v>264</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29359,11 +29362,11 @@
       </c>
       <c r="C51" s="19" t="n">
         <f aca="false">SUM(C4:C50)</f>
-        <v>33.6943</v>
+        <v>37.4859666666667</v>
       </c>
       <c r="D51" s="19" t="n">
         <f aca="false">SUM(D4:D50)</f>
-        <v>302.241891666667</v>
+        <v>306.033558333333</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" s="2"/>
@@ -29378,7 +29381,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="4" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B53" s="2"/>
       <c r="C53" s="18" t="n">
@@ -29391,7 +29394,7 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="4" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B54" s="18" t="n">
         <f aca="false">Assumptions!$B$33</f>
@@ -29404,7 +29407,7 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="4" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B55" s="4" t="n">
         <f aca="false">B51+B54</f>
@@ -29412,18 +29415,18 @@
       </c>
       <c r="C55" s="4" t="n">
         <f aca="false">C51+C53</f>
-        <v>58.6943</v>
+        <v>62.4859666666667</v>
       </c>
       <c r="D55" s="4" t="n">
         <f aca="false">B55+C55</f>
-        <v>337.241891666667</v>
+        <v>341.033558333333</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" s="2"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="3" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
@@ -29460,7 +29463,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="33" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -29471,7 +29474,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -29491,30 +29494,30 @@
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B5" s="9" t="n">
         <v>66</v>
@@ -29532,12 +29535,12 @@
         <v>32.2</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B6" s="9" t="n">
         <v>48</v>
@@ -29555,12 +29558,12 @@
         <v>57.8</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B7" s="9" t="n">
         <v>31</v>
@@ -29578,12 +29581,12 @@
         <v>20</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B8" s="9" t="n">
         <v>28</v>
@@ -29601,12 +29604,12 @@
         <v>22.1</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B9" s="9" t="n">
         <v>26</v>
@@ -29624,12 +29627,12 @@
         <v>22.2</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B10" s="9" t="n">
         <v>12</v>
@@ -29647,12 +29650,12 @@
         <v>14.4</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B11" s="9" t="n">
         <v>9</v>
@@ -29670,12 +29673,12 @@
         <v>2.5</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B12" s="9" t="n">
         <v>9</v>
@@ -29693,12 +29696,12 @@
         <v>10</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B13" s="9" t="n">
         <v>8</v>
@@ -29716,7 +29719,7 @@
         <v>2.5</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29739,7 +29742,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -29750,13 +29753,13 @@
     </row>
     <row r="17" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
@@ -29765,13 +29768,13 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B18" s="9" t="n">
         <v>0.5</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
@@ -29780,13 +29783,13 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B19" s="9" t="n">
         <v>2.5</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
@@ -29801,7 +29804,7 @@
         <v>5.5</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
@@ -29810,13 +29813,13 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B21" s="9" t="s">
         <v>227</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
@@ -29850,7 +29853,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="33" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -29869,7 +29872,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -29888,49 +29891,49 @@
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="N3" s="5" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29938,7 +29941,7 @@
         <v>11</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C4" s="35" t="n">
         <v>1.25</v>
@@ -29983,7 +29986,7 @@
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2"/>
       <c r="B5" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C5" s="35" t="n">
         <v>0.75</v>
@@ -30020,7 +30023,7 @@
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2"/>
       <c r="B6" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C6" s="35"/>
       <c r="D6" s="35" t="n">
@@ -30049,7 +30052,7 @@
         <v>16</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C7" s="35" t="n">
         <v>1.1</v>
@@ -30080,7 +30083,7 @@
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2"/>
       <c r="B8" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C8" s="35"/>
       <c r="D8" s="35" t="n">
@@ -30107,7 +30110,7 @@
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2"/>
       <c r="B9" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C9" s="35"/>
       <c r="D9" s="35" t="n">
@@ -30134,7 +30137,7 @@
         <v>19</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C10" s="35" t="n">
         <v>1</v>
@@ -30163,7 +30166,7 @@
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2"/>
       <c r="B11" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C11" s="35"/>
       <c r="D11" s="35"/>
@@ -30184,7 +30187,7 @@
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2"/>
       <c r="B12" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C12" s="35"/>
       <c r="D12" s="35"/>
@@ -30209,7 +30212,7 @@
         <v>22</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C13" s="35" t="n">
         <v>1.4</v>
@@ -30254,7 +30257,7 @@
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2"/>
       <c r="B14" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C14" s="35" t="n">
         <v>0.75</v>
@@ -30295,7 +30298,7 @@
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2"/>
       <c r="B15" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C15" s="35"/>
       <c r="D15" s="35"/>
@@ -30322,7 +30325,7 @@
         <v>23</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C16" s="35" t="n">
         <v>1.25</v>
@@ -30367,7 +30370,7 @@
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2"/>
       <c r="B17" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C17" s="35" t="n">
         <v>0.75</v>
@@ -30408,7 +30411,7 @@
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2"/>
       <c r="B18" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C18" s="35"/>
       <c r="D18" s="35"/>
@@ -30435,7 +30438,7 @@
         <v>24</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C19" s="35" t="n">
         <v>1.1</v>
@@ -30480,7 +30483,7 @@
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2"/>
       <c r="B20" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C20" s="35" t="n">
         <v>0.5</v>
@@ -30519,7 +30522,7 @@
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2"/>
       <c r="B21" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C21" s="35"/>
       <c r="D21" s="35" t="n">
@@ -30550,7 +30553,7 @@
         <v>25</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C22" s="35" t="n">
         <v>0.8</v>
@@ -30595,7 +30598,7 @@
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2"/>
       <c r="B23" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C23" s="35" t="n">
         <v>0.5</v>
@@ -30636,7 +30639,7 @@
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2"/>
       <c r="B24" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C24" s="35"/>
       <c r="D24" s="35" t="n">
@@ -30665,7 +30668,7 @@
         <v>26</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C25" s="35" t="n">
         <v>1</v>
@@ -30710,7 +30713,7 @@
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2"/>
       <c r="B26" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C26" s="35" t="n">
         <v>0.5</v>
@@ -30753,7 +30756,7 @@
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2"/>
       <c r="B27" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C27" s="35"/>
       <c r="D27" s="35" t="n">
@@ -30784,7 +30787,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C28" s="35" t="n">
         <v>29.8</v>
@@ -30829,7 +30832,7 @@
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2"/>
       <c r="B29" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C29" s="35" t="n">
         <v>1</v>
@@ -30868,7 +30871,7 @@
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2"/>
       <c r="B30" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C30" s="35" t="n">
         <v>6.95</v>
@@ -30911,7 +30914,7 @@
         <v>31</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C31" s="35"/>
       <c r="D31" s="35" t="n">
@@ -30954,7 +30957,7 @@
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2"/>
       <c r="B32" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C32" s="35"/>
       <c r="D32" s="35" t="n">
@@ -30985,7 +30988,7 @@
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2"/>
       <c r="B33" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C33" s="35"/>
       <c r="D33" s="35" t="n">
@@ -31014,7 +31017,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C34" s="35" t="n">
         <v>3.25</v>
@@ -31055,7 +31058,7 @@
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2"/>
       <c r="B35" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C35" s="35"/>
       <c r="D35" s="35"/>
@@ -31080,7 +31083,7 @@
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2"/>
       <c r="B36" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C36" s="35"/>
       <c r="D36" s="35" t="n">
@@ -31107,7 +31110,7 @@
         <v>33</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C37" s="35" t="n">
         <v>18.45</v>
@@ -31152,7 +31155,7 @@
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2"/>
       <c r="B38" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C38" s="35" t="n">
         <v>1.5</v>
@@ -31191,7 +31194,7 @@
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2"/>
       <c r="B39" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C39" s="35" t="n">
         <v>6</v>
@@ -31234,7 +31237,7 @@
         <v>34</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C40" s="35"/>
       <c r="D40" s="35" t="n">
@@ -31277,7 +31280,7 @@
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="2"/>
       <c r="B41" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C41" s="35"/>
       <c r="D41" s="35" t="n">
@@ -31308,7 +31311,7 @@
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2"/>
       <c r="B42" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C42" s="35"/>
       <c r="D42" s="35" t="n">
@@ -31343,7 +31346,7 @@
         <v>35</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C43" s="35" t="n">
         <v>33</v>
@@ -31388,7 +31391,7 @@
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2"/>
       <c r="B44" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C44" s="35" t="n">
         <v>2</v>
@@ -31421,7 +31424,7 @@
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2"/>
       <c r="B45" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C45" s="35" t="n">
         <v>13.5</v>
@@ -31462,7 +31465,7 @@
         <v>91</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C46" s="35" t="n">
         <v>21.35</v>
@@ -31491,7 +31494,7 @@
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2"/>
       <c r="B47" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C47" s="35" t="n">
         <v>1.5</v>
@@ -31514,7 +31517,7 @@
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2"/>
       <c r="B48" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C48" s="35" t="n">
         <v>1.25</v>
@@ -31543,7 +31546,7 @@
         <v>36</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C49" s="35"/>
       <c r="D49" s="35"/>
@@ -31578,7 +31581,7 @@
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2"/>
       <c r="B50" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C50" s="35"/>
       <c r="D50" s="35"/>
@@ -31601,7 +31604,7 @@
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="2"/>
       <c r="B51" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C51" s="35"/>
       <c r="D51" s="35"/>
@@ -31636,7 +31639,7 @@
         <v>37</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C52" s="35" t="n">
         <v>12.4</v>
@@ -31681,7 +31684,7 @@
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="2"/>
       <c r="B53" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C53" s="35"/>
       <c r="D53" s="35" t="n">
@@ -31716,7 +31719,7 @@
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="2"/>
       <c r="B54" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C54" s="35" t="n">
         <v>2.25</v>
@@ -31761,7 +31764,7 @@
         <v>38</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C55" s="35" t="n">
         <v>8</v>
@@ -31806,7 +31809,7 @@
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2"/>
       <c r="B56" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C56" s="35" t="n">
         <v>2.5</v>
@@ -31843,7 +31846,7 @@
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="2"/>
       <c r="B57" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C57" s="35" t="n">
         <v>3.25</v>
@@ -31882,7 +31885,7 @@
         <v>39</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C58" s="35"/>
       <c r="D58" s="35"/>
@@ -31923,7 +31926,7 @@
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="2"/>
       <c r="B59" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C59" s="35"/>
       <c r="D59" s="35"/>
@@ -31958,7 +31961,7 @@
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="2"/>
       <c r="B60" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C60" s="35"/>
       <c r="D60" s="35"/>
@@ -31983,7 +31986,7 @@
         <v>40</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C61" s="35" t="n">
         <v>4.1</v>
@@ -32028,7 +32031,7 @@
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="2"/>
       <c r="B62" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C62" s="35" t="n">
         <v>0.25</v>
@@ -32061,7 +32064,7 @@
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="2"/>
       <c r="B63" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C63" s="35"/>
       <c r="D63" s="35" t="n">
@@ -32102,7 +32105,7 @@
         <v>41</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C64" s="35" t="n">
         <v>19</v>
@@ -32147,7 +32150,7 @@
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="2"/>
       <c r="B65" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C65" s="35" t="n">
         <v>5.25</v>
@@ -32184,7 +32187,7 @@
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="2"/>
       <c r="B66" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C66" s="35"/>
       <c r="D66" s="35"/>
@@ -32213,7 +32216,7 @@
         <v>43</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C67" s="35"/>
       <c r="D67" s="35" t="n">
@@ -32254,7 +32257,7 @@
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="2"/>
       <c r="B68" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C68" s="35"/>
       <c r="D68" s="35"/>
@@ -32287,7 +32290,7 @@
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="2"/>
       <c r="B69" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C69" s="35"/>
       <c r="D69" s="35"/>
@@ -32326,7 +32329,7 @@
         <v>45</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C70" s="35"/>
       <c r="D70" s="35"/>
@@ -32357,7 +32360,7 @@
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="2"/>
       <c r="B71" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C71" s="35"/>
       <c r="D71" s="35"/>
@@ -32378,7 +32381,7 @@
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="2"/>
       <c r="B72" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C72" s="35"/>
       <c r="D72" s="35"/>
@@ -32406,10 +32409,10 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="2" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C73" s="35"/>
       <c r="D73" s="35"/>
@@ -32442,7 +32445,7 @@
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="2"/>
       <c r="B74" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C74" s="35"/>
       <c r="D74" s="35"/>
@@ -32465,7 +32468,7 @@
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="2"/>
       <c r="B75" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C75" s="35"/>
       <c r="D75" s="35"/>
@@ -32498,7 +32501,7 @@
         <v>46</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C76" s="35" t="n">
         <v>1.75</v>
@@ -32543,7 +32546,7 @@
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="2"/>
       <c r="B77" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C77" s="35"/>
       <c r="D77" s="35"/>
@@ -32562,7 +32565,7 @@
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="2"/>
       <c r="B78" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C78" s="35" t="n">
         <v>0.75</v>
@@ -32601,7 +32604,7 @@
         <v>203</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C79" s="35" t="n">
         <v>46.85</v>
@@ -32646,7 +32649,7 @@
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="2"/>
       <c r="B80" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C80" s="35" t="n">
         <v>2.75</v>
@@ -32689,7 +32692,7 @@
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="2"/>
       <c r="B81" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C81" s="35" t="n">
         <v>14.65</v>
@@ -32734,7 +32737,7 @@
         <v>47</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C82" s="35" t="n">
         <v>0.6</v>
@@ -32779,7 +32782,7 @@
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="2"/>
       <c r="B83" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C83" s="35" t="n">
         <v>0.5</v>
@@ -32822,7 +32825,7 @@
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="2"/>
       <c r="B84" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C84" s="35"/>
       <c r="D84" s="35"/>
@@ -32844,10 +32847,10 @@
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="2" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C85" s="35"/>
       <c r="D85" s="35"/>
@@ -32872,7 +32875,7 @@
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="2"/>
       <c r="B86" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C86" s="35"/>
       <c r="D86" s="35"/>
@@ -32895,7 +32898,7 @@
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="2"/>
       <c r="B87" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C87" s="35"/>
       <c r="D87" s="35"/>
@@ -32916,7 +32919,7 @@
         <v>99</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C88" s="35"/>
       <c r="D88" s="35"/>
@@ -32935,13 +32938,13 @@
         <v>8.9</v>
       </c>
       <c r="O88" s="2" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="2"/>
       <c r="B89" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C89" s="35"/>
       <c r="D89" s="35"/>
@@ -32960,7 +32963,7 @@
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="2"/>
       <c r="B90" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C90" s="35"/>
       <c r="D90" s="35"/>
@@ -32985,7 +32988,7 @@
         <v>48</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C91" s="35" t="n">
         <v>2.75</v>
@@ -33030,7 +33033,7 @@
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="2"/>
       <c r="B92" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C92" s="35" t="n">
         <v>1.25</v>
@@ -33073,7 +33076,7 @@
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="2"/>
       <c r="B93" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C93" s="35"/>
       <c r="D93" s="35"/>
@@ -33102,7 +33105,7 @@
         <v>50</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C94" s="35" t="n">
         <v>6</v>
@@ -33147,7 +33150,7 @@
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="2"/>
       <c r="B95" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C95" s="35"/>
       <c r="D95" s="35" t="n">
@@ -33186,7 +33189,7 @@
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="2"/>
       <c r="B96" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C96" s="35" t="n">
         <v>0.25</v>
@@ -33231,7 +33234,7 @@
         <v>52</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C97" s="35" t="n">
         <v>8.35</v>
@@ -33272,7 +33275,7 @@
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="2"/>
       <c r="B98" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C98" s="35" t="n">
         <v>0.7</v>
@@ -33305,7 +33308,7 @@
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="2"/>
       <c r="B99" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C99" s="35" t="n">
         <v>4.7</v>
@@ -33342,7 +33345,7 @@
         <v>53</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C100" s="35" t="n">
         <v>4.4</v>
@@ -33387,7 +33390,7 @@
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="2"/>
       <c r="B101" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C101" s="35" t="n">
         <v>1</v>
@@ -33422,7 +33425,7 @@
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="2"/>
       <c r="B102" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C102" s="35" t="n">
         <v>0.25</v>
@@ -33459,7 +33462,7 @@
         <v>54</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C103" s="35"/>
       <c r="D103" s="35"/>
@@ -33500,7 +33503,7 @@
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="2"/>
       <c r="B104" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C104" s="35"/>
       <c r="D104" s="35"/>
@@ -33527,7 +33530,7 @@
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="2"/>
       <c r="B105" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C105" s="35"/>
       <c r="D105" s="35"/>
@@ -33566,7 +33569,7 @@
         <v>58</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C106" s="35" t="n">
         <v>1.65</v>
@@ -33607,7 +33610,7 @@
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="2"/>
       <c r="B107" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C107" s="35" t="n">
         <v>0.75</v>
@@ -33644,7 +33647,7 @@
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="2"/>
       <c r="B108" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C108" s="35"/>
       <c r="D108" s="35" t="n">
@@ -33675,7 +33678,7 @@
         <v>61</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C109" s="35" t="n">
         <v>16</v>
@@ -33720,7 +33723,7 @@
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="2"/>
       <c r="B110" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C110" s="35" t="n">
         <v>2.05</v>
@@ -33761,7 +33764,7 @@
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="2"/>
       <c r="B111" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C111" s="35"/>
       <c r="D111" s="35"/>
@@ -33798,7 +33801,7 @@
         <v>63</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C112" s="35" t="n">
         <v>1</v>
@@ -33835,7 +33838,7 @@
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="2"/>
       <c r="B113" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C113" s="35"/>
       <c r="D113" s="35" t="n">
@@ -33862,7 +33865,7 @@
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="2"/>
       <c r="B114" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C114" s="35"/>
       <c r="D114" s="35"/>
@@ -33891,7 +33894,7 @@
         <v>68</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C115" s="35" t="n">
         <v>13.5</v>
@@ -33936,7 +33939,7 @@
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="2"/>
       <c r="B116" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C116" s="35" t="n">
         <v>2.25</v>
@@ -33973,7 +33976,7 @@
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="2"/>
       <c r="B117" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C117" s="35"/>
       <c r="D117" s="35" t="n">
@@ -34016,7 +34019,7 @@
         <v>69</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C118" s="35" t="n">
         <v>0.1</v>
@@ -34055,7 +34058,7 @@
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="2"/>
       <c r="B119" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C119" s="35"/>
       <c r="D119" s="35"/>
@@ -34078,7 +34081,7 @@
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="2"/>
       <c r="B120" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C120" s="35"/>
       <c r="D120" s="35" t="n">
@@ -34109,7 +34112,7 @@
         <v>70</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C121" s="35" t="n">
         <v>6.55</v>
@@ -34154,7 +34157,7 @@
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="2"/>
       <c r="B122" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C122" s="35" t="n">
         <v>1.35</v>
@@ -34195,7 +34198,7 @@
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="2"/>
       <c r="B123" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C123" s="35" t="n">
         <v>2</v>
@@ -34238,7 +34241,7 @@
         <v>71</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C124" s="35" t="n">
         <v>4.8</v>
@@ -34283,7 +34286,7 @@
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="2"/>
       <c r="B125" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C125" s="35" t="n">
         <v>1.7</v>
@@ -34322,7 +34325,7 @@
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="2"/>
       <c r="B126" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C126" s="35" t="n">
         <v>0.75</v>
@@ -34356,10 +34359,10 @@
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="2" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C127" s="35"/>
       <c r="D127" s="35"/>
@@ -34382,7 +34385,7 @@
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="2"/>
       <c r="B128" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C128" s="35"/>
       <c r="D128" s="35"/>
@@ -34401,7 +34404,7 @@
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="2"/>
       <c r="B129" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C129" s="35"/>
       <c r="D129" s="35"/>
@@ -34422,7 +34425,7 @@
         <v>72</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C130" s="35" t="n">
         <v>3.85</v>
@@ -34459,7 +34462,7 @@
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="2"/>
       <c r="B131" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C131" s="35"/>
       <c r="D131" s="35" t="n">
@@ -34484,7 +34487,7 @@
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="2"/>
       <c r="B132" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C132" s="35" t="n">
         <v>1</v>
@@ -34515,7 +34518,7 @@
         <v>73</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C133" s="35"/>
       <c r="D133" s="35" t="n">
@@ -34556,7 +34559,7 @@
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="2"/>
       <c r="B134" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C134" s="35"/>
       <c r="D134" s="35"/>
@@ -34575,7 +34578,7 @@
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="2"/>
       <c r="B135" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C135" s="35"/>
       <c r="D135" s="35" t="n">
@@ -34610,7 +34613,7 @@
         <v>74</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C136" s="35" t="n">
         <v>0.35</v>
@@ -34655,7 +34658,7 @@
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="2"/>
       <c r="B137" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C137" s="35"/>
       <c r="D137" s="35" t="n">
@@ -34688,7 +34691,7 @@
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="2"/>
       <c r="B138" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C138" s="35"/>
       <c r="D138" s="35" t="n">
@@ -34729,7 +34732,7 @@
         <v>75</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C139" s="35" t="n">
         <v>0.7</v>
@@ -34774,7 +34777,7 @@
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="2"/>
       <c r="B140" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C140" s="35" t="n">
         <v>0.5</v>
@@ -34817,7 +34820,7 @@
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="2"/>
       <c r="B141" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C141" s="35"/>
       <c r="D141" s="35" t="n">
@@ -34844,7 +34847,7 @@
         <v>112</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C142" s="35"/>
       <c r="D142" s="35"/>
@@ -34861,13 +34864,13 @@
         <v>11.33</v>
       </c>
       <c r="O142" s="2" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="2"/>
       <c r="B143" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C143" s="35"/>
       <c r="D143" s="35"/>
@@ -34886,7 +34889,7 @@
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="2"/>
       <c r="B144" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C144" s="35"/>
       <c r="D144" s="35"/>
@@ -34909,7 +34912,7 @@
         <v>76</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C145" s="35"/>
       <c r="D145" s="35"/>
@@ -34940,7 +34943,7 @@
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="2"/>
       <c r="B146" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C146" s="35"/>
       <c r="D146" s="35"/>
@@ -34967,7 +34970,7 @@
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="2"/>
       <c r="B147" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C147" s="35"/>
       <c r="D147" s="35"/>
@@ -34998,7 +35001,7 @@
         <v>81</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C148" s="35" t="n">
         <v>0.95</v>
@@ -35043,7 +35046,7 @@
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="2"/>
       <c r="B149" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C149" s="35" t="n">
         <v>0.5</v>
@@ -35084,7 +35087,7 @@
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="2"/>
       <c r="B150" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C150" s="35"/>
       <c r="D150" s="35" t="n">
@@ -35113,7 +35116,7 @@
         <v>82</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C151" s="35" t="n">
         <v>18.15</v>
@@ -35152,13 +35155,13 @@
         <v>53.25</v>
       </c>
       <c r="O151" s="2" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="2"/>
       <c r="B152" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C152" s="35" t="n">
         <v>2.25</v>
@@ -35201,7 +35204,7 @@
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="2"/>
       <c r="B153" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C153" s="35" t="n">
         <v>8</v>
@@ -35244,7 +35247,7 @@
         <v>83</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C154" s="35" t="n">
         <v>6.5</v>
@@ -35283,7 +35286,7 @@
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="2"/>
       <c r="B155" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C155" s="35"/>
       <c r="D155" s="35" t="n">
@@ -35308,7 +35311,7 @@
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="2"/>
       <c r="B156" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C156" s="35"/>
       <c r="D156" s="35"/>

--- a/budget-hours/Karbon_Budget_Hours_2026-10.xlsx
+++ b/budget-hours/Karbon_Budget_Hours_2026-10.xlsx
@@ -4758,7 +4758,7 @@
       </c>
       <c r="E69" s="7" t="n">
         <f aca="false">ROUND('Recurring Budgets'!F75*IF(H69="CFO",Assumptions!$B$5,Assumptions!$B$4),0)</f>
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="F69" s="6" t="n">
         <f aca="false">ROUND('Recurring Budgets'!G75*60,0)/1440</f>
@@ -4770,7 +4770,7 @@
       </c>
       <c r="H69" s="8" t="str">
         <f aca="false">'Recurring Budgets'!L75</f>
-        <v>CFO</v>
+        <v>Staff</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="E70" s="7" t="n">
         <f aca="false">ROUND('Recurring Budgets'!F76*IF(H70="CFO",Assumptions!$B$5,Assumptions!$B$4),0)</f>
-        <v>229</v>
+        <v>87</v>
       </c>
       <c r="F70" s="6" t="n">
         <f aca="false">ROUND('Recurring Budgets'!G76*60,0)/1440</f>
@@ -4801,7 +4801,7 @@
       </c>
       <c r="H70" s="8" t="str">
         <f aca="false">'Recurring Budgets'!L76</f>
-        <v>CFO</v>
+        <v>Staff</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15109,11 +15109,11 @@
         <v>0</v>
       </c>
       <c r="L75" s="9" t="s">
-        <v>185</v>
+        <v>87</v>
       </c>
       <c r="M75" s="22" t="n">
         <f aca="false">F75*IF(L75="CFO",Assumptions!$B$5,Assumptions!$B$4)+G75*Assumptions!$B$5</f>
-        <v>83.325</v>
+        <v>31.6635</v>
       </c>
       <c r="N75" s="16" t="n">
         <f aca="false">F75*INDEX(Assumptions!$B$8:$B$14,MATCH(E75,Assumptions!$A$8:$A$14,0))</f>
@@ -15172,11 +15172,11 @@
         <v>15</v>
       </c>
       <c r="L76" s="9" t="s">
-        <v>185</v>
+        <v>87</v>
       </c>
       <c r="M76" s="22" t="n">
         <f aca="false">F76*IF(L76="CFO",Assumptions!$B$5,Assumptions!$B$4)+G76*Assumptions!$B$5</f>
-        <v>291.675</v>
+        <v>149.5865</v>
       </c>
       <c r="N76" s="16" t="n">
         <f aca="false">F76*INDEX(Assumptions!$B$8:$B$14,MATCH(E76,Assumptions!$A$8:$A$14,0))</f>
@@ -23829,7 +23829,7 @@
       </c>
       <c r="M105" s="22" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$M$2:$M$125,MATCH(P105,'Recurring Budgets'!$A$2:$A$125,0))</f>
-        <v>291.675</v>
+        <v>149.5865</v>
       </c>
       <c r="N105" s="8" t="str">
         <f aca="false">INDEX('Recurring Budgets'!$P$2:$P$125,MATCH(P105,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -23886,7 +23886,7 @@
       </c>
       <c r="M106" s="22" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$M$2:$M$125,MATCH(P106,'Recurring Budgets'!$A$2:$A$125,0))</f>
-        <v>83.325</v>
+        <v>31.6635</v>
       </c>
       <c r="N106" s="8" t="str">
         <f aca="false">INDEX('Recurring Budgets'!$P$2:$P$125,MATCH(P106,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -28270,7 +28270,7 @@
       </c>
       <c r="M186" s="32" t="n">
         <f aca="false">SUM(M2:M184)</f>
-        <v>72508.356</v>
+        <v>72314.606</v>
       </c>
       <c r="N186" s="2"/>
       <c r="O186" s="2"/>

--- a/budget-hours/Karbon_Budget_Hours_2026-10.xlsx
+++ b/budget-hours/Karbon_Budget_Hours_2026-10.xlsx
@@ -800,6 +800,9 @@
     <t xml:space="preserve">7327 Tierra Buena LLC|1099|1099 Quarterly Review|1099</t>
   </si>
   <si>
+    <t xml:space="preserve">1099 tier Standard: ongoing quarterly review (half a full review). See 1099 tab for the Oct 30 cycle.</t>
+  </si>
+  <si>
     <t xml:space="preserve">7327 Tierra Buena LLC|Monthly Financials|Month End Close|Monthly</t>
   </si>
   <si>
@@ -842,36 +845,36 @@
     <t xml:space="preserve">Amerisource HR Consulting Group LLC|1099|1099 Quarterly Review|1099</t>
   </si>
   <si>
+    <t xml:space="preserve">Amerisource HR Consulting Group LLC|Year-end review|Adjusting Journal Entry Request|Annual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Year-end review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Year-end/tax hours Oct 2025–Sep 2026 (5.6h).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amerisource HR Consulting Group LLC|Monthly Financials|Month End Close|Monthly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Includes Month-end 5.0, Payroll 11.7, CFO advisory 0.2.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amerisource HR Consulting Group LLC|Bookkeeping|Bookkeeping &amp; Bill Pay|Weekly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bookkeeping</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weekly bookkeeping/settlement time ÷ weeks per month.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSD Contracting LLC|1099|1099 Quarterly Review|1099</t>
+  </si>
+  <si>
     <t xml:space="preserve">1099 tier Complex: ongoing quarterly review (half a full review). See 1099 tab for the Oct 30 cycle.</t>
   </si>
   <si>
-    <t xml:space="preserve">Amerisource HR Consulting Group LLC|Year-end review|Adjusting Journal Entry Request|Annual</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Year-end review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Year-end/tax hours Oct 2025–Sep 2026 (5.6h).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amerisource HR Consulting Group LLC|Monthly Financials|Month End Close|Monthly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Includes Month-end 5.0, Payroll 11.7, CFO advisory 0.2.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amerisource HR Consulting Group LLC|Bookkeeping|Bookkeeping &amp; Bill Pay|Weekly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bookkeeping</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weekly bookkeeping/settlement time ÷ weeks per month.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSD Contracting LLC|1099|1099 Quarterly Review|1099</t>
-  </si>
-  <si>
     <t xml:space="preserve">BSD Contracting LLC|Monthly Financials|Month End Close|Monthly</t>
   </si>
   <si>
@@ -896,9 +899,6 @@
     <t xml:space="preserve">BeckShar Development LLC|1099|1099 Quarterly Review|1099</t>
   </si>
   <si>
-    <t xml:space="preserve">1099 tier Standard: ongoing quarterly review (half a full review). See 1099 tab for the Oct 30 cycle.</t>
-  </si>
-  <si>
     <t xml:space="preserve">BeckShar Development LLC|Monthly Financials|Month End Close|Monthly</t>
   </si>
   <si>
@@ -935,7 +935,7 @@
     <t xml:space="preserve">Capital Financial LLC|1099|1099 Quarterly Review|1099</t>
   </si>
   <si>
-    <t xml:space="preserve">1099 tier Complex: ongoing quarterly review (half a full review). See 1099 tab for the Oct 30 cycle. Aug–Sep 2026 excluded (one-time payroll JE re-entry, resolved).</t>
+    <t xml:space="preserve">1099 tier Standard: ongoing quarterly review (half a full review). See 1099 tab for the Oct 30 cycle. Aug–Sep 2026 excluded (one-time payroll JE re-entry, resolved).</t>
   </si>
   <si>
     <t xml:space="preserve">Settled from 2026-03 (2026-03 – 2026-07)</t>
@@ -1304,7 +1304,7 @@
     <t xml:space="preserve">Southwest Rents Inc|1099|1099 Quarterly Review|1099</t>
   </si>
   <si>
-    <t xml:space="preserve">1099 tier Standard: ongoing quarterly review (half a full review). See 1099 tab for the Oct 30 cycle. Catch-up still underway; steady level uncertain. Backlog closes carry the remaining catch-up (~15–20h).</t>
+    <t xml:space="preserve">1099 tier Complex: ongoing quarterly review (half a full review). See 1099 tab for the Oct 30 cycle. Catch-up still underway; steady level uncertain. Backlog closes carry the remaining catch-up (~15–20h).</t>
   </si>
   <si>
     <t xml:space="preserve">Southwest Rents Inc|Year-end review|Adjusting Journal Entry Request|Annual</t>
@@ -1322,7 +1322,7 @@
     <t xml:space="preserve">T5 Family Holdings LLC|1099|1099 Quarterly Review|1099</t>
   </si>
   <si>
-    <t xml:space="preserve">1099 tier Standard: ongoing quarterly review (half a full review). See 1099 tab for the Oct 30 cycle. Carries Tavasci Group shared work since Harvest (moved from ESH). Group weekly items under Phil Tavasci Companies are budgeted from T5 history.</t>
+    <t xml:space="preserve">1099 tier Simple: ongoing quarterly review (half a full review). See 1099 tab for the Oct 30 cycle. Carries Tavasci Group shared work since Harvest (moved from ESH). Group weekly items under Phil Tavasci Companies are budgeted from T5 history.</t>
   </si>
   <si>
     <t xml:space="preserve">T5 Family Holdings LLC|Monthly Financials|Month End Close|Monthly</t>
@@ -3111,11 +3111,11 @@
       </c>
       <c r="D16" s="6" t="n">
         <f aca="false">ROUND('Recurring Budgets'!F12*60,0)/1440</f>
-        <v>0.0520833333333333</v>
+        <v>0.03125</v>
       </c>
       <c r="E16" s="7" t="n">
         <f aca="false">ROUND('Recurring Budgets'!F12*IF(H16="CFO",Assumptions!$B$5,Assumptions!$B$4),0)</f>
-        <v>119</v>
+        <v>71</v>
       </c>
       <c r="F16" s="6" t="n">
         <f aca="false">ROUND('Recurring Budgets'!G12*60,0)/1440</f>
@@ -3297,11 +3297,11 @@
       </c>
       <c r="D22" s="6" t="n">
         <f aca="false">ROUND('Recurring Budgets'!F18*60,0)/1440</f>
-        <v>0.0833333333333333</v>
+        <v>0.03125</v>
       </c>
       <c r="E22" s="7" t="n">
         <f aca="false">ROUND('Recurring Budgets'!F18*IF(H22="CFO",Assumptions!$B$5,Assumptions!$B$4),0)</f>
-        <v>190</v>
+        <v>71</v>
       </c>
       <c r="F22" s="6" t="n">
         <f aca="false">ROUND('Recurring Budgets'!G18*60,0)/1440</f>
@@ -3731,11 +3731,11 @@
       </c>
       <c r="D36" s="6" t="n">
         <f aca="false">ROUND('Recurring Budgets'!F32*60,0)/1440</f>
-        <v>0.03125</v>
+        <v>0.0833333333333333</v>
       </c>
       <c r="E36" s="7" t="n">
         <f aca="false">ROUND('Recurring Budgets'!F32*IF(H36="CFO",Assumptions!$B$5,Assumptions!$B$4),0)</f>
-        <v>71</v>
+        <v>190</v>
       </c>
       <c r="F36" s="6" t="n">
         <f aca="false">ROUND('Recurring Budgets'!G32*60,0)/1440</f>
@@ -3793,11 +3793,11 @@
       </c>
       <c r="D38" s="6" t="n">
         <f aca="false">ROUND('Recurring Budgets'!F34*60,0)/1440</f>
-        <v>0.0833333333333333</v>
+        <v>0.03125</v>
       </c>
       <c r="E38" s="7" t="n">
         <f aca="false">ROUND('Recurring Budgets'!F34*IF(H38="CFO",Assumptions!$B$5,Assumptions!$B$4),0)</f>
-        <v>190</v>
+        <v>71</v>
       </c>
       <c r="F38" s="6" t="n">
         <f aca="false">ROUND('Recurring Budgets'!G34*60,0)/1440</f>
@@ -4196,11 +4196,11 @@
       </c>
       <c r="D51" s="6" t="n">
         <f aca="false">ROUND('Recurring Budgets'!F48*60,0)/1440</f>
-        <v>0.03125</v>
+        <v>0.0833333333333333</v>
       </c>
       <c r="E51" s="7" t="n">
         <f aca="false">ROUND('Recurring Budgets'!F48*IF(H51="CFO",Assumptions!$B$5,Assumptions!$B$4),0)</f>
-        <v>71</v>
+        <v>190</v>
       </c>
       <c r="F51" s="6" t="n">
         <f aca="false">ROUND('Recurring Budgets'!G48*60,0)/1440</f>
@@ -4351,11 +4351,11 @@
       </c>
       <c r="D56" s="6" t="n">
         <f aca="false">ROUND('Recurring Budgets'!F62*60,0)/1440</f>
-        <v>0.03125</v>
+        <v>0.0159722222222222</v>
       </c>
       <c r="E56" s="7" t="n">
         <f aca="false">ROUND('Recurring Budgets'!F62*IF(H56="CFO",Assumptions!$B$5,Assumptions!$B$4),0)</f>
-        <v>71</v>
+        <v>36</v>
       </c>
       <c r="F56" s="6" t="n">
         <f aca="false">ROUND('Recurring Budgets'!G62*60,0)/1440</f>
@@ -5622,11 +5622,11 @@
       </c>
       <c r="D97" s="6" t="n">
         <f aca="false">ROUND('Recurring Budgets'!F103*60,0)/1440</f>
-        <v>0.03125</v>
+        <v>0.0833333333333333</v>
       </c>
       <c r="E97" s="7" t="n">
         <f aca="false">ROUND('Recurring Budgets'!F103*IF(H97="CFO",Assumptions!$B$5,Assumptions!$B$4),0)</f>
-        <v>71</v>
+        <v>190</v>
       </c>
       <c r="F97" s="6" t="n">
         <f aca="false">ROUND('Recurring Budgets'!G103*60,0)/1440</f>
@@ -5715,11 +5715,11 @@
       </c>
       <c r="D100" s="6" t="n">
         <f aca="false">ROUND('Recurring Budgets'!F106*60,0)/1440</f>
-        <v>0.03125</v>
+        <v>0.0159722222222222</v>
       </c>
       <c r="E100" s="7" t="n">
         <f aca="false">ROUND('Recurring Budgets'!F106*IF(H100="CFO",Assumptions!$B$5,Assumptions!$B$4),0)</f>
-        <v>71</v>
+        <v>36</v>
       </c>
       <c r="F100" s="6" t="n">
         <f aca="false">ROUND('Recurring Budgets'!G106*60,0)/1440</f>
@@ -6503,11 +6503,11 @@
       </c>
       <c r="D127" s="6" t="n">
         <f aca="false">ROUND('Open Items (Karbon)'!I15*60,0)/1440</f>
-        <v>0.104166666666667</v>
+        <v>0.0625</v>
       </c>
       <c r="E127" s="7" t="n">
         <f aca="false">ROUND('Open Items (Karbon)'!I15*IF(H127="CFO",Assumptions!$B$5,Assumptions!$B$4),0)</f>
-        <v>238</v>
+        <v>143</v>
       </c>
       <c r="F127" s="6" t="n">
         <f aca="false">ROUND('Open Items (Karbon)'!J15*60,0)/1440</f>
@@ -6593,11 +6593,11 @@
       </c>
       <c r="D130" s="6" t="n">
         <f aca="false">ROUND('Open Items (Karbon)'!I23*60,0)/1440</f>
-        <v>0.0833333333333333</v>
+        <v>0.03125</v>
       </c>
       <c r="E130" s="7" t="n">
         <f aca="false">ROUND('Open Items (Karbon)'!I23*IF(H130="CFO",Assumptions!$B$5,Assumptions!$B$4),0)</f>
-        <v>190</v>
+        <v>71</v>
       </c>
       <c r="F130" s="6" t="n">
         <f aca="false">ROUND('Open Items (Karbon)'!J23*60,0)/1440</f>
@@ -6863,11 +6863,11 @@
       </c>
       <c r="D139" s="6" t="n">
         <f aca="false">ROUND('Open Items (Karbon)'!I44*60,0)/1440</f>
-        <v>0.0625</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="E139" s="7" t="n">
         <f aca="false">ROUND('Open Items (Karbon)'!I44*IF(H139="CFO",Assumptions!$B$5,Assumptions!$B$4),0)</f>
-        <v>143</v>
+        <v>380</v>
       </c>
       <c r="F139" s="6" t="n">
         <f aca="false">ROUND('Open Items (Karbon)'!J44*60,0)/1440</f>
@@ -6923,11 +6923,11 @@
       </c>
       <c r="D141" s="6" t="n">
         <f aca="false">ROUND('Open Items (Karbon)'!I47*60,0)/1440</f>
-        <v>0.0833333333333333</v>
+        <v>0.03125</v>
       </c>
       <c r="E141" s="7" t="n">
         <f aca="false">ROUND('Open Items (Karbon)'!I47*IF(H141="CFO",Assumptions!$B$5,Assumptions!$B$4),0)</f>
-        <v>190</v>
+        <v>71</v>
       </c>
       <c r="F141" s="6" t="n">
         <f aca="false">ROUND('Open Items (Karbon)'!J47*60,0)/1440</f>
@@ -7163,11 +7163,11 @@
       </c>
       <c r="D149" s="6" t="n">
         <f aca="false">ROUND('Open Items (Karbon)'!I66*60,0)/1440</f>
-        <v>0.0625</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="E149" s="7" t="n">
         <f aca="false">ROUND('Open Items (Karbon)'!I66*IF(H149="CFO",Assumptions!$B$5,Assumptions!$B$4),0)</f>
-        <v>143</v>
+        <v>380</v>
       </c>
       <c r="F149" s="6" t="n">
         <f aca="false">ROUND('Open Items (Karbon)'!J66*60,0)/1440</f>
@@ -7223,11 +7223,11 @@
       </c>
       <c r="D151" s="6" t="n">
         <f aca="false">ROUND('Open Items (Karbon)'!I88*60,0)/1440</f>
-        <v>0.03125</v>
+        <v>0.0159722222222222</v>
       </c>
       <c r="E151" s="7" t="n">
         <f aca="false">ROUND('Open Items (Karbon)'!I88*IF(H151="CFO",Assumptions!$B$5,Assumptions!$B$4),0)</f>
-        <v>71</v>
+        <v>36</v>
       </c>
       <c r="F151" s="6" t="n">
         <f aca="false">ROUND('Open Items (Karbon)'!J88*60,0)/1440</f>
@@ -8033,11 +8033,11 @@
       </c>
       <c r="D178" s="6" t="n">
         <f aca="false">ROUND('Open Items (Karbon)'!I157*60,0)/1440</f>
-        <v>0.0625</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="E178" s="7" t="n">
         <f aca="false">ROUND('Open Items (Karbon)'!I157*IF(H178="CFO",Assumptions!$B$5,Assumptions!$B$4),0)</f>
-        <v>143</v>
+        <v>380</v>
       </c>
       <c r="F178" s="6" t="n">
         <f aca="false">ROUND('Open Items (Karbon)'!J157*60,0)/1440</f>
@@ -8063,11 +8063,11 @@
       </c>
       <c r="D179" s="6" t="n">
         <f aca="false">ROUND('Open Items (Karbon)'!I160*60,0)/1440</f>
-        <v>0.0472222222222222</v>
+        <v>0.0236111111111111</v>
       </c>
       <c r="E179" s="7" t="n">
         <f aca="false">ROUND('Open Items (Karbon)'!I160*IF(H179="CFO",Assumptions!$B$5,Assumptions!$B$4),0)</f>
-        <v>107</v>
+        <v>53</v>
       </c>
       <c r="F179" s="6" t="n">
         <f aca="false">ROUND('Open Items (Karbon)'!J160*60,0)/1440</f>
@@ -9273,14 +9273,14 @@
         <v>24</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>177</v>
       </c>
       <c r="D9" s="16" t="n">
         <f aca="false">INDEX(Assumptions!$B$17:$B$20,MATCH(B9,Assumptions!$A$17:$A$20,0))</f>
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="E9" s="16" t="n">
         <f aca="false">INDEX(Assumptions!$B$23:$B$27,MATCH(C9,Assumptions!$A$23:$A$27,0))</f>
@@ -9288,15 +9288,15 @@
       </c>
       <c r="F9" s="17" t="n">
         <f aca="false">D9*E9</f>
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="G9" s="10" t="n">
         <f aca="false">ROUND(F9*60,0)</f>
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="H9" s="16" t="n">
         <f aca="false">IF(C9="Excluded (in-house)",0,D9*Assumptions!$B$29)</f>
-        <v>1.25</v>
+        <v>0.75</v>
       </c>
       <c r="I9" s="15" t="n">
         <v>0</v>
@@ -9378,14 +9378,14 @@
         <v>27</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>173</v>
       </c>
       <c r="D12" s="16" t="n">
         <f aca="false">INDEX(Assumptions!$B$17:$B$20,MATCH(B12,Assumptions!$A$17:$A$20,0))</f>
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="E12" s="16" t="n">
         <f aca="false">INDEX(Assumptions!$B$23:$B$27,MATCH(C12,Assumptions!$A$23:$A$27,0))</f>
@@ -9393,15 +9393,15 @@
       </c>
       <c r="F12" s="17" t="n">
         <f aca="false">D12*E12</f>
-        <v>2</v>
+        <v>0.75</v>
       </c>
       <c r="G12" s="10" t="n">
         <f aca="false">ROUND(F12*60,0)</f>
-        <v>120</v>
+        <v>45</v>
       </c>
       <c r="H12" s="16" t="n">
         <f aca="false">IF(C12="Excluded (in-house)",0,D12*Assumptions!$B$29)</f>
-        <v>2</v>
+        <v>0.75</v>
       </c>
       <c r="I12" s="15" t="n">
         <v>4.5</v>
@@ -9555,14 +9555,14 @@
         <v>36</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C17" s="9" t="s">
         <v>177</v>
       </c>
       <c r="D17" s="16" t="n">
         <f aca="false">INDEX(Assumptions!$B$17:$B$20,MATCH(B17,Assumptions!$A$17:$A$20,0))</f>
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="E17" s="16" t="n">
         <f aca="false">INDEX(Assumptions!$B$23:$B$27,MATCH(C17,Assumptions!$A$23:$A$27,0))</f>
@@ -9570,15 +9570,15 @@
       </c>
       <c r="F17" s="17" t="n">
         <f aca="false">D17*E17</f>
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="G17" s="10" t="n">
         <f aca="false">ROUND(F17*60,0)</f>
-        <v>90</v>
+        <v>240</v>
       </c>
       <c r="H17" s="16" t="n">
         <f aca="false">IF(C17="Excluded (in-house)",0,D17*Assumptions!$B$29)</f>
-        <v>0.75</v>
+        <v>2</v>
       </c>
       <c r="I17" s="15" t="n">
         <v>0</v>
@@ -9590,14 +9590,14 @@
         <v>37</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C18" s="9" t="s">
         <v>173</v>
       </c>
       <c r="D18" s="16" t="n">
         <f aca="false">INDEX(Assumptions!$B$17:$B$20,MATCH(B18,Assumptions!$A$17:$A$20,0))</f>
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="E18" s="16" t="n">
         <f aca="false">INDEX(Assumptions!$B$23:$B$27,MATCH(C18,Assumptions!$A$23:$A$27,0))</f>
@@ -9605,15 +9605,15 @@
       </c>
       <c r="F18" s="17" t="n">
         <f aca="false">D18*E18</f>
-        <v>2</v>
+        <v>0.75</v>
       </c>
       <c r="G18" s="10" t="n">
         <f aca="false">ROUND(F18*60,0)</f>
-        <v>120</v>
+        <v>45</v>
       </c>
       <c r="H18" s="16" t="n">
         <f aca="false">IF(C18="Excluded (in-house)",0,D18*Assumptions!$B$29)</f>
-        <v>2</v>
+        <v>0.75</v>
       </c>
       <c r="I18" s="15" t="n">
         <v>3</v>
@@ -9769,14 +9769,14 @@
         <v>45</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C23" s="9" t="s">
         <v>177</v>
       </c>
       <c r="D23" s="16" t="n">
         <f aca="false">INDEX(Assumptions!$B$17:$B$20,MATCH(B23,Assumptions!$A$17:$A$20,0))</f>
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="E23" s="16" t="n">
         <f aca="false">INDEX(Assumptions!$B$23:$B$27,MATCH(C23,Assumptions!$A$23:$A$27,0))</f>
@@ -9784,15 +9784,15 @@
       </c>
       <c r="F23" s="17" t="n">
         <f aca="false">D23*E23</f>
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="G23" s="10" t="n">
         <f aca="false">ROUND(F23*60,0)</f>
-        <v>90</v>
+        <v>240</v>
       </c>
       <c r="H23" s="16" t="n">
         <f aca="false">IF(C23="Excluded (in-house)",0,D23*Assumptions!$B$29)</f>
-        <v>0.75</v>
+        <v>2</v>
       </c>
       <c r="I23" s="15" t="n">
         <v>0</v>
@@ -9878,14 +9878,14 @@
         <v>47</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C26" s="9" t="s">
         <v>173</v>
       </c>
       <c r="D26" s="16" t="n">
         <f aca="false">INDEX(Assumptions!$B$17:$B$20,MATCH(B26,Assumptions!$A$17:$A$20,0))</f>
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="E26" s="16" t="n">
         <f aca="false">INDEX(Assumptions!$B$23:$B$27,MATCH(C26,Assumptions!$A$23:$A$27,0))</f>
@@ -9893,15 +9893,15 @@
       </c>
       <c r="F26" s="17" t="n">
         <f aca="false">D26*E26</f>
-        <v>0.75</v>
+        <v>0.375</v>
       </c>
       <c r="G26" s="10" t="n">
         <f aca="false">ROUND(F26*60,0)</f>
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="H26" s="16" t="n">
         <f aca="false">IF(C26="Excluded (in-house)",0,D26*Assumptions!$B$29)</f>
-        <v>0.75</v>
+        <v>0.375</v>
       </c>
       <c r="I26" s="15" t="n">
         <v>1</v>
@@ -10341,14 +10341,14 @@
         <v>73</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C39" s="9" t="s">
         <v>177</v>
       </c>
       <c r="D39" s="16" t="n">
         <f aca="false">INDEX(Assumptions!$B$17:$B$20,MATCH(B39,Assumptions!$A$17:$A$20,0))</f>
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="E39" s="16" t="n">
         <f aca="false">INDEX(Assumptions!$B$23:$B$27,MATCH(C39,Assumptions!$A$23:$A$27,0))</f>
@@ -10356,15 +10356,15 @@
       </c>
       <c r="F39" s="17" t="n">
         <f aca="false">D39*E39</f>
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="G39" s="10" t="n">
         <f aca="false">ROUND(F39*60,0)</f>
-        <v>90</v>
+        <v>240</v>
       </c>
       <c r="H39" s="16" t="n">
         <f aca="false">IF(C39="Excluded (in-house)",0,D39*Assumptions!$B$29)</f>
-        <v>0.75</v>
+        <v>2</v>
       </c>
       <c r="I39" s="15" t="n">
         <v>0</v>
@@ -10376,14 +10376,14 @@
         <v>74</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C40" s="9" t="s">
         <v>175</v>
       </c>
       <c r="D40" s="16" t="n">
         <f aca="false">INDEX(Assumptions!$B$17:$B$20,MATCH(B40,Assumptions!$A$17:$A$20,0))</f>
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="E40" s="16" t="n">
         <f aca="false">INDEX(Assumptions!$B$23:$B$27,MATCH(C40,Assumptions!$A$23:$A$27,0))</f>
@@ -10391,15 +10391,15 @@
       </c>
       <c r="F40" s="17" t="n">
         <f aca="false">D40*E40</f>
-        <v>1.125</v>
+        <v>0.5625</v>
       </c>
       <c r="G40" s="10" t="n">
         <f aca="false">ROUND(F40*60,0)</f>
-        <v>68</v>
+        <v>34</v>
       </c>
       <c r="H40" s="16" t="n">
         <f aca="false">IF(C40="Excluded (in-house)",0,D40*Assumptions!$B$29)</f>
-        <v>0.75</v>
+        <v>0.375</v>
       </c>
       <c r="I40" s="15" t="n">
         <v>0.75</v>
@@ -10591,11 +10591,11 @@
       <c r="E46" s="2"/>
       <c r="F46" s="19" t="n">
         <f aca="false">SUM(F5:F45)</f>
-        <v>71.75</v>
+        <v>74.8125</v>
       </c>
       <c r="G46" s="20" t="n">
         <f aca="false">SUM(G5:G45)</f>
-        <v>4309</v>
+        <v>4493</v>
       </c>
       <c r="H46" s="19" t="n">
         <f aca="false">SUM(H5:H45)</f>
@@ -11387,22 +11387,22 @@
       </c>
       <c r="F12" s="16" t="n">
         <f aca="false">IFERROR(INDEX('1099 Oct 30'!$H$5:$H$45,MATCH(B12,'1099 Oct 30'!$A$5:$A$45,0)),0)</f>
-        <v>1.25</v>
+        <v>0.75</v>
       </c>
       <c r="G12" s="15" t="n">
         <v>0</v>
       </c>
       <c r="H12" s="21" t="n">
         <f aca="false">F12+G12</f>
-        <v>1.25</v>
+        <v>0.75</v>
       </c>
       <c r="I12" s="2" t="n">
         <f aca="false">ROUND(H12*60,0)</f>
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="J12" s="2" t="n">
         <f aca="false">ROUND(F12*60,0)</f>
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="K12" s="2" t="n">
         <f aca="false">ROUND(G12*60,0)</f>
@@ -11413,11 +11413,11 @@
       </c>
       <c r="M12" s="22" t="n">
         <f aca="false">F12*IF(L12="CFO",Assumptions!$B$5,Assumptions!$B$4)+G12*Assumptions!$B$5</f>
-        <v>118.75</v>
+        <v>71.25</v>
       </c>
       <c r="N12" s="16" t="n">
         <f aca="false">F12*INDEX(Assumptions!$B$8:$B$14,MATCH(E12,Assumptions!$A$8:$A$14,0))</f>
-        <v>0.416666666666667</v>
+        <v>0.25</v>
       </c>
       <c r="O12" s="16" t="n">
         <f aca="false">G12*INDEX(Assumptions!$B$8:$B$14,MATCH(E12,Assumptions!$A$8:$A$14,0))</f>
@@ -11427,7 +11427,7 @@
         <v>227</v>
       </c>
       <c r="Q12" s="24" t="s">
-        <v>228</v>
+        <v>255</v>
       </c>
       <c r="R12" s="2" t="s">
         <v>251</v>
@@ -11435,7 +11435,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B13" s="10" t="s">
         <v>24</v>
@@ -11490,7 +11490,7 @@
         <v>232</v>
       </c>
       <c r="Q13" s="24" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="R13" s="2" t="s">
         <v>251</v>
@@ -11498,7 +11498,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B14" s="10" t="s">
         <v>25</v>
@@ -11554,15 +11554,15 @@
         <v>227</v>
       </c>
       <c r="Q14" s="24" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="R14" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B15" s="10" t="s">
         <v>25</v>
@@ -11614,18 +11614,18 @@
         <v>0.25</v>
       </c>
       <c r="P15" s="26" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q15" s="24" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B16" s="10" t="s">
         <v>26</v>
@@ -11678,10 +11678,10 @@
         <v>0</v>
       </c>
       <c r="P16" s="27" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q16" s="24" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="R16" s="2" t="s">
         <v>229</v>
@@ -11689,7 +11689,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B17" s="10" t="s">
         <v>26</v>
@@ -11741,10 +11741,10 @@
         <v>0.3333</v>
       </c>
       <c r="P17" s="27" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q17" s="24" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="R17" s="2" t="s">
         <v>229</v>
@@ -11752,7 +11752,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B18" s="10" t="s">
         <v>27</v>
@@ -11768,22 +11768,22 @@
       </c>
       <c r="F18" s="16" t="n">
         <f aca="false">IFERROR(INDEX('1099 Oct 30'!$H$5:$H$45,MATCH(B18,'1099 Oct 30'!$A$5:$A$45,0)),0)</f>
-        <v>2</v>
+        <v>0.75</v>
       </c>
       <c r="G18" s="15" t="n">
         <v>0</v>
       </c>
       <c r="H18" s="21" t="n">
         <f aca="false">F18+G18</f>
-        <v>2</v>
+        <v>0.75</v>
       </c>
       <c r="I18" s="2" t="n">
         <f aca="false">ROUND(H18*60,0)</f>
-        <v>120</v>
+        <v>45</v>
       </c>
       <c r="J18" s="2" t="n">
         <f aca="false">ROUND(F18*60,0)</f>
-        <v>120</v>
+        <v>45</v>
       </c>
       <c r="K18" s="2" t="n">
         <f aca="false">ROUND(G18*60,0)</f>
@@ -11794,11 +11794,11 @@
       </c>
       <c r="M18" s="22" t="n">
         <f aca="false">F18*IF(L18="CFO",Assumptions!$B$5,Assumptions!$B$4)+G18*Assumptions!$B$5</f>
-        <v>190</v>
+        <v>71.25</v>
       </c>
       <c r="N18" s="16" t="n">
         <f aca="false">F18*INDEX(Assumptions!$B$8:$B$14,MATCH(E18,Assumptions!$A$8:$A$14,0))</f>
-        <v>0.666666666666667</v>
+        <v>0.25</v>
       </c>
       <c r="O18" s="16" t="n">
         <f aca="false">G18*INDEX(Assumptions!$B$8:$B$14,MATCH(E18,Assumptions!$A$8:$A$14,0))</f>
@@ -11808,7 +11808,7 @@
         <v>227</v>
       </c>
       <c r="Q18" s="24" t="s">
-        <v>269</v>
+        <v>255</v>
       </c>
       <c r="R18" s="2" t="s">
         <v>247</v>
@@ -12061,15 +12061,15 @@
         <v>227</v>
       </c>
       <c r="Q22" s="24" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="R22" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B23" s="10" t="s">
         <v>31</v>
@@ -12124,15 +12124,15 @@
         <v>232</v>
       </c>
       <c r="Q23" s="24" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="R23" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B24" s="10" t="s">
         <v>32</v>
@@ -12187,15 +12187,15 @@
         <v>232</v>
       </c>
       <c r="Q24" s="24" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="R24" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B25" s="10" t="s">
         <v>32</v>
@@ -12250,15 +12250,15 @@
         <v>232</v>
       </c>
       <c r="Q25" s="24" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="R25" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B26" s="10" t="s">
         <v>33</v>
@@ -12314,7 +12314,7 @@
         <v>227</v>
       </c>
       <c r="Q26" s="24" t="s">
-        <v>287</v>
+        <v>255</v>
       </c>
       <c r="R26" s="2" t="s">
         <v>229</v>
@@ -12441,7 +12441,7 @@
         <v>227</v>
       </c>
       <c r="Q28" s="24" t="s">
-        <v>287</v>
+        <v>255</v>
       </c>
       <c r="R28" s="2" t="s">
         <v>229</v>
@@ -12568,7 +12568,7 @@
         <v>227</v>
       </c>
       <c r="Q30" s="24" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="R30" s="2" t="s">
         <v>293</v>
@@ -12655,22 +12655,22 @@
       </c>
       <c r="F32" s="16" t="n">
         <f aca="false">IFERROR(INDEX('1099 Oct 30'!$H$5:$H$45,MATCH(B32,'1099 Oct 30'!$A$5:$A$45,0)),0)</f>
-        <v>0.75</v>
+        <v>2</v>
       </c>
       <c r="G32" s="15" t="n">
         <v>0</v>
       </c>
       <c r="H32" s="21" t="n">
         <f aca="false">F32+G32</f>
-        <v>0.75</v>
+        <v>2</v>
       </c>
       <c r="I32" s="2" t="n">
         <f aca="false">ROUND(H32*60,0)</f>
-        <v>45</v>
+        <v>120</v>
       </c>
       <c r="J32" s="2" t="n">
         <f aca="false">ROUND(F32*60,0)</f>
-        <v>45</v>
+        <v>120</v>
       </c>
       <c r="K32" s="2" t="n">
         <f aca="false">ROUND(G32*60,0)</f>
@@ -12681,11 +12681,11 @@
       </c>
       <c r="M32" s="22" t="n">
         <f aca="false">F32*IF(L32="CFO",Assumptions!$B$5,Assumptions!$B$4)+G32*Assumptions!$B$5</f>
-        <v>71.25</v>
+        <v>190</v>
       </c>
       <c r="N32" s="16" t="n">
         <f aca="false">F32*INDEX(Assumptions!$B$8:$B$14,MATCH(E32,Assumptions!$A$8:$A$14,0))</f>
-        <v>0.25</v>
+        <v>0.666666666666667</v>
       </c>
       <c r="O32" s="16" t="n">
         <f aca="false">G32*INDEX(Assumptions!$B$8:$B$14,MATCH(E32,Assumptions!$A$8:$A$14,0))</f>
@@ -12695,10 +12695,10 @@
         <v>227</v>
       </c>
       <c r="Q32" s="24" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="R32" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12761,7 +12761,7 @@
         <v>298</v>
       </c>
       <c r="R33" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12782,22 +12782,22 @@
       </c>
       <c r="F34" s="16" t="n">
         <f aca="false">IFERROR(INDEX('1099 Oct 30'!$H$5:$H$45,MATCH(B34,'1099 Oct 30'!$A$5:$A$45,0)),0)</f>
-        <v>2</v>
+        <v>0.75</v>
       </c>
       <c r="G34" s="15" t="n">
         <v>0</v>
       </c>
       <c r="H34" s="21" t="n">
         <f aca="false">F34+G34</f>
-        <v>2</v>
+        <v>0.75</v>
       </c>
       <c r="I34" s="2" t="n">
         <f aca="false">ROUND(H34*60,0)</f>
-        <v>120</v>
+        <v>45</v>
       </c>
       <c r="J34" s="2" t="n">
         <f aca="false">ROUND(F34*60,0)</f>
-        <v>120</v>
+        <v>45</v>
       </c>
       <c r="K34" s="2" t="n">
         <f aca="false">ROUND(G34*60,0)</f>
@@ -12808,11 +12808,11 @@
       </c>
       <c r="M34" s="22" t="n">
         <f aca="false">F34*IF(L34="CFO",Assumptions!$B$5,Assumptions!$B$4)+G34*Assumptions!$B$5</f>
-        <v>190</v>
+        <v>71.25</v>
       </c>
       <c r="N34" s="16" t="n">
         <f aca="false">F34*INDEX(Assumptions!$B$8:$B$14,MATCH(E34,Assumptions!$A$8:$A$14,0))</f>
-        <v>0.666666666666667</v>
+        <v>0.25</v>
       </c>
       <c r="O34" s="16" t="n">
         <f aca="false">G34*INDEX(Assumptions!$B$8:$B$14,MATCH(E34,Assumptions!$A$8:$A$14,0))</f>
@@ -12949,10 +12949,10 @@
         <v>227</v>
       </c>
       <c r="Q36" s="24" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="R36" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13015,7 +13015,7 @@
         <v>306</v>
       </c>
       <c r="R37" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13076,10 +13076,10 @@
         <v>227</v>
       </c>
       <c r="Q38" s="24" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="R38" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13136,13 +13136,13 @@
         <v>0.3333</v>
       </c>
       <c r="P39" s="26" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q39" s="24" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="R39" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13203,7 +13203,7 @@
         <v>227</v>
       </c>
       <c r="Q40" s="24" t="s">
-        <v>287</v>
+        <v>255</v>
       </c>
       <c r="R40" s="2" t="s">
         <v>310</v>
@@ -13360,7 +13360,7 @@
         <v>0</v>
       </c>
       <c r="P43" s="26" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q43" s="24" t="s">
         <v>319</v>
@@ -13429,7 +13429,7 @@
         <v>322</v>
       </c>
       <c r="R44" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13640,22 +13640,22 @@
       </c>
       <c r="F48" s="16" t="n">
         <f aca="false">IFERROR(INDEX('1099 Oct 30'!$H$5:$H$45,MATCH(B48,'1099 Oct 30'!$A$5:$A$45,0)),0)</f>
-        <v>0.75</v>
+        <v>2</v>
       </c>
       <c r="G48" s="15" t="n">
         <v>0</v>
       </c>
       <c r="H48" s="21" t="n">
         <f aca="false">F48+G48</f>
-        <v>0.75</v>
+        <v>2</v>
       </c>
       <c r="I48" s="2" t="n">
         <f aca="false">ROUND(H48*60,0)</f>
-        <v>45</v>
+        <v>120</v>
       </c>
       <c r="J48" s="2" t="n">
         <f aca="false">ROUND(F48*60,0)</f>
-        <v>45</v>
+        <v>120</v>
       </c>
       <c r="K48" s="2" t="n">
         <f aca="false">ROUND(G48*60,0)</f>
@@ -13666,11 +13666,11 @@
       </c>
       <c r="M48" s="22" t="n">
         <f aca="false">F48*IF(L48="CFO",Assumptions!$B$5,Assumptions!$B$4)+G48*Assumptions!$B$5</f>
-        <v>71.25</v>
+        <v>190</v>
       </c>
       <c r="N48" s="16" t="n">
         <f aca="false">F48*INDEX(Assumptions!$B$8:$B$14,MATCH(E48,Assumptions!$A$8:$A$14,0))</f>
-        <v>0.25</v>
+        <v>0.666666666666667</v>
       </c>
       <c r="O48" s="16" t="n">
         <f aca="false">G48*INDEX(Assumptions!$B$8:$B$14,MATCH(E48,Assumptions!$A$8:$A$14,0))</f>
@@ -13680,7 +13680,7 @@
         <v>227</v>
       </c>
       <c r="Q48" s="24" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="R48" s="2" t="s">
         <v>293</v>
@@ -13744,7 +13744,7 @@
         <v>227</v>
       </c>
       <c r="Q49" s="24" t="s">
-        <v>287</v>
+        <v>255</v>
       </c>
       <c r="R49" s="2" t="s">
         <v>235</v>
@@ -14263,22 +14263,22 @@
       </c>
       <c r="F62" s="16" t="n">
         <f aca="false">IFERROR(INDEX('1099 Oct 30'!$H$5:$H$45,MATCH(B62,'1099 Oct 30'!$A$5:$A$45,0)),0)</f>
-        <v>0.75</v>
+        <v>0.375</v>
       </c>
       <c r="G62" s="15" t="n">
         <v>0</v>
       </c>
       <c r="H62" s="21" t="n">
         <f aca="false">F62+G62</f>
-        <v>0.75</v>
+        <v>0.375</v>
       </c>
       <c r="I62" s="2" t="n">
         <f aca="false">ROUND(H62*60,0)</f>
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="J62" s="2" t="n">
         <f aca="false">ROUND(F62*60,0)</f>
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="K62" s="2" t="n">
         <f aca="false">ROUND(G62*60,0)</f>
@@ -14289,11 +14289,11 @@
       </c>
       <c r="M62" s="22" t="n">
         <f aca="false">F62*IF(L62="CFO",Assumptions!$B$5,Assumptions!$B$4)+G62*Assumptions!$B$5</f>
-        <v>71.25</v>
+        <v>35.625</v>
       </c>
       <c r="N62" s="16" t="n">
         <f aca="false">F62*INDEX(Assumptions!$B$8:$B$14,MATCH(E62,Assumptions!$A$8:$A$14,0))</f>
-        <v>0.25</v>
+        <v>0.125</v>
       </c>
       <c r="O62" s="16" t="n">
         <f aca="false">G62*INDEX(Assumptions!$B$8:$B$14,MATCH(E62,Assumptions!$A$8:$A$14,0))</f>
@@ -14303,10 +14303,10 @@
         <v>227</v>
       </c>
       <c r="Q62" s="24" t="s">
-        <v>287</v>
+        <v>259</v>
       </c>
       <c r="R62" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14363,13 +14363,13 @@
         <v>0.4167</v>
       </c>
       <c r="P63" s="26" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q63" s="24" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="R63" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14427,7 +14427,7 @@
         <v>0</v>
       </c>
       <c r="P64" s="27" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q64" s="24" t="s">
         <v>353</v>
@@ -14490,7 +14490,7 @@
         <v>0.25</v>
       </c>
       <c r="P65" s="27" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q65" s="24" t="s">
         <v>355</v>
@@ -14553,7 +14553,7 @@
         <v>0</v>
       </c>
       <c r="P66" s="27" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q66" s="24" t="s">
         <v>357</v>
@@ -14620,7 +14620,7 @@
         <v>227</v>
       </c>
       <c r="Q67" s="24" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="R67" s="2" t="s">
         <v>247</v>
@@ -14810,10 +14810,10 @@
         <v>227</v>
       </c>
       <c r="Q70" s="24" t="s">
-        <v>287</v>
+        <v>255</v>
       </c>
       <c r="R70" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14876,7 +14876,7 @@
         <v>364</v>
       </c>
       <c r="R71" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14937,7 +14937,7 @@
         <v>227</v>
       </c>
       <c r="Q72" s="24" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="R72" s="2" t="s">
         <v>229</v>
@@ -15067,7 +15067,7 @@
         <v>369</v>
       </c>
       <c r="R74" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15130,7 +15130,7 @@
         <v>372</v>
       </c>
       <c r="R75" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15193,7 +15193,7 @@
         <v>374</v>
       </c>
       <c r="R76" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15256,7 +15256,7 @@
         <v>377</v>
       </c>
       <c r="R77" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15317,7 +15317,7 @@
         <v>227</v>
       </c>
       <c r="Q78" s="24" t="s">
-        <v>287</v>
+        <v>255</v>
       </c>
       <c r="R78" s="2" t="s">
         <v>235</v>
@@ -15507,7 +15507,7 @@
         <v>227</v>
       </c>
       <c r="Q81" s="24" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="R81" s="2" t="s">
         <v>293</v>
@@ -15882,7 +15882,7 @@
         <v>0</v>
       </c>
       <c r="P87" s="26" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q87" s="24" t="s">
         <v>395</v>
@@ -15943,7 +15943,7 @@
         <v>0</v>
       </c>
       <c r="P88" s="26" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q88" s="24" t="s">
         <v>397</v>
@@ -16004,7 +16004,7 @@
         <v>0</v>
       </c>
       <c r="P89" s="26" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q89" s="24" t="s">
         <v>399</v>
@@ -16069,7 +16069,7 @@
         <v>227</v>
       </c>
       <c r="Q90" s="24" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="R90" s="2" t="s">
         <v>229</v>
@@ -16199,7 +16199,7 @@
         <v>404</v>
       </c>
       <c r="R92" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16262,7 +16262,7 @@
         <v>406</v>
       </c>
       <c r="R93" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16325,7 +16325,7 @@
         <v>408</v>
       </c>
       <c r="R94" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16388,7 +16388,7 @@
         <v>410</v>
       </c>
       <c r="R95" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16449,7 +16449,7 @@
         <v>227</v>
       </c>
       <c r="Q96" s="24" t="s">
-        <v>287</v>
+        <v>255</v>
       </c>
       <c r="R96" s="2" t="s">
         <v>247</v>
@@ -16639,10 +16639,10 @@
         <v>227</v>
       </c>
       <c r="Q99" s="24" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="R99" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16705,7 +16705,7 @@
         <v>418</v>
       </c>
       <c r="R100" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16766,7 +16766,7 @@
         <v>227</v>
       </c>
       <c r="Q101" s="24" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="R101" s="2" t="s">
         <v>235</v>
@@ -16853,22 +16853,22 @@
       </c>
       <c r="F103" s="16" t="n">
         <f aca="false">IFERROR(INDEX('1099 Oct 30'!$H$5:$H$45,MATCH(B103,'1099 Oct 30'!$A$5:$A$45,0)),0)</f>
-        <v>0.75</v>
+        <v>2</v>
       </c>
       <c r="G103" s="15" t="n">
         <v>0</v>
       </c>
       <c r="H103" s="21" t="n">
         <f aca="false">F103+G103</f>
-        <v>0.75</v>
+        <v>2</v>
       </c>
       <c r="I103" s="2" t="n">
         <f aca="false">ROUND(H103*60,0)</f>
-        <v>45</v>
+        <v>120</v>
       </c>
       <c r="J103" s="2" t="n">
         <f aca="false">ROUND(F103*60,0)</f>
-        <v>45</v>
+        <v>120</v>
       </c>
       <c r="K103" s="2" t="n">
         <f aca="false">ROUND(G103*60,0)</f>
@@ -16879,11 +16879,11 @@
       </c>
       <c r="M103" s="22" t="n">
         <f aca="false">F103*IF(L103="CFO",Assumptions!$B$5,Assumptions!$B$4)+G103*Assumptions!$B$5</f>
-        <v>71.25</v>
+        <v>190</v>
       </c>
       <c r="N103" s="16" t="n">
         <f aca="false">F103*INDEX(Assumptions!$B$8:$B$14,MATCH(E103,Assumptions!$A$8:$A$14,0))</f>
-        <v>0.25</v>
+        <v>0.666666666666667</v>
       </c>
       <c r="O103" s="16" t="n">
         <f aca="false">G103*INDEX(Assumptions!$B$8:$B$14,MATCH(E103,Assumptions!$A$8:$A$14,0))</f>
@@ -17043,22 +17043,22 @@
       </c>
       <c r="F106" s="16" t="n">
         <f aca="false">IFERROR(INDEX('1099 Oct 30'!$H$5:$H$45,MATCH(B106,'1099 Oct 30'!$A$5:$A$45,0)),0)</f>
-        <v>0.75</v>
+        <v>0.375</v>
       </c>
       <c r="G106" s="15" t="n">
         <v>0</v>
       </c>
       <c r="H106" s="21" t="n">
         <f aca="false">F106+G106</f>
-        <v>0.75</v>
+        <v>0.375</v>
       </c>
       <c r="I106" s="2" t="n">
         <f aca="false">ROUND(H106*60,0)</f>
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="J106" s="2" t="n">
         <f aca="false">ROUND(F106*60,0)</f>
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="K106" s="2" t="n">
         <f aca="false">ROUND(G106*60,0)</f>
@@ -17069,11 +17069,11 @@
       </c>
       <c r="M106" s="22" t="n">
         <f aca="false">F106*IF(L106="CFO",Assumptions!$B$5,Assumptions!$B$4)+G106*Assumptions!$B$5</f>
-        <v>71.25</v>
+        <v>35.625</v>
       </c>
       <c r="N106" s="16" t="n">
         <f aca="false">F106*INDEX(Assumptions!$B$8:$B$14,MATCH(E106,Assumptions!$A$8:$A$14,0))</f>
-        <v>0.25</v>
+        <v>0.125</v>
       </c>
       <c r="O106" s="16" t="n">
         <f aca="false">G106*INDEX(Assumptions!$B$8:$B$14,MATCH(E106,Assumptions!$A$8:$A$14,0))</f>
@@ -17210,7 +17210,7 @@
         <v>227</v>
       </c>
       <c r="Q108" s="24" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="R108" s="2" t="s">
         <v>229</v>
@@ -17270,10 +17270,10 @@
         <v>0.25</v>
       </c>
       <c r="P109" s="26" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q109" s="24" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="R109" s="2" t="s">
         <v>229</v>
@@ -17337,7 +17337,7 @@
         <v>227</v>
       </c>
       <c r="Q110" s="24" t="s">
-        <v>287</v>
+        <v>255</v>
       </c>
       <c r="R110" s="2" t="s">
         <v>229</v>
@@ -17716,7 +17716,7 @@
         <v>227</v>
       </c>
       <c r="Q116" s="24" t="s">
-        <v>287</v>
+        <v>255</v>
       </c>
       <c r="R116" s="2" t="s">
         <v>229</v>
@@ -17776,10 +17776,10 @@
         <v>0.5</v>
       </c>
       <c r="P117" s="26" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q117" s="24" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="R117" s="2" t="s">
         <v>229</v>
@@ -17840,7 +17840,7 @@
         <v>0</v>
       </c>
       <c r="P118" s="27" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q118" s="24" t="s">
         <v>448</v>
@@ -17903,7 +17903,7 @@
         <v>0.541666666666667</v>
       </c>
       <c r="P119" s="27" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q119" s="24" t="s">
         <v>450</v>
@@ -17966,7 +17966,7 @@
         <v>2.8333</v>
       </c>
       <c r="P120" s="27" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q120" s="24" t="s">
         <v>452</v>
@@ -18029,7 +18029,7 @@
         <v>0</v>
       </c>
       <c r="P121" s="27" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q121" s="24" t="s">
         <v>454</v>
@@ -18092,7 +18092,7 @@
         <v>1.08333333333333</v>
       </c>
       <c r="P122" s="27" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q122" s="24" t="s">
         <v>456</v>
@@ -18155,7 +18155,7 @@
         <v>0</v>
       </c>
       <c r="P123" s="27" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q123" s="24" t="s">
         <v>458</v>
@@ -18222,7 +18222,7 @@
         <v>227</v>
       </c>
       <c r="Q124" s="24" t="s">
-        <v>287</v>
+        <v>255</v>
       </c>
       <c r="R124" s="2" t="s">
         <v>235</v>
@@ -19111,7 +19111,7 @@
         <v>Includes Month-end 1.3.</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19141,22 +19141,22 @@
       </c>
       <c r="I15" s="16" t="n">
         <f aca="false">INDEX('1099 Oct 30'!$F$5:$F$45,MATCH(P15,'1099 Oct 30'!$A$5:$A$45,0))</f>
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J15" s="15" t="n">
         <v>0</v>
       </c>
       <c r="K15" s="21" t="n">
         <f aca="false">I15+J15</f>
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="L15" s="2" t="n">
         <f aca="false">ROUND(K15*60,0)</f>
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="M15" s="22" t="n">
         <f aca="false">I15*Assumptions!$B$4</f>
-        <v>237.5</v>
+        <v>142.5</v>
       </c>
       <c r="N15" s="23" t="s">
         <v>227</v>
@@ -19222,7 +19222,7 @@
         <v>Josephine's Apr–May 2026 closes + allowance for a new person (Valentina's hours not used).</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19333,7 +19333,7 @@
         <v>Josephine's Apr–May 2026 closes + allowance for a new person (Valentina's hours not used). Will become an Airbnb – provisional. Revisit once it converts.</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19588,22 +19588,22 @@
       </c>
       <c r="I23" s="16" t="n">
         <f aca="false">INDEX('1099 Oct 30'!$F$5:$F$45,MATCH(P23,'1099 Oct 30'!$A$5:$A$45,0))</f>
-        <v>2</v>
+        <v>0.75</v>
       </c>
       <c r="J23" s="15" t="n">
         <v>0</v>
       </c>
       <c r="K23" s="21" t="n">
         <f aca="false">I23+J23</f>
-        <v>2</v>
+        <v>0.75</v>
       </c>
       <c r="L23" s="2" t="n">
         <f aca="false">ROUND(K23*60,0)</f>
-        <v>120</v>
+        <v>45</v>
       </c>
       <c r="M23" s="22" t="n">
         <f aca="false">I23*Assumptions!$B$4</f>
-        <v>190</v>
+        <v>71.25</v>
       </c>
       <c r="N23" s="23" t="s">
         <v>227</v>
@@ -19726,7 +19726,7 @@
         <v>Includes Month-end 0.7, Payroll 0.4.</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19783,7 +19783,7 @@
         <v>Includes Month-end 0.7, Payroll 0.4.</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19894,7 +19894,7 @@
         <v>Includes Month-end 2.6, Bookkeeping 0.9.</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19951,7 +19951,7 @@
         <v>Year-end/tax hours Oct 2025–Sep 2026 (0.5h).</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20746,22 +20746,22 @@
       </c>
       <c r="I44" s="16" t="n">
         <f aca="false">INDEX('1099 Oct 30'!$F$5:$F$45,MATCH(P44,'1099 Oct 30'!$A$5:$A$45,0))</f>
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="J44" s="15" t="n">
         <v>0</v>
       </c>
       <c r="K44" s="21" t="n">
         <f aca="false">I44+J44</f>
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="L44" s="2" t="n">
         <f aca="false">ROUND(K44*60,0)</f>
-        <v>90</v>
+        <v>240</v>
       </c>
       <c r="M44" s="22" t="n">
         <f aca="false">I44*Assumptions!$B$4</f>
-        <v>142.5</v>
+        <v>380</v>
       </c>
       <c r="N44" s="23" t="s">
         <v>227</v>
@@ -20908,22 +20908,22 @@
       </c>
       <c r="I47" s="16" t="n">
         <f aca="false">INDEX('1099 Oct 30'!$F$5:$F$45,MATCH(P47,'1099 Oct 30'!$A$5:$A$45,0))</f>
-        <v>2</v>
+        <v>0.75</v>
       </c>
       <c r="J47" s="15" t="n">
         <v>0</v>
       </c>
       <c r="K47" s="21" t="n">
         <f aca="false">I47+J47</f>
-        <v>2</v>
+        <v>0.75</v>
       </c>
       <c r="L47" s="2" t="n">
         <f aca="false">ROUND(K47*60,0)</f>
-        <v>120</v>
+        <v>45</v>
       </c>
       <c r="M47" s="22" t="n">
         <f aca="false">I47*Assumptions!$B$4</f>
-        <v>190</v>
+        <v>71.25</v>
       </c>
       <c r="N47" s="23" t="s">
         <v>227</v>
@@ -21939,22 +21939,22 @@
       </c>
       <c r="I66" s="16" t="n">
         <f aca="false">INDEX('1099 Oct 30'!$F$5:$F$45,MATCH(P66,'1099 Oct 30'!$A$5:$A$45,0))</f>
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="J66" s="15" t="n">
         <v>0</v>
       </c>
       <c r="K66" s="21" t="n">
         <f aca="false">I66+J66</f>
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="L66" s="2" t="n">
         <f aca="false">ROUND(K66*60,0)</f>
-        <v>90</v>
+        <v>240</v>
       </c>
       <c r="M66" s="22" t="n">
         <f aca="false">I66*Assumptions!$B$4</f>
-        <v>142.5</v>
+        <v>380</v>
       </c>
       <c r="N66" s="23" t="s">
         <v>227</v>
@@ -22883,22 +22883,22 @@
       </c>
       <c r="I88" s="16" t="n">
         <f aca="false">INDEX('1099 Oct 30'!$F$5:$F$45,MATCH(P88,'1099 Oct 30'!$A$5:$A$45,0))</f>
-        <v>0.75</v>
+        <v>0.375</v>
       </c>
       <c r="J88" s="15" t="n">
         <v>0</v>
       </c>
       <c r="K88" s="21" t="n">
         <f aca="false">I88+J88</f>
-        <v>0.75</v>
+        <v>0.375</v>
       </c>
       <c r="L88" s="2" t="n">
         <f aca="false">ROUND(K88*60,0)</f>
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="M88" s="22" t="n">
         <f aca="false">I88*Assumptions!$B$4</f>
-        <v>71.25</v>
+        <v>35.625</v>
       </c>
       <c r="N88" s="23" t="s">
         <v>227</v>
@@ -26693,22 +26693,22 @@
       </c>
       <c r="I157" s="16" t="n">
         <f aca="false">INDEX('1099 Oct 30'!$F$5:$F$45,MATCH(P157,'1099 Oct 30'!$A$5:$A$45,0))</f>
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="J157" s="15" t="n">
         <v>0</v>
       </c>
       <c r="K157" s="21" t="n">
         <f aca="false">I157+J157</f>
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="L157" s="2" t="n">
         <f aca="false">ROUND(K157*60,0)</f>
-        <v>90</v>
+        <v>240</v>
       </c>
       <c r="M157" s="22" t="n">
         <f aca="false">I157*Assumptions!$B$4</f>
-        <v>142.5</v>
+        <v>380</v>
       </c>
       <c r="N157" s="23" t="s">
         <v>227</v>
@@ -26861,22 +26861,22 @@
       </c>
       <c r="I160" s="16" t="n">
         <f aca="false">INDEX('1099 Oct 30'!$F$5:$F$45,MATCH(P160,'1099 Oct 30'!$A$5:$A$45,0))</f>
-        <v>1.125</v>
+        <v>0.5625</v>
       </c>
       <c r="J160" s="15" t="n">
         <v>0</v>
       </c>
       <c r="K160" s="21" t="n">
         <f aca="false">I160+J160</f>
-        <v>1.125</v>
+        <v>0.5625</v>
       </c>
       <c r="L160" s="2" t="n">
         <f aca="false">ROUND(K160*60,0)</f>
-        <v>68</v>
+        <v>34</v>
       </c>
       <c r="M160" s="22" t="n">
         <f aca="false">I160*Assumptions!$B$4</f>
-        <v>106.875</v>
+        <v>53.4375</v>
       </c>
       <c r="N160" s="23" t="s">
         <v>227</v>
@@ -28254,7 +28254,7 @@
       <c r="H186" s="2"/>
       <c r="I186" s="4" t="n">
         <f aca="false">SUM(I2:I184)</f>
-        <v>537.8333</v>
+        <v>540.8958</v>
       </c>
       <c r="J186" s="4" t="n">
         <f aca="false">SUM(J2:J184)</f>
@@ -28262,15 +28262,15 @@
       </c>
       <c r="K186" s="4" t="n">
         <f aca="false">SUM(K2:K184)</f>
-        <v>593.8333</v>
+        <v>596.8958</v>
       </c>
       <c r="L186" s="4" t="n">
         <f aca="false">SUM(L2:L184)</f>
-        <v>35634</v>
+        <v>35818</v>
       </c>
       <c r="M186" s="32" t="n">
         <f aca="false">SUM(M2:M184)</f>
-        <v>72314.606</v>
+        <v>72605.5435</v>
       </c>
       <c r="N186" s="2"/>
       <c r="O186" s="2"/>
@@ -28452,7 +28452,7 @@
       </c>
       <c r="B9" s="34" t="n">
         <f aca="false">SUMIFS('Recurring Budgets'!$N$2:$N$125,'Recurring Budgets'!$B$2:$B$125,A9)</f>
-        <v>1.66666666666667</v>
+        <v>1.5</v>
       </c>
       <c r="C9" s="34" t="n">
         <f aca="false">SUMIFS('Recurring Budgets'!$O$2:$O$125,'Recurring Budgets'!$B$2:$B$125,A9)</f>
@@ -28460,7 +28460,7 @@
       </c>
       <c r="D9" s="35" t="n">
         <f aca="false">B9+C9</f>
-        <v>2.24996666666667</v>
+        <v>2.0833</v>
       </c>
       <c r="E9" s="25" t="s">
         <v>232</v>
@@ -28484,7 +28484,7 @@
         <v>1.125</v>
       </c>
       <c r="E10" s="26" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F10" s="2"/>
     </row>
@@ -28505,7 +28505,7 @@
         <v>1.7083</v>
       </c>
       <c r="E11" s="27" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>549</v>
@@ -28517,7 +28517,7 @@
       </c>
       <c r="B12" s="34" t="n">
         <f aca="false">SUMIFS('Recurring Budgets'!$N$2:$N$125,'Recurring Budgets'!$B$2:$B$125,A12)</f>
-        <v>25.9164916666667</v>
+        <v>25.499825</v>
       </c>
       <c r="C12" s="34" t="n">
         <f aca="false">SUMIFS('Recurring Budgets'!$O$2:$O$125,'Recurring Budgets'!$B$2:$B$125,A12)</f>
@@ -28525,7 +28525,7 @@
       </c>
       <c r="D12" s="35" t="n">
         <f aca="false">B12+C12</f>
-        <v>26.2497916666667</v>
+        <v>25.833125</v>
       </c>
       <c r="E12" s="25" t="s">
         <v>232</v>
@@ -28643,7 +28643,7 @@
       </c>
       <c r="B18" s="34" t="n">
         <f aca="false">SUMIFS('Recurring Budgets'!$N$2:$N$125,'Recurring Budgets'!$B$2:$B$125,A18)</f>
-        <v>2.6667</v>
+        <v>3.08336666666667</v>
       </c>
       <c r="C18" s="34" t="n">
         <f aca="false">SUMIFS('Recurring Budgets'!$O$2:$O$125,'Recurring Budgets'!$B$2:$B$125,A18)</f>
@@ -28651,7 +28651,7 @@
       </c>
       <c r="D18" s="35" t="n">
         <f aca="false">B18+C18</f>
-        <v>3.5</v>
+        <v>3.91666666666667</v>
       </c>
       <c r="E18" s="25" t="s">
         <v>232</v>
@@ -28664,7 +28664,7 @@
       </c>
       <c r="B19" s="34" t="n">
         <f aca="false">SUMIFS('Recurring Budgets'!$N$2:$N$125,'Recurring Budgets'!$B$2:$B$125,A19)</f>
-        <v>7.74996666666667</v>
+        <v>7.3333</v>
       </c>
       <c r="C19" s="34" t="n">
         <f aca="false">SUMIFS('Recurring Budgets'!$O$2:$O$125,'Recurring Budgets'!$B$2:$B$125,A19)</f>
@@ -28672,7 +28672,7 @@
       </c>
       <c r="D19" s="35" t="n">
         <f aca="false">B19+C19</f>
-        <v>9.49996666666667</v>
+        <v>9.0833</v>
       </c>
       <c r="E19" s="25" t="s">
         <v>232</v>
@@ -28719,7 +28719,7 @@
         <v>1.2083</v>
       </c>
       <c r="E21" s="26" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F21" s="2"/>
     </row>
@@ -28784,7 +28784,7 @@
         <v>7.5</v>
       </c>
       <c r="E24" s="26" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>551</v>
@@ -28819,7 +28819,7 @@
       </c>
       <c r="B26" s="34" t="n">
         <f aca="false">SUMIFS('Recurring Budgets'!$N$2:$N$125,'Recurring Budgets'!$B$2:$B$125,A26)</f>
-        <v>0.25</v>
+        <v>0.666666666666667</v>
       </c>
       <c r="C26" s="34" t="n">
         <f aca="false">SUMIFS('Recurring Budgets'!$O$2:$O$125,'Recurring Budgets'!$B$2:$B$125,A26)</f>
@@ -28827,7 +28827,7 @@
       </c>
       <c r="D26" s="35" t="n">
         <f aca="false">B26+C26</f>
-        <v>0.25</v>
+        <v>0.666666666666667</v>
       </c>
       <c r="E26" s="23" t="s">
         <v>227</v>
@@ -28884,7 +28884,7 @@
       </c>
       <c r="B29" s="34" t="n">
         <f aca="false">SUMIFS('Recurring Budgets'!$N$2:$N$125,'Recurring Budgets'!$B$2:$B$125,A29)</f>
-        <v>0.75</v>
+        <v>0.625</v>
       </c>
       <c r="C29" s="34" t="n">
         <f aca="false">SUMIFS('Recurring Budgets'!$O$2:$O$125,'Recurring Budgets'!$B$2:$B$125,A29)</f>
@@ -28892,10 +28892,10 @@
       </c>
       <c r="D29" s="35" t="n">
         <f aca="false">B29+C29</f>
-        <v>1.1667</v>
+        <v>1.0417</v>
       </c>
       <c r="E29" s="26" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F29" s="2"/>
     </row>
@@ -28916,7 +28916,7 @@
         <v>3.125</v>
       </c>
       <c r="E30" s="27" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>553</v>
@@ -29088,7 +29088,7 @@
         <v>8.311775</v>
       </c>
       <c r="E38" s="26" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F38" s="2"/>
     </row>
@@ -29205,7 +29205,7 @@
       </c>
       <c r="B44" s="34" t="n">
         <f aca="false">SUMIFS('Recurring Budgets'!$N$2:$N$125,'Recurring Budgets'!$B$2:$B$125,A44)</f>
-        <v>2.125</v>
+        <v>2.54166666666667</v>
       </c>
       <c r="C44" s="34" t="n">
         <f aca="false">SUMIFS('Recurring Budgets'!$O$2:$O$125,'Recurring Budgets'!$B$2:$B$125,A44)</f>
@@ -29213,7 +29213,7 @@
       </c>
       <c r="D44" s="35" t="n">
         <f aca="false">B44+C44</f>
-        <v>2.125</v>
+        <v>2.54166666666667</v>
       </c>
       <c r="E44" s="28" t="s">
         <v>376</v>
@@ -29228,7 +29228,7 @@
       </c>
       <c r="B45" s="34" t="n">
         <f aca="false">SUMIFS('Recurring Budgets'!$N$2:$N$125,'Recurring Budgets'!$B$2:$B$125,A45)</f>
-        <v>1.5833</v>
+        <v>1.4583</v>
       </c>
       <c r="C45" s="34" t="n">
         <f aca="false">SUMIFS('Recurring Budgets'!$O$2:$O$125,'Recurring Budgets'!$B$2:$B$125,A45)</f>
@@ -29236,7 +29236,7 @@
       </c>
       <c r="D45" s="35" t="n">
         <f aca="false">B45+C45</f>
-        <v>2.3333</v>
+        <v>2.2083</v>
       </c>
       <c r="E45" s="28" t="s">
         <v>312</v>
@@ -29262,7 +29262,7 @@
         <v>1.125</v>
       </c>
       <c r="E46" s="26" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F46" s="2"/>
     </row>
@@ -29304,7 +29304,7 @@
         <v>1.25</v>
       </c>
       <c r="E48" s="26" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F48" s="2"/>
     </row>
@@ -29325,7 +29325,7 @@
         <v>27</v>
       </c>
       <c r="E49" s="27" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>557</v>
@@ -29798,7 +29798,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B20" s="9" t="n">
         <v>5.5</v>
@@ -30592,7 +30592,7 @@
         <v>0.75</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30951,7 +30951,7 @@
         <v>4.75</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31052,7 +31052,7 @@
         <v>2.5</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31575,7 +31575,7 @@
         <v>12.2</v>
       </c>
       <c r="O49" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31803,7 +31803,7 @@
         <v>17.6</v>
       </c>
       <c r="O55" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31920,7 +31920,7 @@
         <v>1</v>
       </c>
       <c r="O58" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32144,7 +32144,7 @@
         <v>7.25</v>
       </c>
       <c r="O64" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32776,7 +32776,7 @@
         <v>1</v>
       </c>
       <c r="O82" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32869,7 +32869,7 @@
       <c r="M85" s="36"/>
       <c r="N85" s="36"/>
       <c r="O85" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33269,7 +33269,7 @@
       </c>
       <c r="N97" s="36"/>
       <c r="O97" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33497,7 +33497,7 @@
         <v>50.85</v>
       </c>
       <c r="O103" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34052,7 +34052,7 @@
         <v>3.3</v>
       </c>
       <c r="O118" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34280,7 +34280,7 @@
         <v>7</v>
       </c>
       <c r="O124" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/budget-hours/Karbon_Budget_Hours_2026-10.xlsx
+++ b/budget-hours/Karbon_Budget_Hours_2026-10.xlsx
@@ -749,7 +749,7 @@
     <t xml:space="preserve">Accounting</t>
   </si>
   <si>
-    <t xml:space="preserve">Includes Month-end 0.5. Review = 1.25h (only 2 reviewed close(s) in Harvest; 0.7h standard applied as minimum).</t>
+    <t xml:space="preserve">Includes Month-end 0.5. Review = 1.25h as logged (only 2 reviewed close(s) in Harvest – check).</t>
   </si>
   <si>
     <t xml:space="preserve">15650 Northsight LLC|Sales tax|Quarterly Sales Tax Filing - Onyx Prepares the Returns for Client|Quarterly</t>
@@ -893,7 +893,7 @@
     <t xml:space="preserve">Barrett Living Trust|Accounting|Month End Close|Monthly</t>
   </si>
   <si>
-    <t xml:space="preserve">Includes Month-end 2.6, Bookkeeping 0.9. Review = 1.10h (only 2 reviewed close(s) in Harvest; 0.7h standard applied as minimum).</t>
+    <t xml:space="preserve">Includes Month-end 2.6, Bookkeeping 0.9. Review = 1.10h as logged (only 2 reviewed close(s) in Harvest – check).</t>
   </si>
   <si>
     <t xml:space="preserve">BeckShar Development LLC|1099|1099 Quarterly Review|1099</t>
@@ -923,7 +923,7 @@
     <t xml:space="preserve">BeckShar LLC|Monthly Financials|Month End Close|Monthly</t>
   </si>
   <si>
-    <t xml:space="preserve">Includes Month-end 1.2, Bookkeeping 0.5, Payroll 1.3, Sales tax 0.8. Review = 1.25h (only 2 reviewed close(s) in Harvest; 0.7h standard applied as minimum).</t>
+    <t xml:space="preserve">Includes Month-end 1.2, Bookkeeping 0.5, Payroll 1.3, Sales tax 0.8. Review = 1.25h as logged (only 2 reviewed close(s) in Harvest – check).</t>
   </si>
   <si>
     <t xml:space="preserve">Building and Development Professionals LLC|1099|1099 Quarterly Review|1099</t>
@@ -932,7 +932,7 @@
     <t xml:space="preserve">Building and Development Professionals LLC|Monthly Financials|Month End Close|Monthly</t>
   </si>
   <si>
-    <t xml:space="preserve">Includes Month-end 0.5, CFO advisory 1.9. Review = 0.7h standard (no close reviews found in Harvest).</t>
+    <t xml:space="preserve">Includes Month-end 0.5, CFO advisory 1.9. Review = 0.5h placeholder (no close reviews found in Harvest) – check.</t>
   </si>
   <si>
     <t xml:space="preserve">Capital Financial LLC|1099|1099 Quarterly Review|1099</t>
@@ -1049,7 +1049,7 @@
     <t xml:space="preserve">GAV Enterprises Inc|Accounting|Quarter End Close|Quarterly</t>
   </si>
   <si>
-    <t xml:space="preserve">Includes Month-end 10.4, Bookkeeping 7.8, CFO advisory 0.7. Review = 0.70h (only 1 reviewed close(s) in Harvest; 0.7h standard applied as minimum).</t>
+    <t xml:space="preserve">Includes Month-end 10.4, Bookkeeping 7.8, CFO advisory 0.7. Review = 0.25h as logged (only 1 reviewed close(s) in Harvest – check).</t>
   </si>
   <si>
     <t xml:space="preserve">International Alliance Group LLC|1099|1099 Quarterly Review|1099</t>
@@ -1172,7 +1172,7 @@
     <t xml:space="preserve">Low</t>
   </si>
   <si>
-    <t xml:space="preserve">SUGGESTED – no recurring month-end item in the Oct list (only the July clean-up). Payroll takeover in progress (Paychex/401k/PFML); tax audit budgeted separately. Confirm payroll is ongoing. Review = 0.70h (only 1 reviewed close(s) in Harvest; 0.7h standard applied as minimum).</t>
+    <t xml:space="preserve">SUGGESTED – no recurring month-end item in the Oct list (only the July clean-up). Payroll takeover in progress (Paychex/401k/PFML); tax audit budgeted separately. Confirm payroll is ongoing. Review = 0.25h as logged (only 1 reviewed close(s) in Harvest – check).</t>
   </si>
   <si>
     <t xml:space="preserve">Newport Classic Cars LLC|1099|1099 Quarterly Review|1099</t>
@@ -1220,7 +1220,7 @@
     <t xml:space="preserve">Paradise Village LLC|Accounting|Quarter End Close|Quarterly</t>
   </si>
   <si>
-    <t xml:space="preserve">Includes Month-end 1.0. Review = 1.00h (only 2 reviewed close(s) in Harvest; 0.7h standard applied as minimum).</t>
+    <t xml:space="preserve">Includes Month-end 1.0. Review = 1.00h as logged (only 2 reviewed close(s) in Harvest – check).</t>
   </si>
   <si>
     <t xml:space="preserve">Phil Tavasci Companies|Bookkeeping|Daily Chase Fraud Review|Daily</t>
@@ -1265,7 +1265,7 @@
     <t xml:space="preserve">Prestige Arms Worldwide|Monthly Financials|Month End Close|Monthly</t>
   </si>
   <si>
-    <t xml:space="preserve">Little recent history (backlog not yet worked). Close set at 1.0h from 2025 pattern, adjusted for contractor under-recording. Review = 0.7h standard (no close reviews found in Harvest).</t>
+    <t xml:space="preserve">Little recent history (backlog not yet worked). Close set at 1.0h from 2025 pattern, adjusted for contractor under-recording. Review = 0.5h placeholder (no close reviews found in Harvest) – check.</t>
   </si>
   <si>
     <t xml:space="preserve">Prestige Arms Worldwide|Sales tax|Sales Tax Filing - Onyx Prepares the Returns for Client|Monthly</t>
@@ -1322,7 +1322,7 @@
     <t xml:space="preserve">Southwest Rents Inc|Monthly Financials|Month End Close|Monthly</t>
   </si>
   <si>
-    <t xml:space="preserve">Includes Month-end 0.2, Bookkeeping 0.5, Sales tax 0.2, CFO advisory 0.6. Catch-up still underway; steady level uncertain. Backlog closes carry the remaining catch-up (~15–20h). Review = 0.7h standard (no close reviews found in Harvest).</t>
+    <t xml:space="preserve">Includes Month-end 0.2, Bookkeeping 0.5, Sales tax 0.2, CFO advisory 0.6. Catch-up still underway; steady level uncertain. Backlog closes carry the remaining catch-up (~15–20h). Review = 0.5h placeholder (no close reviews found in Harvest) – check.</t>
   </si>
   <si>
     <t xml:space="preserve">T5 Family Holdings LLC|1099|1099 Quarterly Review|1099</t>
@@ -1427,7 +1427,7 @@
     <t xml:space="preserve">Young Wealth Management PLLC|Accounting|Quarter End Close|Quarterly</t>
   </si>
   <si>
-    <t xml:space="preserve">Includes Month-end 6.5, Payroll 1.2. Review = 0.70h (only 1 reviewed close(s) in Harvest; 0.7h standard applied as minimum).</t>
+    <t xml:space="preserve">Includes Month-end 6.5, Payroll 1.2. Review = 0.35h as logged (only 1 reviewed close(s) in Harvest – check).</t>
   </si>
   <si>
     <t xml:space="preserve">Work Title</t>
@@ -3771,19 +3771,19 @@
       </c>
       <c r="D37" s="6" t="n">
         <f aca="false">ROUND('Recurring Budgets'!F33*60,0)/1440</f>
-        <v>0.107638888888889</v>
+        <v>0.114583333333333</v>
       </c>
       <c r="E37" s="7" t="n">
         <f aca="false">ROUND('Recurring Budgets'!F33*IF(H37="CFO",Assumptions!$B$5,Assumptions!$B$4),0)</f>
-        <v>646</v>
+        <v>688</v>
       </c>
       <c r="F37" s="6" t="n">
         <f aca="false">ROUND('Recurring Budgets'!G33*60,0)/1440</f>
-        <v>0.0291666666666667</v>
+        <v>0.0208333333333333</v>
       </c>
       <c r="G37" s="7" t="n">
         <f aca="false">ROUND('Recurring Budgets'!G33*Assumptions!$B$5,0)</f>
-        <v>175</v>
+        <v>125</v>
       </c>
       <c r="H37" s="8" t="str">
         <f aca="false">'Recurring Budgets'!L33</f>
@@ -4329,19 +4329,19 @@
       </c>
       <c r="D55" s="6" t="n">
         <f aca="false">ROUND('Recurring Budgets'!F52*60,0)/1440</f>
-        <v>0.756944444444444</v>
+        <v>0.774305555555556</v>
       </c>
       <c r="E55" s="7" t="n">
         <f aca="false">ROUND('Recurring Budgets'!F52*IF(H55="CFO",Assumptions!$B$5,Assumptions!$B$4),0)</f>
-        <v>1726</v>
+        <v>1765</v>
       </c>
       <c r="F55" s="6" t="n">
         <f aca="false">ROUND('Recurring Budgets'!G52*60,0)/1440</f>
-        <v>0.0291666666666667</v>
+        <v>0.0104166666666667</v>
       </c>
       <c r="G55" s="7" t="n">
         <f aca="false">ROUND('Recurring Budgets'!G52*Assumptions!$B$5,0)</f>
-        <v>175</v>
+        <v>63</v>
       </c>
       <c r="H55" s="8" t="str">
         <f aca="false">'Recurring Budgets'!L52</f>
@@ -4825,19 +4825,19 @@
       </c>
       <c r="D71" s="6" t="n">
         <f aca="false">ROUND('Recurring Budgets'!F77*60,0)/1440</f>
-        <v>0.177083333333333</v>
+        <v>0.194444444444444</v>
       </c>
       <c r="E71" s="7" t="n">
         <f aca="false">ROUND('Recurring Budgets'!F77*IF(H71="CFO",Assumptions!$B$5,Assumptions!$B$4),0)</f>
-        <v>404</v>
+        <v>443</v>
       </c>
       <c r="F71" s="6" t="n">
         <f aca="false">ROUND('Recurring Budgets'!G77*60,0)/1440</f>
-        <v>0.0291666666666667</v>
+        <v>0.0104166666666667</v>
       </c>
       <c r="G71" s="7" t="n">
         <f aca="false">ROUND('Recurring Budgets'!G77*Assumptions!$B$5,0)</f>
-        <v>175</v>
+        <v>63</v>
       </c>
       <c r="H71" s="8" t="str">
         <f aca="false">'Recurring Budgets'!L77</f>
@@ -5360,11 +5360,11 @@
       </c>
       <c r="F88" s="6" t="n">
         <f aca="false">ROUND('Recurring Budgets'!G94*60,0)/1440</f>
-        <v>0.0291666666666667</v>
+        <v>0.0208333333333333</v>
       </c>
       <c r="G88" s="7" t="n">
         <f aca="false">ROUND('Recurring Budgets'!G94*Assumptions!$B$5,0)</f>
-        <v>175</v>
+        <v>125</v>
       </c>
       <c r="H88" s="8" t="str">
         <f aca="false">'Recurring Budgets'!L94</f>
@@ -5662,19 +5662,19 @@
       </c>
       <c r="D98" s="6" t="n">
         <f aca="false">ROUND('Recurring Budgets'!F105*60,0)/1440</f>
-        <v>0.0347222222222222</v>
+        <v>0.0416666666666667</v>
       </c>
       <c r="E98" s="7" t="n">
         <f aca="false">ROUND('Recurring Budgets'!F105*IF(H98="CFO",Assumptions!$B$5,Assumptions!$B$4),0)</f>
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="F98" s="6" t="n">
         <f aca="false">ROUND('Recurring Budgets'!G105*60,0)/1440</f>
-        <v>0.0291666666666667</v>
+        <v>0.0208333333333333</v>
       </c>
       <c r="G98" s="7" t="n">
         <f aca="false">ROUND('Recurring Budgets'!G105*Assumptions!$B$5,0)</f>
-        <v>175</v>
+        <v>125</v>
       </c>
       <c r="H98" s="8" t="str">
         <f aca="false">'Recurring Budgets'!L105</f>
@@ -6282,19 +6282,19 @@
       </c>
       <c r="D118" s="6" t="n">
         <f aca="false">ROUND('Recurring Budgets'!F125*60,0)/1440</f>
-        <v>0.302083333333333</v>
+        <v>0.315972222222222</v>
       </c>
       <c r="E118" s="7" t="n">
         <f aca="false">ROUND('Recurring Budgets'!F125*IF(H118="CFO",Assumptions!$B$5,Assumptions!$B$4),0)</f>
-        <v>689</v>
+        <v>720</v>
       </c>
       <c r="F118" s="6" t="n">
         <f aca="false">ROUND('Recurring Budgets'!G125*60,0)/1440</f>
-        <v>0.0291666666666667</v>
+        <v>0.0145833333333333</v>
       </c>
       <c r="G118" s="7" t="n">
         <f aca="false">ROUND('Recurring Budgets'!G125*Assumptions!$B$5,0)</f>
-        <v>175</v>
+        <v>88</v>
       </c>
       <c r="H118" s="8" t="str">
         <f aca="false">'Recurring Budgets'!L125</f>
@@ -12636,41 +12636,41 @@
         <v>15</v>
       </c>
       <c r="F33" s="15" t="n">
-        <v>2.5833</v>
+        <v>2.75</v>
       </c>
       <c r="G33" s="15" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="H33" s="21" t="n">
         <f aca="false">F33+G33</f>
-        <v>3.2833</v>
+        <v>3.25</v>
       </c>
       <c r="I33" s="2" t="n">
         <f aca="false">ROUND(H33*60,0)</f>
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="J33" s="2" t="n">
         <f aca="false">ROUND(F33*60,0)</f>
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="K33" s="2" t="n">
         <f aca="false">ROUND(G33*60,0)</f>
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="L33" s="9" t="s">
         <v>185</v>
       </c>
       <c r="M33" s="22" t="n">
         <f aca="false">F33*IF(L33="CFO",Assumptions!$B$5,Assumptions!$B$4)+G33*Assumptions!$B$5</f>
-        <v>820.825</v>
+        <v>812.5</v>
       </c>
       <c r="N33" s="16" t="n">
         <f aca="false">F33*INDEX(Assumptions!$B$8:$B$14,MATCH(E33,Assumptions!$A$8:$A$14,0))</f>
-        <v>2.5833</v>
+        <v>2.75</v>
       </c>
       <c r="O33" s="16" t="n">
         <f aca="false">G33*INDEX(Assumptions!$B$8:$B$14,MATCH(E33,Assumptions!$A$8:$A$14,0))</f>
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="P33" s="25" t="s">
         <v>232</v>
@@ -13811,41 +13811,41 @@
         <v>13</v>
       </c>
       <c r="F52" s="15" t="n">
-        <v>18.1667</v>
+        <v>18.5833</v>
       </c>
       <c r="G52" s="15" t="n">
-        <v>0.7</v>
+        <v>0.25</v>
       </c>
       <c r="H52" s="21" t="n">
         <f aca="false">F52+G52</f>
-        <v>18.8667</v>
+        <v>18.8333</v>
       </c>
       <c r="I52" s="2" t="n">
         <f aca="false">ROUND(H52*60,0)</f>
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="J52" s="2" t="n">
         <f aca="false">ROUND(F52*60,0)</f>
-        <v>1090</v>
+        <v>1115</v>
       </c>
       <c r="K52" s="2" t="n">
         <f aca="false">ROUND(G52*60,0)</f>
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="L52" s="9" t="s">
         <v>87</v>
       </c>
       <c r="M52" s="22" t="n">
         <f aca="false">F52*IF(L52="CFO",Assumptions!$B$5,Assumptions!$B$4)+G52*Assumptions!$B$5</f>
-        <v>1900.8365</v>
+        <v>1827.9135</v>
       </c>
       <c r="N52" s="16" t="n">
         <f aca="false">F52*INDEX(Assumptions!$B$8:$B$14,MATCH(E52,Assumptions!$A$8:$A$14,0))</f>
-        <v>6.05556666666667</v>
+        <v>6.19443333333333</v>
       </c>
       <c r="O52" s="16" t="n">
         <f aca="false">G52*INDEX(Assumptions!$B$8:$B$14,MATCH(E52,Assumptions!$A$8:$A$14,0))</f>
-        <v>0.233333333333333</v>
+        <v>0.0833333333333333</v>
       </c>
       <c r="P52" s="25" t="s">
         <v>232</v>
@@ -15131,41 +15131,41 @@
         <v>15</v>
       </c>
       <c r="F77" s="15" t="n">
-        <v>4.25</v>
+        <v>4.6667</v>
       </c>
       <c r="G77" s="15" t="n">
-        <v>0.7</v>
+        <v>0.25</v>
       </c>
       <c r="H77" s="21" t="n">
         <f aca="false">F77+G77</f>
-        <v>4.95</v>
+        <v>4.9167</v>
       </c>
       <c r="I77" s="2" t="n">
         <f aca="false">ROUND(H77*60,0)</f>
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="J77" s="2" t="n">
         <f aca="false">ROUND(F77*60,0)</f>
-        <v>255</v>
+        <v>280</v>
       </c>
       <c r="K77" s="2" t="n">
         <f aca="false">ROUND(G77*60,0)</f>
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="L77" s="9" t="s">
         <v>87</v>
       </c>
       <c r="M77" s="22" t="n">
         <f aca="false">F77*IF(L77="CFO",Assumptions!$B$5,Assumptions!$B$4)+G77*Assumptions!$B$5</f>
-        <v>578.75</v>
+        <v>505.8365</v>
       </c>
       <c r="N77" s="16" t="n">
         <f aca="false">F77*INDEX(Assumptions!$B$8:$B$14,MATCH(E77,Assumptions!$A$8:$A$14,0))</f>
-        <v>4.25</v>
+        <v>4.6667</v>
       </c>
       <c r="O77" s="16" t="n">
         <f aca="false">G77*INDEX(Assumptions!$B$8:$B$14,MATCH(E77,Assumptions!$A$8:$A$14,0))</f>
-        <v>0.7</v>
+        <v>0.25</v>
       </c>
       <c r="P77" s="28" t="s">
         <v>378</v>
@@ -16203,15 +16203,15 @@
         <v>1</v>
       </c>
       <c r="G94" s="15" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="H94" s="21" t="n">
         <f aca="false">F94+G94</f>
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="I94" s="2" t="n">
         <f aca="false">ROUND(H94*60,0)</f>
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="J94" s="2" t="n">
         <f aca="false">ROUND(F94*60,0)</f>
@@ -16219,14 +16219,14 @@
       </c>
       <c r="K94" s="2" t="n">
         <f aca="false">ROUND(G94*60,0)</f>
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="L94" s="9" t="s">
         <v>87</v>
       </c>
       <c r="M94" s="22" t="n">
         <f aca="false">F94*IF(L94="CFO",Assumptions!$B$5,Assumptions!$B$4)+G94*Assumptions!$B$5</f>
-        <v>270</v>
+        <v>220</v>
       </c>
       <c r="N94" s="16" t="n">
         <f aca="false">F94*INDEX(Assumptions!$B$8:$B$14,MATCH(E94,Assumptions!$A$8:$A$14,0))</f>
@@ -16234,7 +16234,7 @@
       </c>
       <c r="O94" s="16" t="n">
         <f aca="false">G94*INDEX(Assumptions!$B$8:$B$14,MATCH(E94,Assumptions!$A$8:$A$14,0))</f>
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="P94" s="23" t="s">
         <v>227</v>
@@ -16897,41 +16897,41 @@
         <v>15</v>
       </c>
       <c r="F105" s="15" t="n">
-        <v>0.8333</v>
+        <v>1</v>
       </c>
       <c r="G105" s="15" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="H105" s="21" t="n">
         <f aca="false">F105+G105</f>
-        <v>1.5333</v>
+        <v>1.5</v>
       </c>
       <c r="I105" s="2" t="n">
         <f aca="false">ROUND(H105*60,0)</f>
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="J105" s="2" t="n">
         <f aca="false">ROUND(F105*60,0)</f>
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="K105" s="2" t="n">
         <f aca="false">ROUND(G105*60,0)</f>
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="L105" s="9" t="s">
         <v>87</v>
       </c>
       <c r="M105" s="22" t="n">
         <f aca="false">F105*IF(L105="CFO",Assumptions!$B$5,Assumptions!$B$4)+G105*Assumptions!$B$5</f>
-        <v>254.1635</v>
+        <v>220</v>
       </c>
       <c r="N105" s="16" t="n">
         <f aca="false">F105*INDEX(Assumptions!$B$8:$B$14,MATCH(E105,Assumptions!$A$8:$A$14,0))</f>
-        <v>0.8333</v>
+        <v>1</v>
       </c>
       <c r="O105" s="16" t="n">
         <f aca="false">G105*INDEX(Assumptions!$B$8:$B$14,MATCH(E105,Assumptions!$A$8:$A$14,0))</f>
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="P105" s="28" t="s">
         <v>378</v>
@@ -18163,41 +18163,41 @@
         <v>13</v>
       </c>
       <c r="F125" s="15" t="n">
-        <v>7.25</v>
+        <v>7.5833</v>
       </c>
       <c r="G125" s="15" t="n">
-        <v>0.7</v>
+        <v>0.35</v>
       </c>
       <c r="H125" s="21" t="n">
         <f aca="false">F125+G125</f>
-        <v>7.95</v>
+        <v>7.9333</v>
       </c>
       <c r="I125" s="2" t="n">
         <f aca="false">ROUND(H125*60,0)</f>
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="J125" s="2" t="n">
         <f aca="false">ROUND(F125*60,0)</f>
-        <v>435</v>
+        <v>455</v>
       </c>
       <c r="K125" s="2" t="n">
         <f aca="false">ROUND(G125*60,0)</f>
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="L125" s="9" t="s">
         <v>87</v>
       </c>
       <c r="M125" s="22" t="n">
         <f aca="false">F125*IF(L125="CFO",Assumptions!$B$5,Assumptions!$B$4)+G125*Assumptions!$B$5</f>
-        <v>863.75</v>
+        <v>807.9135</v>
       </c>
       <c r="N125" s="16" t="n">
         <f aca="false">F125*INDEX(Assumptions!$B$8:$B$14,MATCH(E125,Assumptions!$A$8:$A$14,0))</f>
-        <v>2.41666666666667</v>
+        <v>2.52776666666667</v>
       </c>
       <c r="O125" s="16" t="n">
         <f aca="false">G125*INDEX(Assumptions!$B$8:$B$14,MATCH(E125,Assumptions!$A$8:$A$14,0))</f>
-        <v>0.233333333333333</v>
+        <v>0.116666666666667</v>
       </c>
       <c r="P125" s="28" t="s">
         <v>314</v>
@@ -18522,7 +18522,7 @@
       </c>
       <c r="O5" s="8" t="str">
         <f aca="false">INDEX('Recurring Budgets'!$Q$2:$Q$125,MATCH(P5,'Recurring Budgets'!$A$2:$A$125,0))</f>
-        <v>Includes Month-end 0.5. Review = 1.25h (only 2 reviewed close(s) in Harvest; 0.7h standard applied as minimum).</v>
+        <v>Includes Month-end 0.5. Review = 1.25h as logged (only 2 reviewed close(s) in Harvest – check).</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>236</v>
@@ -19809,7 +19809,7 @@
       </c>
       <c r="O28" s="8" t="str">
         <f aca="false">INDEX('Recurring Budgets'!$Q$2:$Q$125,MATCH(P28,'Recurring Budgets'!$A$2:$A$125,0))</f>
-        <v>Includes Month-end 2.6, Bookkeeping 0.9. Review = 1.10h (only 2 reviewed close(s) in Harvest; 0.7h standard applied as minimum).</v>
+        <v>Includes Month-end 2.6, Bookkeeping 0.9. Review = 1.10h as logged (only 2 reviewed close(s) in Harvest – check).</v>
       </c>
       <c r="P28" s="2" t="s">
         <v>285</v>
@@ -20310,7 +20310,7 @@
       </c>
       <c r="O37" s="8" t="str">
         <f aca="false">INDEX('Recurring Budgets'!$Q$2:$Q$125,MATCH(P37,'Recurring Budgets'!$A$2:$A$125,0))</f>
-        <v>Includes Month-end 1.2, Bookkeeping 0.5, Payroll 1.3, Sales tax 0.8. Review = 1.25h (only 2 reviewed close(s) in Harvest; 0.7h standard applied as minimum).</v>
+        <v>Includes Month-end 1.2, Bookkeeping 0.5, Payroll 1.3, Sales tax 0.8. Review = 1.25h as logged (only 2 reviewed close(s) in Harvest – check).</v>
       </c>
       <c r="P37" s="2" t="s">
         <v>295</v>
@@ -20367,7 +20367,7 @@
       </c>
       <c r="O38" s="8" t="str">
         <f aca="false">INDEX('Recurring Budgets'!$Q$2:$Q$125,MATCH(P38,'Recurring Budgets'!$A$2:$A$125,0))</f>
-        <v>Includes Month-end 1.2, Bookkeeping 0.5, Payroll 1.3, Sales tax 0.8. Review = 1.25h (only 2 reviewed close(s) in Harvest; 0.7h standard applied as minimum).</v>
+        <v>Includes Month-end 1.2, Bookkeeping 0.5, Payroll 1.3, Sales tax 0.8. Review = 1.25h as logged (only 2 reviewed close(s) in Harvest – check).</v>
       </c>
       <c r="P38" s="2" t="s">
         <v>295</v>
@@ -20607,23 +20607,23 @@
       </c>
       <c r="I43" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P43,'Recurring Budgets'!$A$2:$A$125,0))</f>
-        <v>2.5833</v>
+        <v>2.75</v>
       </c>
       <c r="J43" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$G$2:$G$125,MATCH(P43,'Recurring Budgets'!$A$2:$A$125,0))</f>
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K43" s="21" t="n">
         <f aca="false">I43+J43</f>
-        <v>3.2833</v>
+        <v>3.25</v>
       </c>
       <c r="L43" s="2" t="n">
         <f aca="false">ROUND(K43*60,0)</f>
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="M43" s="22" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$M$2:$M$125,MATCH(P43,'Recurring Budgets'!$A$2:$A$125,0))</f>
-        <v>820.825</v>
+        <v>812.5</v>
       </c>
       <c r="N43" s="8" t="str">
         <f aca="false">INDEX('Recurring Budgets'!$P$2:$P$125,MATCH(P43,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -20631,7 +20631,7 @@
       </c>
       <c r="O43" s="8" t="str">
         <f aca="false">INDEX('Recurring Budgets'!$Q$2:$Q$125,MATCH(P43,'Recurring Budgets'!$A$2:$A$125,0))</f>
-        <v>Includes Month-end 0.5, CFO advisory 1.9. Review = 0.7h standard (no close reviews found in Harvest).</v>
+        <v>Includes Month-end 0.5, CFO advisory 1.9. Review = 0.5h placeholder (no close reviews found in Harvest) – check.</v>
       </c>
       <c r="P43" s="2" t="s">
         <v>298</v>
@@ -21968,23 +21968,23 @@
       </c>
       <c r="I68" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P68,'Recurring Budgets'!$A$2:$A$125,0))</f>
-        <v>18.1667</v>
+        <v>18.5833</v>
       </c>
       <c r="J68" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$G$2:$G$125,MATCH(P68,'Recurring Budgets'!$A$2:$A$125,0))</f>
-        <v>0.7</v>
+        <v>0.25</v>
       </c>
       <c r="K68" s="21" t="n">
         <f aca="false">I68+J68</f>
-        <v>18.8667</v>
+        <v>18.8333</v>
       </c>
       <c r="L68" s="2" t="n">
         <f aca="false">ROUND(K68*60,0)</f>
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="M68" s="22" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$M$2:$M$125,MATCH(P68,'Recurring Budgets'!$A$2:$A$125,0))</f>
-        <v>1900.8365</v>
+        <v>1827.9135</v>
       </c>
       <c r="N68" s="8" t="str">
         <f aca="false">INDEX('Recurring Budgets'!$P$2:$P$125,MATCH(P68,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -21992,7 +21992,7 @@
       </c>
       <c r="O68" s="8" t="str">
         <f aca="false">INDEX('Recurring Budgets'!$Q$2:$Q$125,MATCH(P68,'Recurring Budgets'!$A$2:$A$125,0))</f>
-        <v>Includes Month-end 10.4, Bookkeeping 7.8, CFO advisory 0.7. Review = 0.70h (only 1 reviewed close(s) in Harvest; 0.7h standard applied as minimum).</v>
+        <v>Includes Month-end 10.4, Bookkeeping 7.8, CFO advisory 0.7. Review = 0.25h as logged (only 1 reviewed close(s) in Harvest – check).</v>
       </c>
       <c r="P68" s="2" t="s">
         <v>337</v>
@@ -24430,7 +24430,7 @@
       </c>
       <c r="O117" s="8" t="str">
         <f aca="false">INDEX('Recurring Budgets'!$Q$2:$Q$125,MATCH(P117,'Recurring Budgets'!$A$2:$A$125,0))</f>
-        <v>Includes Month-end 1.0. Review = 1.00h (only 2 reviewed close(s) in Harvest; 0.7h standard applied as minimum).</v>
+        <v>Includes Month-end 1.0. Review = 1.00h as logged (only 2 reviewed close(s) in Harvest – check).</v>
       </c>
       <c r="P117" s="2" t="s">
         <v>394</v>
@@ -25079,19 +25079,19 @@
       </c>
       <c r="J129" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$G$2:$G$125,MATCH(P129,'Recurring Budgets'!$A$2:$A$125,0))</f>
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K129" s="21" t="n">
         <f aca="false">I129+J129</f>
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="L129" s="2" t="n">
         <f aca="false">ROUND(K129*60,0)</f>
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="M129" s="22" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$M$2:$M$125,MATCH(P129,'Recurring Budgets'!$A$2:$A$125,0))</f>
-        <v>270</v>
+        <v>220</v>
       </c>
       <c r="N129" s="8" t="str">
         <f aca="false">INDEX('Recurring Budgets'!$P$2:$P$125,MATCH(P129,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -25099,7 +25099,7 @@
       </c>
       <c r="O129" s="8" t="str">
         <f aca="false">INDEX('Recurring Budgets'!$Q$2:$Q$125,MATCH(P129,'Recurring Budgets'!$A$2:$A$125,0))</f>
-        <v>Little recent history (backlog not yet worked). Close set at 1.0h from 2025 pattern, adjusted for contractor under-recording. Review = 0.7h standard (no close reviews found in Harvest).</v>
+        <v>Little recent history (backlog not yet worked). Close set at 1.0h from 2025 pattern, adjusted for contractor under-recording. Review = 0.5h placeholder (no close reviews found in Harvest) – check.</v>
       </c>
       <c r="P129" s="2" t="s">
         <v>409</v>
@@ -25190,19 +25190,19 @@
       </c>
       <c r="J131" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$G$2:$G$125,MATCH(P131,'Recurring Budgets'!$A$2:$A$125,0))</f>
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K131" s="21" t="n">
         <f aca="false">I131+J131</f>
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="L131" s="2" t="n">
         <f aca="false">ROUND(K131*60,0)</f>
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="M131" s="22" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$M$2:$M$125,MATCH(P131,'Recurring Budgets'!$A$2:$A$125,0))</f>
-        <v>270</v>
+        <v>220</v>
       </c>
       <c r="N131" s="8" t="str">
         <f aca="false">INDEX('Recurring Budgets'!$P$2:$P$125,MATCH(P131,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -25210,7 +25210,7 @@
       </c>
       <c r="O131" s="8" t="str">
         <f aca="false">INDEX('Recurring Budgets'!$Q$2:$Q$125,MATCH(P131,'Recurring Budgets'!$A$2:$A$125,0))</f>
-        <v>Little recent history (backlog not yet worked). Close set at 1.0h from 2025 pattern, adjusted for contractor under-recording. Review = 0.7h standard (no close reviews found in Harvest).</v>
+        <v>Little recent history (backlog not yet worked). Close set at 1.0h from 2025 pattern, adjusted for contractor under-recording. Review = 0.5h placeholder (no close reviews found in Harvest) – check.</v>
       </c>
       <c r="P131" s="2" t="s">
         <v>409</v>
@@ -25247,19 +25247,19 @@
       </c>
       <c r="J132" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$G$2:$G$125,MATCH(P132,'Recurring Budgets'!$A$2:$A$125,0))</f>
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K132" s="21" t="n">
         <f aca="false">I132+J132</f>
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="L132" s="2" t="n">
         <f aca="false">ROUND(K132*60,0)</f>
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="M132" s="22" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$M$2:$M$125,MATCH(P132,'Recurring Budgets'!$A$2:$A$125,0))</f>
-        <v>270</v>
+        <v>220</v>
       </c>
       <c r="N132" s="8" t="str">
         <f aca="false">INDEX('Recurring Budgets'!$P$2:$P$125,MATCH(P132,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -25267,7 +25267,7 @@
       </c>
       <c r="O132" s="8" t="str">
         <f aca="false">INDEX('Recurring Budgets'!$Q$2:$Q$125,MATCH(P132,'Recurring Budgets'!$A$2:$A$125,0))</f>
-        <v>Little recent history (backlog not yet worked). Close set at 1.0h from 2025 pattern, adjusted for contractor under-recording. Review = 0.7h standard (no close reviews found in Harvest).</v>
+        <v>Little recent history (backlog not yet worked). Close set at 1.0h from 2025 pattern, adjusted for contractor under-recording. Review = 0.5h placeholder (no close reviews found in Harvest) – check.</v>
       </c>
       <c r="P132" s="2" t="s">
         <v>409</v>
@@ -25304,19 +25304,19 @@
       </c>
       <c r="J133" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$G$2:$G$125,MATCH(P133,'Recurring Budgets'!$A$2:$A$125,0))</f>
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K133" s="21" t="n">
         <f aca="false">I133+J133</f>
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="L133" s="2" t="n">
         <f aca="false">ROUND(K133*60,0)</f>
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="M133" s="22" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$M$2:$M$125,MATCH(P133,'Recurring Budgets'!$A$2:$A$125,0))</f>
-        <v>270</v>
+        <v>220</v>
       </c>
       <c r="N133" s="8" t="str">
         <f aca="false">INDEX('Recurring Budgets'!$P$2:$P$125,MATCH(P133,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -25324,7 +25324,7 @@
       </c>
       <c r="O133" s="8" t="str">
         <f aca="false">INDEX('Recurring Budgets'!$Q$2:$Q$125,MATCH(P133,'Recurring Budgets'!$A$2:$A$125,0))</f>
-        <v>Little recent history (backlog not yet worked). Close set at 1.0h from 2025 pattern, adjusted for contractor under-recording. Review = 0.7h standard (no close reviews found in Harvest).</v>
+        <v>Little recent history (backlog not yet worked). Close set at 1.0h from 2025 pattern, adjusted for contractor under-recording. Review = 0.5h placeholder (no close reviews found in Harvest) – check.</v>
       </c>
       <c r="P133" s="2" t="s">
         <v>409</v>
@@ -25361,19 +25361,19 @@
       </c>
       <c r="J134" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$G$2:$G$125,MATCH(P134,'Recurring Budgets'!$A$2:$A$125,0))</f>
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K134" s="21" t="n">
         <f aca="false">I134+J134</f>
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="L134" s="2" t="n">
         <f aca="false">ROUND(K134*60,0)</f>
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="M134" s="22" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$M$2:$M$125,MATCH(P134,'Recurring Budgets'!$A$2:$A$125,0))</f>
-        <v>270</v>
+        <v>220</v>
       </c>
       <c r="N134" s="8" t="str">
         <f aca="false">INDEX('Recurring Budgets'!$P$2:$P$125,MATCH(P134,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -25381,7 +25381,7 @@
       </c>
       <c r="O134" s="8" t="str">
         <f aca="false">INDEX('Recurring Budgets'!$Q$2:$Q$125,MATCH(P134,'Recurring Budgets'!$A$2:$A$125,0))</f>
-        <v>Little recent history (backlog not yet worked). Close set at 1.0h from 2025 pattern, adjusted for contractor under-recording. Review = 0.7h standard (no close reviews found in Harvest).</v>
+        <v>Little recent history (backlog not yet worked). Close set at 1.0h from 2025 pattern, adjusted for contractor under-recording. Review = 0.5h placeholder (no close reviews found in Harvest) – check.</v>
       </c>
       <c r="P134" s="2" t="s">
         <v>409</v>
@@ -25418,19 +25418,19 @@
       </c>
       <c r="J135" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$G$2:$G$125,MATCH(P135,'Recurring Budgets'!$A$2:$A$125,0))</f>
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K135" s="21" t="n">
         <f aca="false">I135+J135</f>
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="L135" s="2" t="n">
         <f aca="false">ROUND(K135*60,0)</f>
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="M135" s="22" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$M$2:$M$125,MATCH(P135,'Recurring Budgets'!$A$2:$A$125,0))</f>
-        <v>270</v>
+        <v>220</v>
       </c>
       <c r="N135" s="8" t="str">
         <f aca="false">INDEX('Recurring Budgets'!$P$2:$P$125,MATCH(P135,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -25438,7 +25438,7 @@
       </c>
       <c r="O135" s="8" t="str">
         <f aca="false">INDEX('Recurring Budgets'!$Q$2:$Q$125,MATCH(P135,'Recurring Budgets'!$A$2:$A$125,0))</f>
-        <v>Little recent history (backlog not yet worked). Close set at 1.0h from 2025 pattern, adjusted for contractor under-recording. Review = 0.7h standard (no close reviews found in Harvest).</v>
+        <v>Little recent history (backlog not yet worked). Close set at 1.0h from 2025 pattern, adjusted for contractor under-recording. Review = 0.5h placeholder (no close reviews found in Harvest) – check.</v>
       </c>
       <c r="P135" s="2" t="s">
         <v>409</v>
@@ -25475,19 +25475,19 @@
       </c>
       <c r="J136" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$G$2:$G$125,MATCH(P136,'Recurring Budgets'!$A$2:$A$125,0))</f>
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K136" s="21" t="n">
         <f aca="false">I136+J136</f>
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="L136" s="2" t="n">
         <f aca="false">ROUND(K136*60,0)</f>
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="M136" s="22" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$M$2:$M$125,MATCH(P136,'Recurring Budgets'!$A$2:$A$125,0))</f>
-        <v>270</v>
+        <v>220</v>
       </c>
       <c r="N136" s="8" t="str">
         <f aca="false">INDEX('Recurring Budgets'!$P$2:$P$125,MATCH(P136,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -25495,7 +25495,7 @@
       </c>
       <c r="O136" s="8" t="str">
         <f aca="false">INDEX('Recurring Budgets'!$Q$2:$Q$125,MATCH(P136,'Recurring Budgets'!$A$2:$A$125,0))</f>
-        <v>Little recent history (backlog not yet worked). Close set at 1.0h from 2025 pattern, adjusted for contractor under-recording. Review = 0.7h standard (no close reviews found in Harvest).</v>
+        <v>Little recent history (backlog not yet worked). Close set at 1.0h from 2025 pattern, adjusted for contractor under-recording. Review = 0.5h placeholder (no close reviews found in Harvest) – check.</v>
       </c>
       <c r="P136" s="2" t="s">
         <v>409</v>
@@ -25532,19 +25532,19 @@
       </c>
       <c r="J137" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$G$2:$G$125,MATCH(P137,'Recurring Budgets'!$A$2:$A$125,0))</f>
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K137" s="21" t="n">
         <f aca="false">I137+J137</f>
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="L137" s="2" t="n">
         <f aca="false">ROUND(K137*60,0)</f>
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="M137" s="22" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$M$2:$M$125,MATCH(P137,'Recurring Budgets'!$A$2:$A$125,0))</f>
-        <v>270</v>
+        <v>220</v>
       </c>
       <c r="N137" s="8" t="str">
         <f aca="false">INDEX('Recurring Budgets'!$P$2:$P$125,MATCH(P137,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -25552,7 +25552,7 @@
       </c>
       <c r="O137" s="8" t="str">
         <f aca="false">INDEX('Recurring Budgets'!$Q$2:$Q$125,MATCH(P137,'Recurring Budgets'!$A$2:$A$125,0))</f>
-        <v>Little recent history (backlog not yet worked). Close set at 1.0h from 2025 pattern, adjusted for contractor under-recording. Review = 0.7h standard (no close reviews found in Harvest).</v>
+        <v>Little recent history (backlog not yet worked). Close set at 1.0h from 2025 pattern, adjusted for contractor under-recording. Review = 0.5h placeholder (no close reviews found in Harvest) – check.</v>
       </c>
       <c r="P137" s="2" t="s">
         <v>409</v>
@@ -25589,19 +25589,19 @@
       </c>
       <c r="J138" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$G$2:$G$125,MATCH(P138,'Recurring Budgets'!$A$2:$A$125,0))</f>
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K138" s="21" t="n">
         <f aca="false">I138+J138</f>
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="L138" s="2" t="n">
         <f aca="false">ROUND(K138*60,0)</f>
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="M138" s="22" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$M$2:$M$125,MATCH(P138,'Recurring Budgets'!$A$2:$A$125,0))</f>
-        <v>270</v>
+        <v>220</v>
       </c>
       <c r="N138" s="8" t="str">
         <f aca="false">INDEX('Recurring Budgets'!$P$2:$P$125,MATCH(P138,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -25609,7 +25609,7 @@
       </c>
       <c r="O138" s="8" t="str">
         <f aca="false">INDEX('Recurring Budgets'!$Q$2:$Q$125,MATCH(P138,'Recurring Budgets'!$A$2:$A$125,0))</f>
-        <v>Little recent history (backlog not yet worked). Close set at 1.0h from 2025 pattern, adjusted for contractor under-recording. Review = 0.7h standard (no close reviews found in Harvest).</v>
+        <v>Little recent history (backlog not yet worked). Close set at 1.0h from 2025 pattern, adjusted for contractor under-recording. Review = 0.5h placeholder (no close reviews found in Harvest) – check.</v>
       </c>
       <c r="P138" s="2" t="s">
         <v>409</v>
@@ -26350,23 +26350,23 @@
       </c>
       <c r="I152" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P152,'Recurring Budgets'!$A$2:$A$125,0))</f>
-        <v>0.8333</v>
+        <v>1</v>
       </c>
       <c r="J152" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$G$2:$G$125,MATCH(P152,'Recurring Budgets'!$A$2:$A$125,0))</f>
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K152" s="21" t="n">
         <f aca="false">I152+J152</f>
-        <v>1.5333</v>
+        <v>1.5</v>
       </c>
       <c r="L152" s="2" t="n">
         <f aca="false">ROUND(K152*60,0)</f>
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="M152" s="22" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$M$2:$M$125,MATCH(P152,'Recurring Budgets'!$A$2:$A$125,0))</f>
-        <v>254.1635</v>
+        <v>220</v>
       </c>
       <c r="N152" s="8" t="str">
         <f aca="false">INDEX('Recurring Budgets'!$P$2:$P$125,MATCH(P152,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -26374,7 +26374,7 @@
       </c>
       <c r="O152" s="8" t="str">
         <f aca="false">INDEX('Recurring Budgets'!$Q$2:$Q$125,MATCH(P152,'Recurring Budgets'!$A$2:$A$125,0))</f>
-        <v>Includes Month-end 0.2, Bookkeeping 0.5, Sales tax 0.2, CFO advisory 0.6. Catch-up still underway; steady level uncertain. Backlog closes carry the remaining catch-up (~15–20h). Review = 0.7h standard (no close reviews found in Harvest).</v>
+        <v>Includes Month-end 0.2, Bookkeeping 0.5, Sales tax 0.2, CFO advisory 0.6. Catch-up still underway; steady level uncertain. Backlog closes carry the remaining catch-up (~15–20h). Review = 0.5h placeholder (no close reviews found in Harvest) – check.</v>
       </c>
       <c r="P152" s="2" t="s">
         <v>428</v>
@@ -26560,23 +26560,23 @@
       </c>
       <c r="I156" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P156,'Recurring Budgets'!$A$2:$A$125,0))</f>
-        <v>0.8333</v>
+        <v>1</v>
       </c>
       <c r="J156" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$G$2:$G$125,MATCH(P156,'Recurring Budgets'!$A$2:$A$125,0))</f>
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K156" s="21" t="n">
         <f aca="false">I156+J156</f>
-        <v>1.5333</v>
+        <v>1.5</v>
       </c>
       <c r="L156" s="2" t="n">
         <f aca="false">ROUND(K156*60,0)</f>
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="M156" s="22" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$M$2:$M$125,MATCH(P156,'Recurring Budgets'!$A$2:$A$125,0))</f>
-        <v>254.1635</v>
+        <v>220</v>
       </c>
       <c r="N156" s="8" t="str">
         <f aca="false">INDEX('Recurring Budgets'!$P$2:$P$125,MATCH(P156,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -26584,7 +26584,7 @@
       </c>
       <c r="O156" s="8" t="str">
         <f aca="false">INDEX('Recurring Budgets'!$Q$2:$Q$125,MATCH(P156,'Recurring Budgets'!$A$2:$A$125,0))</f>
-        <v>Includes Month-end 0.2, Bookkeeping 0.5, Sales tax 0.2, CFO advisory 0.6. Catch-up still underway; steady level uncertain. Backlog closes carry the remaining catch-up (~15–20h). Review = 0.7h standard (no close reviews found in Harvest).</v>
+        <v>Includes Month-end 0.2, Bookkeeping 0.5, Sales tax 0.2, CFO advisory 0.6. Catch-up still underway; steady level uncertain. Backlog closes carry the remaining catch-up (~15–20h). Review = 0.5h placeholder (no close reviews found in Harvest) – check.</v>
       </c>
       <c r="P156" s="2" t="s">
         <v>428</v>
@@ -28006,23 +28006,23 @@
       </c>
       <c r="I182" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P182,'Recurring Budgets'!$A$2:$A$125,0))</f>
-        <v>7.25</v>
+        <v>7.5833</v>
       </c>
       <c r="J182" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$G$2:$G$125,MATCH(P182,'Recurring Budgets'!$A$2:$A$125,0))</f>
-        <v>0.7</v>
+        <v>0.35</v>
       </c>
       <c r="K182" s="21" t="n">
         <f aca="false">I182+J182</f>
-        <v>7.95</v>
+        <v>7.9333</v>
       </c>
       <c r="L182" s="2" t="n">
         <f aca="false">ROUND(K182*60,0)</f>
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="M182" s="22" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$M$2:$M$125,MATCH(P182,'Recurring Budgets'!$A$2:$A$125,0))</f>
-        <v>863.75</v>
+        <v>807.9135</v>
       </c>
       <c r="N182" s="8" t="str">
         <f aca="false">INDEX('Recurring Budgets'!$P$2:$P$125,MATCH(P182,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -28030,7 +28030,7 @@
       </c>
       <c r="O182" s="8" t="str">
         <f aca="false">INDEX('Recurring Budgets'!$Q$2:$Q$125,MATCH(P182,'Recurring Budgets'!$A$2:$A$125,0))</f>
-        <v>Includes Month-end 6.5, Payroll 1.2. Review = 0.70h (only 1 reviewed close(s) in Harvest; 0.7h standard applied as minimum).</v>
+        <v>Includes Month-end 6.5, Payroll 1.2. Review = 0.35h as logged (only 1 reviewed close(s) in Harvest – check).</v>
       </c>
       <c r="P182" s="2" t="s">
         <v>463</v>
@@ -28063,23 +28063,23 @@
       </c>
       <c r="I183" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$F$2:$F$125,MATCH(P183,'Recurring Budgets'!$A$2:$A$125,0))</f>
-        <v>7.25</v>
+        <v>7.5833</v>
       </c>
       <c r="J183" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$G$2:$G$125,MATCH(P183,'Recurring Budgets'!$A$2:$A$125,0))</f>
-        <v>0.7</v>
+        <v>0.35</v>
       </c>
       <c r="K183" s="21" t="n">
         <f aca="false">I183+J183</f>
-        <v>7.95</v>
+        <v>7.9333</v>
       </c>
       <c r="L183" s="2" t="n">
         <f aca="false">ROUND(K183*60,0)</f>
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="M183" s="22" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$M$2:$M$125,MATCH(P183,'Recurring Budgets'!$A$2:$A$125,0))</f>
-        <v>863.75</v>
+        <v>807.9135</v>
       </c>
       <c r="N183" s="8" t="str">
         <f aca="false">INDEX('Recurring Budgets'!$P$2:$P$125,MATCH(P183,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -28087,7 +28087,7 @@
       </c>
       <c r="O183" s="8" t="str">
         <f aca="false">INDEX('Recurring Budgets'!$Q$2:$Q$125,MATCH(P183,'Recurring Budgets'!$A$2:$A$125,0))</f>
-        <v>Includes Month-end 6.5, Payroll 1.2. Review = 0.70h (only 1 reviewed close(s) in Harvest; 0.7h standard applied as minimum).</v>
+        <v>Includes Month-end 6.5, Payroll 1.2. Review = 0.35h as logged (only 1 reviewed close(s) in Harvest – check).</v>
       </c>
       <c r="P183" s="2" t="s">
         <v>463</v>
@@ -28178,23 +28178,23 @@
       <c r="H186" s="2"/>
       <c r="I186" s="4" t="n">
         <f aca="false">SUM(I2:I184)</f>
-        <v>549.146</v>
+        <v>550.7293</v>
       </c>
       <c r="J186" s="4" t="n">
         <f aca="false">SUM(J2:J184)</f>
-        <v>55.3831</v>
+        <v>51.8331</v>
       </c>
       <c r="K186" s="4" t="n">
         <f aca="false">SUM(K2:K184)</f>
-        <v>604.5291</v>
+        <v>602.5624</v>
       </c>
       <c r="L186" s="4" t="n">
         <f aca="false">SUM(L2:L184)</f>
-        <v>36276</v>
+        <v>36158</v>
       </c>
       <c r="M186" s="32" t="n">
         <f aca="false">SUM(M2:M184)</f>
-        <v>73092.9835</v>
+        <v>72381.7355</v>
       </c>
       <c r="N186" s="2"/>
       <c r="O186" s="2"/>
@@ -28567,15 +28567,15 @@
       </c>
       <c r="B18" s="34" t="n">
         <f aca="false">SUMIFS('Recurring Budgets'!$N$2:$N$125,'Recurring Budgets'!$B$2:$B$125,A18)</f>
-        <v>3.24996666666667</v>
+        <v>3.41666666666667</v>
       </c>
       <c r="C18" s="34" t="n">
         <f aca="false">SUMIFS('Recurring Budgets'!$O$2:$O$125,'Recurring Budgets'!$B$2:$B$125,A18)</f>
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="D18" s="35" t="n">
         <f aca="false">B18+C18</f>
-        <v>3.94996666666667</v>
+        <v>3.91666666666667</v>
       </c>
       <c r="E18" s="25" t="s">
         <v>232</v>
@@ -28764,15 +28764,15 @@
       </c>
       <c r="B27" s="34" t="n">
         <f aca="false">SUMIFS('Recurring Budgets'!$N$2:$N$125,'Recurring Budgets'!$B$2:$B$125,A27)</f>
-        <v>6.36111666666667</v>
+        <v>6.49998333333333</v>
       </c>
       <c r="C27" s="34" t="n">
         <f aca="false">SUMIFS('Recurring Budgets'!$O$2:$O$125,'Recurring Budgets'!$B$2:$B$125,A27)</f>
-        <v>0.233333333333333</v>
+        <v>0.0833333333333333</v>
       </c>
       <c r="D27" s="35" t="n">
         <f aca="false">B27+C27</f>
-        <v>6.59445</v>
+        <v>6.58331666666667</v>
       </c>
       <c r="E27" s="25" t="s">
         <v>232</v>
@@ -28915,15 +28915,15 @@
       </c>
       <c r="B34" s="34" t="n">
         <f aca="false">SUMIFS('Recurring Budgets'!$N$2:$N$125,'Recurring Budgets'!$B$2:$B$125,A34)</f>
-        <v>7.625</v>
+        <v>8.0417</v>
       </c>
       <c r="C34" s="34" t="n">
         <f aca="false">SUMIFS('Recurring Budgets'!$O$2:$O$125,'Recurring Budgets'!$B$2:$B$125,A34)</f>
-        <v>1.60285</v>
+        <v>1.15285</v>
       </c>
       <c r="D34" s="35" t="n">
         <f aca="false">B34+C34</f>
-        <v>9.22785</v>
+        <v>9.19455</v>
       </c>
       <c r="E34" s="28" t="s">
         <v>378</v>
@@ -29047,11 +29047,11 @@
       </c>
       <c r="C40" s="34" t="n">
         <f aca="false">SUMIFS('Recurring Budgets'!$O$2:$O$125,'Recurring Budgets'!$B$2:$B$125,A40)</f>
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="D40" s="35" t="n">
         <f aca="false">B40+C40</f>
-        <v>2.102775</v>
+        <v>1.902775</v>
       </c>
       <c r="E40" s="25" t="s">
         <v>232</v>
@@ -29129,15 +29129,15 @@
       </c>
       <c r="B44" s="34" t="n">
         <f aca="false">SUMIFS('Recurring Budgets'!$N$2:$N$125,'Recurring Budgets'!$B$2:$B$125,A44)</f>
-        <v>1.87496666666667</v>
+        <v>2.04166666666667</v>
       </c>
       <c r="C44" s="34" t="n">
         <f aca="false">SUMIFS('Recurring Budgets'!$O$2:$O$125,'Recurring Budgets'!$B$2:$B$125,A44)</f>
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="D44" s="35" t="n">
         <f aca="false">B44+C44</f>
-        <v>2.57496666666667</v>
+        <v>2.54166666666667</v>
       </c>
       <c r="E44" s="28" t="s">
         <v>378</v>
@@ -29261,15 +29261,15 @@
       </c>
       <c r="B50" s="34" t="n">
         <f aca="false">SUMIFS('Recurring Budgets'!$N$2:$N$125,'Recurring Budgets'!$B$2:$B$125,A50)</f>
-        <v>2.66666666666667</v>
+        <v>2.77776666666667</v>
       </c>
       <c r="C50" s="34" t="n">
         <f aca="false">SUMIFS('Recurring Budgets'!$O$2:$O$125,'Recurring Budgets'!$B$2:$B$125,A50)</f>
-        <v>0.233333333333333</v>
+        <v>0.116666666666667</v>
       </c>
       <c r="D50" s="35" t="n">
         <f aca="false">B50+C50</f>
-        <v>2.9</v>
+        <v>2.89443333333333</v>
       </c>
       <c r="E50" s="28" t="s">
         <v>314</v>
@@ -29282,15 +29282,15 @@
       </c>
       <c r="B51" s="19" t="n">
         <f aca="false">SUM(B4:B50)</f>
-        <v>274.200525</v>
+        <v>275.200591666667</v>
       </c>
       <c r="C51" s="19" t="n">
         <f aca="false">SUM(C4:C50)</f>
-        <v>33.78595</v>
+        <v>32.4692833333333</v>
       </c>
       <c r="D51" s="19" t="n">
         <f aca="false">SUM(D4:D50)</f>
-        <v>307.986475</v>
+        <v>307.669875</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" s="2"/>
@@ -29335,15 +29335,15 @@
       </c>
       <c r="B55" s="4" t="n">
         <f aca="false">B51+B54</f>
-        <v>284.200525</v>
+        <v>285.200591666667</v>
       </c>
       <c r="C55" s="4" t="n">
         <f aca="false">C51+C53</f>
-        <v>58.78595</v>
+        <v>57.4692833333333</v>
       </c>
       <c r="D55" s="4" t="n">
         <f aca="false">B55+C55</f>
-        <v>342.986475</v>
+        <v>342.669875</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" s="2"/>

--- a/budget-hours/Karbon_Budget_Hours_2026-10.xlsx
+++ b/budget-hours/Karbon_Budget_Hours_2026-10.xlsx
@@ -1172,7 +1172,7 @@
     <t xml:space="preserve">Low</t>
   </si>
   <si>
-    <t xml:space="preserve">SUGGESTED – no recurring month-end item in the Oct list (only the July clean-up). Payroll takeover in progress (Paychex/401k/PFML); tax audit budgeted separately. Confirm payroll is ongoing. Review = 0.25h as logged (only 1 reviewed close(s) in Harvest – check).</t>
+    <t xml:space="preserve">SUGGESTED – no recurring month-end item in the Oct list (only the July clean-up). Payroll takeover in progress (Paychex/401k/PFML); tax audit budgeted separately. Confirm payroll is ongoing. Review = 0.25h as logged (only 1 reviewed close(s) in Harvest – check). Review set to 0:50 per Josephine (CYMA login 5–8 min, complex system; 0.7–1h).</t>
   </si>
   <si>
     <t xml:space="preserve">Newport Classic Cars LLC|1099|1099 Quarterly Review|1099</t>
@@ -4833,11 +4833,11 @@
       </c>
       <c r="F71" s="6" t="n">
         <f aca="false">ROUND('Recurring Budgets'!G77*60,0)/1440</f>
-        <v>0.0104166666666667</v>
+        <v>0.0347222222222222</v>
       </c>
       <c r="G71" s="7" t="n">
         <f aca="false">ROUND('Recurring Budgets'!G77*Assumptions!$B$5,0)</f>
-        <v>63</v>
+        <v>208</v>
       </c>
       <c r="H71" s="8" t="str">
         <f aca="false">'Recurring Budgets'!L77</f>
@@ -15134,15 +15134,15 @@
         <v>4.6667</v>
       </c>
       <c r="G77" s="15" t="n">
-        <v>0.25</v>
+        <v>0.8333</v>
       </c>
       <c r="H77" s="21" t="n">
         <f aca="false">F77+G77</f>
-        <v>4.9167</v>
+        <v>5.5</v>
       </c>
       <c r="I77" s="2" t="n">
         <f aca="false">ROUND(H77*60,0)</f>
-        <v>295</v>
+        <v>330</v>
       </c>
       <c r="J77" s="2" t="n">
         <f aca="false">ROUND(F77*60,0)</f>
@@ -15150,14 +15150,14 @@
       </c>
       <c r="K77" s="2" t="n">
         <f aca="false">ROUND(G77*60,0)</f>
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="L77" s="9" t="s">
         <v>87</v>
       </c>
       <c r="M77" s="22" t="n">
         <f aca="false">F77*IF(L77="CFO",Assumptions!$B$5,Assumptions!$B$4)+G77*Assumptions!$B$5</f>
-        <v>505.8365</v>
+        <v>651.6615</v>
       </c>
       <c r="N77" s="16" t="n">
         <f aca="false">F77*INDEX(Assumptions!$B$8:$B$14,MATCH(E77,Assumptions!$A$8:$A$14,0))</f>
@@ -15165,7 +15165,7 @@
       </c>
       <c r="O77" s="16" t="n">
         <f aca="false">G77*INDEX(Assumptions!$B$8:$B$14,MATCH(E77,Assumptions!$A$8:$A$14,0))</f>
-        <v>0.25</v>
+        <v>0.8333</v>
       </c>
       <c r="P77" s="28" t="s">
         <v>378</v>
@@ -28919,11 +28919,11 @@
       </c>
       <c r="C34" s="34" t="n">
         <f aca="false">SUMIFS('Recurring Budgets'!$O$2:$O$125,'Recurring Budgets'!$B$2:$B$125,A34)</f>
-        <v>1.15285</v>
+        <v>1.73615</v>
       </c>
       <c r="D34" s="35" t="n">
         <f aca="false">B34+C34</f>
-        <v>9.19455</v>
+        <v>9.77785</v>
       </c>
       <c r="E34" s="28" t="s">
         <v>378</v>
@@ -29286,11 +29286,11 @@
       </c>
       <c r="C51" s="19" t="n">
         <f aca="false">SUM(C4:C50)</f>
-        <v>32.4692833333333</v>
+        <v>33.0525833333333</v>
       </c>
       <c r="D51" s="19" t="n">
         <f aca="false">SUM(D4:D50)</f>
-        <v>307.669875</v>
+        <v>308.253175</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" s="2"/>
@@ -29339,11 +29339,11 @@
       </c>
       <c r="C55" s="4" t="n">
         <f aca="false">C51+C53</f>
-        <v>57.4692833333333</v>
+        <v>58.0525833333333</v>
       </c>
       <c r="D55" s="4" t="n">
         <f aca="false">B55+C55</f>
-        <v>342.669875</v>
+        <v>343.253175</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" s="2"/>

--- a/budget-hours/Karbon_Budget_Hours_2026-10.xlsx
+++ b/budget-hours/Karbon_Budget_Hours_2026-10.xlsx
@@ -1049,7 +1049,7 @@
     <t xml:space="preserve">GAV Enterprises Inc|Accounting|Quarter End Close|Quarterly</t>
   </si>
   <si>
-    <t xml:space="preserve">Includes Month-end 10.4, Bookkeeping 7.8, CFO advisory 0.7. Review = 0.25h as logged (only 1 reviewed close(s) in Harvest – check).</t>
+    <t xml:space="preserve">Includes Month-end 10.4, Bookkeeping 7.8, CFO advisory 0.7. Review = 0.25h as logged (only 1 reviewed close(s) in Harvest – check). Quarterly review from history: Q3 2025 Lisa 1.0 first pass + 0.5 complete = 1.5h; Jan–Jun 2024 review ~1.5h.</t>
   </si>
   <si>
     <t xml:space="preserve">International Alliance Group LLC|1099|1099 Quarterly Review|1099</t>
@@ -1427,7 +1427,7 @@
     <t xml:space="preserve">Young Wealth Management PLLC|Accounting|Quarter End Close|Quarterly</t>
   </si>
   <si>
-    <t xml:space="preserve">Includes Month-end 6.5, Payroll 1.2. Review = 0.35h as logged (only 1 reviewed close(s) in Harvest – check).</t>
+    <t xml:space="preserve">Includes Month-end 6.5, Payroll 1.2. Review = 0.35h as logged (only 1 reviewed close(s) in Harvest – check). Quarterly review from history: Lisa Q1–Q2 2025 1.5h (two quarters), Q3 2025 0.7h, Q4 2025 1.25h – about 1h per quarter.</t>
   </si>
   <si>
     <t xml:space="preserve">Work Title</t>
@@ -4337,11 +4337,11 @@
       </c>
       <c r="F55" s="6" t="n">
         <f aca="false">ROUND('Recurring Budgets'!G52*60,0)/1440</f>
-        <v>0.0104166666666667</v>
+        <v>0.0625</v>
       </c>
       <c r="G55" s="7" t="n">
         <f aca="false">ROUND('Recurring Budgets'!G52*Assumptions!$B$5,0)</f>
-        <v>63</v>
+        <v>375</v>
       </c>
       <c r="H55" s="8" t="str">
         <f aca="false">'Recurring Budgets'!L52</f>
@@ -6290,11 +6290,11 @@
       </c>
       <c r="F118" s="6" t="n">
         <f aca="false">ROUND('Recurring Budgets'!G125*60,0)/1440</f>
-        <v>0.0145833333333333</v>
+        <v>0.0416666666666667</v>
       </c>
       <c r="G118" s="7" t="n">
         <f aca="false">ROUND('Recurring Budgets'!G125*Assumptions!$B$5,0)</f>
-        <v>88</v>
+        <v>250</v>
       </c>
       <c r="H118" s="8" t="str">
         <f aca="false">'Recurring Budgets'!L125</f>
@@ -13814,15 +13814,15 @@
         <v>18.5833</v>
       </c>
       <c r="G52" s="15" t="n">
-        <v>0.25</v>
+        <v>1.5</v>
       </c>
       <c r="H52" s="21" t="n">
         <f aca="false">F52+G52</f>
-        <v>18.8333</v>
+        <v>20.0833</v>
       </c>
       <c r="I52" s="2" t="n">
         <f aca="false">ROUND(H52*60,0)</f>
-        <v>1130</v>
+        <v>1205</v>
       </c>
       <c r="J52" s="2" t="n">
         <f aca="false">ROUND(F52*60,0)</f>
@@ -13830,14 +13830,14 @@
       </c>
       <c r="K52" s="2" t="n">
         <f aca="false">ROUND(G52*60,0)</f>
-        <v>15</v>
+        <v>90</v>
       </c>
       <c r="L52" s="9" t="s">
         <v>87</v>
       </c>
       <c r="M52" s="22" t="n">
         <f aca="false">F52*IF(L52="CFO",Assumptions!$B$5,Assumptions!$B$4)+G52*Assumptions!$B$5</f>
-        <v>1827.9135</v>
+        <v>2140.4135</v>
       </c>
       <c r="N52" s="16" t="n">
         <f aca="false">F52*INDEX(Assumptions!$B$8:$B$14,MATCH(E52,Assumptions!$A$8:$A$14,0))</f>
@@ -13845,7 +13845,7 @@
       </c>
       <c r="O52" s="16" t="n">
         <f aca="false">G52*INDEX(Assumptions!$B$8:$B$14,MATCH(E52,Assumptions!$A$8:$A$14,0))</f>
-        <v>0.0833333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="P52" s="25" t="s">
         <v>232</v>
@@ -18166,15 +18166,15 @@
         <v>7.5833</v>
       </c>
       <c r="G125" s="15" t="n">
-        <v>0.35</v>
+        <v>1</v>
       </c>
       <c r="H125" s="21" t="n">
         <f aca="false">F125+G125</f>
-        <v>7.9333</v>
+        <v>8.5833</v>
       </c>
       <c r="I125" s="2" t="n">
         <f aca="false">ROUND(H125*60,0)</f>
-        <v>476</v>
+        <v>515</v>
       </c>
       <c r="J125" s="2" t="n">
         <f aca="false">ROUND(F125*60,0)</f>
@@ -18182,14 +18182,14 @@
       </c>
       <c r="K125" s="2" t="n">
         <f aca="false">ROUND(G125*60,0)</f>
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="L125" s="9" t="s">
         <v>87</v>
       </c>
       <c r="M125" s="22" t="n">
         <f aca="false">F125*IF(L125="CFO",Assumptions!$B$5,Assumptions!$B$4)+G125*Assumptions!$B$5</f>
-        <v>807.9135</v>
+        <v>970.4135</v>
       </c>
       <c r="N125" s="16" t="n">
         <f aca="false">F125*INDEX(Assumptions!$B$8:$B$14,MATCH(E125,Assumptions!$A$8:$A$14,0))</f>
@@ -18197,7 +18197,7 @@
       </c>
       <c r="O125" s="16" t="n">
         <f aca="false">G125*INDEX(Assumptions!$B$8:$B$14,MATCH(E125,Assumptions!$A$8:$A$14,0))</f>
-        <v>0.116666666666667</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="P125" s="28" t="s">
         <v>314</v>
@@ -21972,19 +21972,19 @@
       </c>
       <c r="J68" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$G$2:$G$125,MATCH(P68,'Recurring Budgets'!$A$2:$A$125,0))</f>
-        <v>0.25</v>
+        <v>1.5</v>
       </c>
       <c r="K68" s="21" t="n">
         <f aca="false">I68+J68</f>
-        <v>18.8333</v>
+        <v>20.0833</v>
       </c>
       <c r="L68" s="2" t="n">
         <f aca="false">ROUND(K68*60,0)</f>
-        <v>1130</v>
+        <v>1205</v>
       </c>
       <c r="M68" s="22" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$M$2:$M$125,MATCH(P68,'Recurring Budgets'!$A$2:$A$125,0))</f>
-        <v>1827.9135</v>
+        <v>2140.4135</v>
       </c>
       <c r="N68" s="8" t="str">
         <f aca="false">INDEX('Recurring Budgets'!$P$2:$P$125,MATCH(P68,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -21992,7 +21992,7 @@
       </c>
       <c r="O68" s="8" t="str">
         <f aca="false">INDEX('Recurring Budgets'!$Q$2:$Q$125,MATCH(P68,'Recurring Budgets'!$A$2:$A$125,0))</f>
-        <v>Includes Month-end 10.4, Bookkeeping 7.8, CFO advisory 0.7. Review = 0.25h as logged (only 1 reviewed close(s) in Harvest – check).</v>
+        <v>Includes Month-end 10.4, Bookkeeping 7.8, CFO advisory 0.7. Review = 0.25h as logged (only 1 reviewed close(s) in Harvest – check). Quarterly review from history: Q3 2025 Lisa 1.0 first pass + 0.5 complete = 1.5h; Jan–Jun 2024 review ~1.5h.</v>
       </c>
       <c r="P68" s="2" t="s">
         <v>337</v>
@@ -28010,19 +28010,19 @@
       </c>
       <c r="J182" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$G$2:$G$125,MATCH(P182,'Recurring Budgets'!$A$2:$A$125,0))</f>
-        <v>0.35</v>
+        <v>1</v>
       </c>
       <c r="K182" s="21" t="n">
         <f aca="false">I182+J182</f>
-        <v>7.9333</v>
+        <v>8.5833</v>
       </c>
       <c r="L182" s="2" t="n">
         <f aca="false">ROUND(K182*60,0)</f>
-        <v>476</v>
+        <v>515</v>
       </c>
       <c r="M182" s="22" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$M$2:$M$125,MATCH(P182,'Recurring Budgets'!$A$2:$A$125,0))</f>
-        <v>807.9135</v>
+        <v>970.4135</v>
       </c>
       <c r="N182" s="8" t="str">
         <f aca="false">INDEX('Recurring Budgets'!$P$2:$P$125,MATCH(P182,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -28030,7 +28030,7 @@
       </c>
       <c r="O182" s="8" t="str">
         <f aca="false">INDEX('Recurring Budgets'!$Q$2:$Q$125,MATCH(P182,'Recurring Budgets'!$A$2:$A$125,0))</f>
-        <v>Includes Month-end 6.5, Payroll 1.2. Review = 0.35h as logged (only 1 reviewed close(s) in Harvest – check).</v>
+        <v>Includes Month-end 6.5, Payroll 1.2. Review = 0.35h as logged (only 1 reviewed close(s) in Harvest – check). Quarterly review from history: Lisa Q1–Q2 2025 1.5h (two quarters), Q3 2025 0.7h, Q4 2025 1.25h – about 1h per quarter.</v>
       </c>
       <c r="P182" s="2" t="s">
         <v>463</v>
@@ -28067,19 +28067,19 @@
       </c>
       <c r="J183" s="16" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$G$2:$G$125,MATCH(P183,'Recurring Budgets'!$A$2:$A$125,0))</f>
-        <v>0.35</v>
+        <v>1</v>
       </c>
       <c r="K183" s="21" t="n">
         <f aca="false">I183+J183</f>
-        <v>7.9333</v>
+        <v>8.5833</v>
       </c>
       <c r="L183" s="2" t="n">
         <f aca="false">ROUND(K183*60,0)</f>
-        <v>476</v>
+        <v>515</v>
       </c>
       <c r="M183" s="22" t="n">
         <f aca="false">INDEX('Recurring Budgets'!$M$2:$M$125,MATCH(P183,'Recurring Budgets'!$A$2:$A$125,0))</f>
-        <v>807.9135</v>
+        <v>970.4135</v>
       </c>
       <c r="N183" s="8" t="str">
         <f aca="false">INDEX('Recurring Budgets'!$P$2:$P$125,MATCH(P183,'Recurring Budgets'!$A$2:$A$125,0))</f>
@@ -28087,7 +28087,7 @@
       </c>
       <c r="O183" s="8" t="str">
         <f aca="false">INDEX('Recurring Budgets'!$Q$2:$Q$125,MATCH(P183,'Recurring Budgets'!$A$2:$A$125,0))</f>
-        <v>Includes Month-end 6.5, Payroll 1.2. Review = 0.35h as logged (only 1 reviewed close(s) in Harvest – check).</v>
+        <v>Includes Month-end 6.5, Payroll 1.2. Review = 0.35h as logged (only 1 reviewed close(s) in Harvest – check). Quarterly review from history: Lisa Q1–Q2 2025 1.5h (two quarters), Q3 2025 0.7h, Q4 2025 1.25h – about 1h per quarter.</v>
       </c>
       <c r="P183" s="2" t="s">
         <v>463</v>
@@ -28182,19 +28182,19 @@
       </c>
       <c r="J186" s="4" t="n">
         <f aca="false">SUM(J2:J184)</f>
-        <v>51.8331</v>
+        <v>54.3831</v>
       </c>
       <c r="K186" s="4" t="n">
         <f aca="false">SUM(K2:K184)</f>
-        <v>602.5624</v>
+        <v>605.1124</v>
       </c>
       <c r="L186" s="4" t="n">
         <f aca="false">SUM(L2:L184)</f>
-        <v>36158</v>
+        <v>36311</v>
       </c>
       <c r="M186" s="32" t="n">
         <f aca="false">SUM(M2:M184)</f>
-        <v>72381.7355</v>
+        <v>73019.2355</v>
       </c>
       <c r="N186" s="2"/>
       <c r="O186" s="2"/>
@@ -28768,11 +28768,11 @@
       </c>
       <c r="C27" s="34" t="n">
         <f aca="false">SUMIFS('Recurring Budgets'!$O$2:$O$125,'Recurring Budgets'!$B$2:$B$125,A27)</f>
-        <v>0.0833333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="D27" s="35" t="n">
         <f aca="false">B27+C27</f>
-        <v>6.58331666666667</v>
+        <v>6.99998333333333</v>
       </c>
       <c r="E27" s="25" t="s">
         <v>232</v>
@@ -29265,11 +29265,11 @@
       </c>
       <c r="C50" s="34" t="n">
         <f aca="false">SUMIFS('Recurring Budgets'!$O$2:$O$125,'Recurring Budgets'!$B$2:$B$125,A50)</f>
-        <v>0.116666666666667</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="D50" s="35" t="n">
         <f aca="false">B50+C50</f>
-        <v>2.89443333333333</v>
+        <v>3.1111</v>
       </c>
       <c r="E50" s="28" t="s">
         <v>314</v>
@@ -29286,11 +29286,11 @@
       </c>
       <c r="C51" s="19" t="n">
         <f aca="false">SUM(C4:C50)</f>
-        <v>33.0525833333333</v>
+        <v>33.6859166666667</v>
       </c>
       <c r="D51" s="19" t="n">
         <f aca="false">SUM(D4:D50)</f>
-        <v>308.253175</v>
+        <v>308.886508333333</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" s="2"/>
@@ -29339,11 +29339,11 @@
       </c>
       <c r="C55" s="4" t="n">
         <f aca="false">C51+C53</f>
-        <v>58.0525833333333</v>
+        <v>58.6859166666667</v>
       </c>
       <c r="D55" s="4" t="n">
         <f aca="false">B55+C55</f>
-        <v>343.253175</v>
+        <v>343.886508333333</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" s="2"/>
